--- a/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\火災見積\テンプレート\new\mark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C699413-1F28-4D73-BDA5-A81CDE352944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3BD8DD-30AA-4747-A4C4-359B89C95C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="地震おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -1134,7 +1134,7 @@
     <xf numFmtId="6" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1222,196 +1222,74 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
     <xf numFmtId="179" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1420,6 +1298,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1498,112 +1394,219 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
     <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2007,10 +2010,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="95"/>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="95"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="28"/>
@@ -2020,16 +2023,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
-      <c r="O3" s="122"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="122"/>
-      <c r="R3" s="122"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+      <c r="R3" s="86"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="122"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="122"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="86"/>
+      <c r="Q4" s="86"/>
+      <c r="R4" s="86"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="27"/>
@@ -2092,196 +2095,196 @@
       <c r="R10" s="23"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="96" t="s">
+      <c r="A11" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="96"/>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="116"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="116"/>
-      <c r="H15" s="116"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="116"/>
-      <c r="K15" s="116"/>
-      <c r="L15" s="116"/>
-      <c r="M15" s="116"/>
-      <c r="N15" s="116"/>
-      <c r="O15" s="116"/>
-      <c r="P15" s="116"/>
-      <c r="Q15" s="116"/>
-      <c r="R15" s="116"/>
+      <c r="B15" s="80"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="80"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="117" t="s">
+      <c r="A18" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="117"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="117"/>
-      <c r="P18" s="117"/>
-      <c r="Q18" s="117"/>
-      <c r="R18" s="117"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="81"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="80" t="s">
+      <c r="A20" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="98"/>
-      <c r="H20" s="98"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="98"/>
-      <c r="K20" s="98"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="98"/>
-      <c r="N20" s="98"/>
-      <c r="O20" s="98"/>
-      <c r="P20" s="98"/>
-      <c r="Q20" s="98"/>
-      <c r="R20" s="99"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="63"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="81"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="100"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="101"/>
-      <c r="G21" s="101"/>
-      <c r="H21" s="101"/>
-      <c r="I21" s="101"/>
-      <c r="J21" s="101"/>
-      <c r="K21" s="101"/>
-      <c r="L21" s="101"/>
-      <c r="M21" s="101"/>
-      <c r="N21" s="101"/>
-      <c r="O21" s="101"/>
-      <c r="P21" s="101"/>
-      <c r="Q21" s="101"/>
-      <c r="R21" s="102"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="65"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="66"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="81" t="s">
+      <c r="A22" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="22"/>
       <c r="L22" s="21"/>
-      <c r="M22" s="103" t="s">
+      <c r="M22" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="104"/>
-      <c r="O22" s="107"/>
-      <c r="P22" s="108"/>
-      <c r="Q22" s="108"/>
-      <c r="R22" s="109"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="81"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="119"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="119"/>
-      <c r="J23" s="119"/>
-      <c r="K23" s="119"/>
-      <c r="L23" s="120"/>
-      <c r="M23" s="103"/>
-      <c r="N23" s="104"/>
-      <c r="O23" s="110"/>
-      <c r="P23" s="111"/>
-      <c r="Q23" s="111"/>
-      <c r="R23" s="112"/>
+      <c r="A23" s="55"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="83"/>
+      <c r="J23" s="83"/>
+      <c r="K23" s="83"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="74"/>
+      <c r="P23" s="75"/>
+      <c r="Q23" s="75"/>
+      <c r="R23" s="76"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="81"/>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="121"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="119"/>
-      <c r="G24" s="119"/>
-      <c r="H24" s="119"/>
-      <c r="I24" s="119"/>
-      <c r="J24" s="119"/>
-      <c r="K24" s="119"/>
-      <c r="L24" s="120"/>
-      <c r="M24" s="103"/>
-      <c r="N24" s="104"/>
-      <c r="O24" s="110"/>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="111"/>
-      <c r="R24" s="112"/>
+      <c r="A24" s="55"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="85"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="83"/>
+      <c r="J24" s="83"/>
+      <c r="K24" s="83"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="74"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="76"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="81"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="119"/>
-      <c r="H25" s="119"/>
-      <c r="I25" s="119"/>
-      <c r="J25" s="119"/>
-      <c r="K25" s="119"/>
-      <c r="L25" s="120"/>
-      <c r="M25" s="103"/>
-      <c r="N25" s="104"/>
-      <c r="O25" s="110"/>
-      <c r="P25" s="111"/>
-      <c r="Q25" s="111"/>
-      <c r="R25" s="112"/>
+      <c r="A25" s="55"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="83"/>
+      <c r="J25" s="83"/>
+      <c r="K25" s="83"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="74"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="76"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="81"/>
-      <c r="B26" s="37"/>
-      <c r="C26" s="37"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="56"/>
       <c r="D26" s="20"/>
       <c r="E26" s="19"/>
       <c r="F26" s="18"/>
@@ -2291,17 +2294,17 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="16"/>
-      <c r="M26" s="103"/>
-      <c r="N26" s="104"/>
-      <c r="O26" s="110"/>
-      <c r="P26" s="111"/>
-      <c r="Q26" s="111"/>
-      <c r="R26" s="112"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="75"/>
+      <c r="R26" s="76"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="81"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
       <c r="D27" s="15"/>
       <c r="F27" s="13"/>
       <c r="G27" s="14"/>
@@ -2309,17 +2312,17 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="L27" s="11"/>
-      <c r="M27" s="103"/>
-      <c r="N27" s="104"/>
-      <c r="O27" s="110"/>
-      <c r="P27" s="111"/>
-      <c r="Q27" s="111"/>
-      <c r="R27" s="112"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="68"/>
+      <c r="O27" s="74"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="75"/>
+      <c r="R27" s="76"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="87"/>
-      <c r="B28" s="88"/>
-      <c r="C28" s="88"/>
+      <c r="A28" s="57"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="58"/>
       <c r="D28" s="10"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -2329,346 +2332,346 @@
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="8"/>
-      <c r="M28" s="105"/>
-      <c r="N28" s="106"/>
-      <c r="O28" s="113"/>
-      <c r="P28" s="114"/>
-      <c r="Q28" s="114"/>
-      <c r="R28" s="115"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="70"/>
+      <c r="O28" s="77"/>
+      <c r="P28" s="78"/>
+      <c r="Q28" s="78"/>
+      <c r="R28" s="79"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="80" t="s">
+      <c r="A31" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="36" t="s">
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="92"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="36"/>
-      <c r="L31" s="36"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="85"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="92"/>
+      <c r="O31" s="92"/>
+      <c r="P31" s="92"/>
+      <c r="Q31" s="92"/>
+      <c r="R31" s="93"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="81"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="37"/>
-      <c r="L32" s="37"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="86"/>
+      <c r="A32" s="55"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
+      <c r="F32" s="94"/>
+      <c r="G32" s="94"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="94"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="94"/>
+      <c r="N32" s="94"/>
+      <c r="O32" s="94"/>
+      <c r="P32" s="94"/>
+      <c r="Q32" s="94"/>
+      <c r="R32" s="95"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="81" t="s">
+      <c r="A33" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="37"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="37" t="s">
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="94"/>
+      <c r="F33" s="94"/>
+      <c r="G33" s="94"/>
+      <c r="H33" s="94"/>
+      <c r="I33" s="94"/>
+      <c r="J33" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="K33" s="37"/>
-      <c r="L33" s="37"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="86"/>
+      <c r="K33" s="56"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="94"/>
+      <c r="N33" s="94"/>
+      <c r="O33" s="94"/>
+      <c r="P33" s="94"/>
+      <c r="Q33" s="94"/>
+      <c r="R33" s="95"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="81"/>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="37"/>
-      <c r="L34" s="37"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="31"/>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="86"/>
+      <c r="A34" s="55"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="94"/>
+      <c r="G34" s="94"/>
+      <c r="H34" s="94"/>
+      <c r="I34" s="94"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="94"/>
+      <c r="N34" s="94"/>
+      <c r="O34" s="94"/>
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="95"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="81" t="s">
+      <c r="A35" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="37"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="90"/>
-      <c r="F35" s="90"/>
-      <c r="G35" s="90"/>
-      <c r="H35" s="90"/>
-      <c r="I35" s="90"/>
-      <c r="J35" s="90"/>
-      <c r="K35" s="90"/>
-      <c r="L35" s="90"/>
-      <c r="M35" s="90"/>
-      <c r="N35" s="90"/>
-      <c r="O35" s="90"/>
-      <c r="P35" s="90"/>
-      <c r="Q35" s="90"/>
-      <c r="R35" s="91"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="97"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="97"/>
+      <c r="I35" s="97"/>
+      <c r="J35" s="97"/>
+      <c r="K35" s="97"/>
+      <c r="L35" s="97"/>
+      <c r="M35" s="97"/>
+      <c r="N35" s="97"/>
+      <c r="O35" s="97"/>
+      <c r="P35" s="97"/>
+      <c r="Q35" s="97"/>
+      <c r="R35" s="98"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="87"/>
-      <c r="B36" s="88"/>
-      <c r="C36" s="88"/>
-      <c r="D36" s="92"/>
-      <c r="E36" s="93"/>
-      <c r="F36" s="93"/>
-      <c r="G36" s="93"/>
-      <c r="H36" s="93"/>
-      <c r="I36" s="93"/>
-      <c r="J36" s="93"/>
-      <c r="K36" s="93"/>
-      <c r="L36" s="93"/>
-      <c r="M36" s="93"/>
-      <c r="N36" s="93"/>
-      <c r="O36" s="93"/>
-      <c r="P36" s="93"/>
-      <c r="Q36" s="93"/>
-      <c r="R36" s="94"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="99"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="100"/>
+      <c r="G36" s="100"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="100"/>
+      <c r="J36" s="100"/>
+      <c r="K36" s="100"/>
+      <c r="L36" s="100"/>
+      <c r="M36" s="100"/>
+      <c r="N36" s="100"/>
+      <c r="O36" s="100"/>
+      <c r="P36" s="100"/>
+      <c r="Q36" s="100"/>
+      <c r="R36" s="101"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="82"/>
-      <c r="B37" s="83"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="83"/>
-      <c r="L37" s="83"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="83"/>
-      <c r="O37" s="83"/>
-      <c r="P37" s="83"/>
-      <c r="Q37" s="83"/>
-      <c r="R37" s="83"/>
+      <c r="A37" s="87"/>
+      <c r="B37" s="88"/>
+      <c r="C37" s="88"/>
+      <c r="D37" s="88"/>
+      <c r="E37" s="88"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="88"/>
+      <c r="I37" s="88"/>
+      <c r="J37" s="88"/>
+      <c r="K37" s="88"/>
+      <c r="L37" s="88"/>
+      <c r="M37" s="88"/>
+      <c r="N37" s="88"/>
+      <c r="O37" s="88"/>
+      <c r="P37" s="88"/>
+      <c r="Q37" s="88"/>
+      <c r="R37" s="88"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="84"/>
-      <c r="B38" s="84"/>
-      <c r="C38" s="84"/>
-      <c r="D38" s="84"/>
-      <c r="E38" s="84"/>
-      <c r="F38" s="84"/>
-      <c r="G38" s="84"/>
-      <c r="H38" s="84"/>
-      <c r="I38" s="84"/>
-      <c r="J38" s="84"/>
-      <c r="K38" s="84"/>
-      <c r="L38" s="84"/>
-      <c r="M38" s="84"/>
-      <c r="N38" s="84"/>
-      <c r="O38" s="84"/>
-      <c r="P38" s="84"/>
-      <c r="Q38" s="84"/>
-      <c r="R38" s="84"/>
+      <c r="A38" s="89"/>
+      <c r="B38" s="89"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="89"/>
+      <c r="H38" s="89"/>
+      <c r="I38" s="89"/>
+      <c r="J38" s="89"/>
+      <c r="K38" s="89"/>
+      <c r="L38" s="89"/>
+      <c r="M38" s="89"/>
+      <c r="N38" s="89"/>
+      <c r="O38" s="89"/>
+      <c r="P38" s="89"/>
+      <c r="Q38" s="89"/>
+      <c r="R38" s="89"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="80" t="s">
+      <c r="A39" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36" t="s">
+      <c r="B39" s="60"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="36" t="s">
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="90"/>
+      <c r="H39" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="I39" s="36"/>
-      <c r="J39" s="36"/>
-      <c r="K39" s="36" t="s">
+      <c r="I39" s="60"/>
+      <c r="J39" s="60"/>
+      <c r="K39" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="L39" s="36"/>
-      <c r="M39" s="36"/>
-      <c r="N39" s="38"/>
-      <c r="O39" s="36" t="s">
+      <c r="L39" s="60"/>
+      <c r="M39" s="60"/>
+      <c r="N39" s="90"/>
+      <c r="O39" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="P39" s="36"/>
-      <c r="Q39" s="36"/>
-      <c r="R39" s="78"/>
+      <c r="P39" s="60"/>
+      <c r="Q39" s="60"/>
+      <c r="R39" s="110"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="81"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
-      <c r="J40" s="37"/>
-      <c r="K40" s="37"/>
-      <c r="L40" s="37"/>
-      <c r="M40" s="37"/>
-      <c r="N40" s="39"/>
-      <c r="O40" s="37"/>
-      <c r="P40" s="37"/>
-      <c r="Q40" s="37"/>
-      <c r="R40" s="79"/>
+      <c r="A40" s="55"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="56"/>
+      <c r="N40" s="91"/>
+      <c r="O40" s="56"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="56"/>
+      <c r="R40" s="111"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="76" t="s">
+      <c r="A41" s="104" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="49"/>
-      <c r="C41" s="50"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="44"/>
-      <c r="H41" s="54" t="s">
+      <c r="B41" s="105"/>
+      <c r="C41" s="106"/>
+      <c r="D41" s="112"/>
+      <c r="E41" s="113"/>
+      <c r="F41" s="113"/>
+      <c r="G41" s="114"/>
+      <c r="H41" s="141" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="55"/>
-      <c r="J41" s="56"/>
-      <c r="K41" s="42"/>
-      <c r="L41" s="43"/>
-      <c r="M41" s="43"/>
-      <c r="N41" s="44"/>
-      <c r="O41" s="32"/>
-      <c r="P41" s="32"/>
-      <c r="Q41" s="32"/>
-      <c r="R41" s="33"/>
+      <c r="I41" s="142"/>
+      <c r="J41" s="143"/>
+      <c r="K41" s="112"/>
+      <c r="L41" s="113"/>
+      <c r="M41" s="113"/>
+      <c r="N41" s="114"/>
+      <c r="O41" s="133"/>
+      <c r="P41" s="133"/>
+      <c r="Q41" s="133"/>
+      <c r="R41" s="134"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="77"/>
-      <c r="B42" s="52"/>
-      <c r="C42" s="53"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="59"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="46"/>
-      <c r="M42" s="46"/>
-      <c r="N42" s="47"/>
-      <c r="O42" s="32"/>
-      <c r="P42" s="32"/>
-      <c r="Q42" s="32"/>
-      <c r="R42" s="33"/>
+      <c r="A42" s="107"/>
+      <c r="B42" s="108"/>
+      <c r="C42" s="109"/>
+      <c r="D42" s="115"/>
+      <c r="E42" s="116"/>
+      <c r="F42" s="116"/>
+      <c r="G42" s="117"/>
+      <c r="H42" s="144"/>
+      <c r="I42" s="145"/>
+      <c r="J42" s="146"/>
+      <c r="K42" s="115"/>
+      <c r="L42" s="116"/>
+      <c r="M42" s="116"/>
+      <c r="N42" s="117"/>
+      <c r="O42" s="133"/>
+      <c r="P42" s="133"/>
+      <c r="Q42" s="133"/>
+      <c r="R42" s="134"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="76" t="s">
+      <c r="A43" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="49"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="44"/>
-      <c r="H43" s="48" t="s">
+      <c r="B43" s="105"/>
+      <c r="C43" s="106"/>
+      <c r="D43" s="112"/>
+      <c r="E43" s="113"/>
+      <c r="F43" s="113"/>
+      <c r="G43" s="114"/>
+      <c r="H43" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="49"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="42"/>
-      <c r="L43" s="43"/>
-      <c r="M43" s="43"/>
-      <c r="N43" s="44"/>
-      <c r="O43" s="32"/>
-      <c r="P43" s="32"/>
-      <c r="Q43" s="32"/>
-      <c r="R43" s="33"/>
+      <c r="I43" s="105"/>
+      <c r="J43" s="106"/>
+      <c r="K43" s="112"/>
+      <c r="L43" s="113"/>
+      <c r="M43" s="113"/>
+      <c r="N43" s="114"/>
+      <c r="O43" s="133"/>
+      <c r="P43" s="133"/>
+      <c r="Q43" s="133"/>
+      <c r="R43" s="134"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="77"/>
-      <c r="B44" s="52"/>
-      <c r="C44" s="53"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="51"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="53"/>
-      <c r="K44" s="45"/>
-      <c r="L44" s="46"/>
-      <c r="M44" s="46"/>
-      <c r="N44" s="47"/>
-      <c r="O44" s="32"/>
-      <c r="P44" s="32"/>
-      <c r="Q44" s="32"/>
-      <c r="R44" s="33"/>
+      <c r="A44" s="107"/>
+      <c r="B44" s="108"/>
+      <c r="C44" s="109"/>
+      <c r="D44" s="115"/>
+      <c r="E44" s="116"/>
+      <c r="F44" s="116"/>
+      <c r="G44" s="117"/>
+      <c r="H44" s="140"/>
+      <c r="I44" s="108"/>
+      <c r="J44" s="109"/>
+      <c r="K44" s="115"/>
+      <c r="L44" s="116"/>
+      <c r="M44" s="116"/>
+      <c r="N44" s="117"/>
+      <c r="O44" s="133"/>
+      <c r="P44" s="133"/>
+      <c r="Q44" s="133"/>
+      <c r="R44" s="134"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="74" t="s">
+      <c r="A45" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="75"/>
-      <c r="C45" s="75"/>
-      <c r="D45" s="40"/>
-      <c r="E45" s="40"/>
-      <c r="F45" s="40"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="75" t="s">
+      <c r="B45" s="103"/>
+      <c r="C45" s="103"/>
+      <c r="D45" s="137"/>
+      <c r="E45" s="137"/>
+      <c r="F45" s="137"/>
+      <c r="G45" s="138"/>
+      <c r="H45" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="75"/>
-      <c r="J45" s="75"/>
-      <c r="K45" s="40"/>
-      <c r="L45" s="40"/>
-      <c r="M45" s="40"/>
-      <c r="N45" s="41"/>
-      <c r="O45" s="34"/>
-      <c r="P45" s="34"/>
-      <c r="Q45" s="34"/>
-      <c r="R45" s="35"/>
+      <c r="I45" s="103"/>
+      <c r="J45" s="103"/>
+      <c r="K45" s="137"/>
+      <c r="L45" s="137"/>
+      <c r="M45" s="137"/>
+      <c r="N45" s="138"/>
+      <c r="O45" s="135"/>
+      <c r="P45" s="135"/>
+      <c r="Q45" s="135"/>
+      <c r="R45" s="136"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2680,233 +2683,233 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="139"/>
-      <c r="B49" s="140"/>
-      <c r="C49" s="141"/>
-      <c r="D49" s="64"/>
-      <c r="E49" s="65"/>
-      <c r="F49" s="65"/>
-      <c r="G49" s="65"/>
-      <c r="H49" s="123"/>
-      <c r="I49" s="64"/>
-      <c r="J49" s="65"/>
-      <c r="K49" s="65"/>
-      <c r="L49" s="65"/>
-      <c r="M49" s="123"/>
-      <c r="N49" s="64"/>
-      <c r="O49" s="65"/>
-      <c r="P49" s="65"/>
-      <c r="Q49" s="65"/>
-      <c r="R49" s="66"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="122"/>
+      <c r="E49" s="123"/>
+      <c r="F49" s="123"/>
+      <c r="G49" s="123"/>
+      <c r="H49" s="131"/>
+      <c r="I49" s="122"/>
+      <c r="J49" s="123"/>
+      <c r="K49" s="123"/>
+      <c r="L49" s="123"/>
+      <c r="M49" s="131"/>
+      <c r="N49" s="122"/>
+      <c r="O49" s="123"/>
+      <c r="P49" s="123"/>
+      <c r="Q49" s="123"/>
+      <c r="R49" s="124"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="142"/>
-      <c r="B50" s="143"/>
-      <c r="C50" s="144"/>
-      <c r="D50" s="67"/>
-      <c r="E50" s="68"/>
-      <c r="F50" s="68"/>
-      <c r="G50" s="68"/>
-      <c r="H50" s="124"/>
-      <c r="I50" s="67"/>
-      <c r="J50" s="68"/>
-      <c r="K50" s="68"/>
-      <c r="L50" s="68"/>
-      <c r="M50" s="124"/>
-      <c r="N50" s="67"/>
-      <c r="O50" s="68"/>
-      <c r="P50" s="68"/>
-      <c r="Q50" s="68"/>
-      <c r="R50" s="69"/>
+      <c r="A50" s="33"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="125"/>
+      <c r="E50" s="126"/>
+      <c r="F50" s="126"/>
+      <c r="G50" s="126"/>
+      <c r="H50" s="132"/>
+      <c r="I50" s="125"/>
+      <c r="J50" s="126"/>
+      <c r="K50" s="126"/>
+      <c r="L50" s="126"/>
+      <c r="M50" s="132"/>
+      <c r="N50" s="125"/>
+      <c r="O50" s="126"/>
+      <c r="P50" s="126"/>
+      <c r="Q50" s="126"/>
+      <c r="R50" s="127"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="133" t="s">
+      <c r="A51" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="134"/>
-      <c r="C51" s="135"/>
-      <c r="D51" s="70"/>
-      <c r="E51" s="70"/>
-      <c r="F51" s="70"/>
-      <c r="G51" s="70"/>
-      <c r="H51" s="70"/>
-      <c r="I51" s="70"/>
-      <c r="J51" s="70"/>
-      <c r="K51" s="70"/>
-      <c r="L51" s="70"/>
-      <c r="M51" s="70"/>
-      <c r="N51" s="70"/>
-      <c r="O51" s="70"/>
-      <c r="P51" s="70"/>
-      <c r="Q51" s="70"/>
-      <c r="R51" s="71"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="52"/>
+      <c r="J51" s="52"/>
+      <c r="K51" s="52"/>
+      <c r="L51" s="52"/>
+      <c r="M51" s="52"/>
+      <c r="N51" s="52"/>
+      <c r="O51" s="52"/>
+      <c r="P51" s="52"/>
+      <c r="Q51" s="52"/>
+      <c r="R51" s="128"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="136"/>
-      <c r="B52" s="137"/>
-      <c r="C52" s="138"/>
-      <c r="D52" s="70"/>
-      <c r="E52" s="70"/>
-      <c r="F52" s="70"/>
-      <c r="G52" s="70"/>
-      <c r="H52" s="70"/>
-      <c r="I52" s="70"/>
-      <c r="J52" s="70"/>
-      <c r="K52" s="70"/>
-      <c r="L52" s="70"/>
-      <c r="M52" s="70"/>
-      <c r="N52" s="70"/>
-      <c r="O52" s="70"/>
-      <c r="P52" s="70"/>
-      <c r="Q52" s="70"/>
-      <c r="R52" s="71"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="50"/>
+      <c r="C52" s="51"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
+      <c r="G52" s="52"/>
+      <c r="H52" s="52"/>
+      <c r="I52" s="52"/>
+      <c r="J52" s="52"/>
+      <c r="K52" s="52"/>
+      <c r="L52" s="52"/>
+      <c r="M52" s="52"/>
+      <c r="N52" s="52"/>
+      <c r="O52" s="52"/>
+      <c r="P52" s="52"/>
+      <c r="Q52" s="52"/>
+      <c r="R52" s="128"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
       <c r="B53" s="4"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="61"/>
-      <c r="E53" s="62"/>
-      <c r="F53" s="62"/>
-      <c r="G53" s="62"/>
-      <c r="H53" s="72"/>
-      <c r="I53" s="61"/>
-      <c r="J53" s="62"/>
-      <c r="K53" s="62"/>
-      <c r="L53" s="62"/>
-      <c r="M53" s="72"/>
-      <c r="N53" s="61"/>
-      <c r="O53" s="62"/>
-      <c r="P53" s="62"/>
-      <c r="Q53" s="62"/>
-      <c r="R53" s="63"/>
+      <c r="D53" s="119"/>
+      <c r="E53" s="120"/>
+      <c r="F53" s="120"/>
+      <c r="G53" s="120"/>
+      <c r="H53" s="129"/>
+      <c r="I53" s="119"/>
+      <c r="J53" s="120"/>
+      <c r="K53" s="120"/>
+      <c r="L53" s="120"/>
+      <c r="M53" s="129"/>
+      <c r="N53" s="119"/>
+      <c r="O53" s="120"/>
+      <c r="P53" s="120"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="121"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="125" t="s">
+      <c r="A54" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="126"/>
-      <c r="C54" s="127"/>
-      <c r="D54" s="131"/>
-      <c r="E54" s="131"/>
-      <c r="F54" s="131"/>
-      <c r="G54" s="131"/>
-      <c r="H54" s="131"/>
-      <c r="I54" s="131"/>
-      <c r="J54" s="131"/>
-      <c r="K54" s="131"/>
-      <c r="L54" s="131"/>
-      <c r="M54" s="131"/>
-      <c r="N54" s="131"/>
-      <c r="O54" s="131"/>
-      <c r="P54" s="131"/>
-      <c r="Q54" s="131"/>
-      <c r="R54" s="145"/>
+      <c r="B54" s="41"/>
+      <c r="C54" s="42"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="36"/>
+      <c r="I54" s="36"/>
+      <c r="J54" s="36"/>
+      <c r="K54" s="36"/>
+      <c r="L54" s="36"/>
+      <c r="M54" s="36"/>
+      <c r="N54" s="36"/>
+      <c r="O54" s="36"/>
+      <c r="P54" s="36"/>
+      <c r="Q54" s="36"/>
+      <c r="R54" s="37"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="128"/>
-      <c r="B55" s="129"/>
-      <c r="C55" s="130"/>
-      <c r="D55" s="132"/>
-      <c r="E55" s="132"/>
-      <c r="F55" s="132"/>
-      <c r="G55" s="132"/>
-      <c r="H55" s="132"/>
-      <c r="I55" s="132"/>
-      <c r="J55" s="132"/>
-      <c r="K55" s="132"/>
-      <c r="L55" s="132"/>
-      <c r="M55" s="132"/>
-      <c r="N55" s="132"/>
-      <c r="O55" s="132"/>
-      <c r="P55" s="132"/>
-      <c r="Q55" s="132"/>
-      <c r="R55" s="146"/>
+      <c r="A55" s="43"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="38"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="38"/>
+      <c r="G55" s="38"/>
+      <c r="H55" s="38"/>
+      <c r="I55" s="38"/>
+      <c r="J55" s="38"/>
+      <c r="K55" s="38"/>
+      <c r="L55" s="38"/>
+      <c r="M55" s="38"/>
+      <c r="N55" s="38"/>
+      <c r="O55" s="38"/>
+      <c r="P55" s="38"/>
+      <c r="Q55" s="38"/>
+      <c r="R55" s="39"/>
     </row>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="125" t="s">
+      <c r="A56" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="B56" s="126"/>
-      <c r="C56" s="127"/>
-      <c r="D56" s="131"/>
-      <c r="E56" s="131"/>
-      <c r="F56" s="131"/>
-      <c r="G56" s="131"/>
-      <c r="H56" s="131"/>
-      <c r="I56" s="131"/>
-      <c r="J56" s="131"/>
-      <c r="K56" s="131"/>
-      <c r="L56" s="131"/>
-      <c r="M56" s="131"/>
-      <c r="N56" s="131"/>
-      <c r="O56" s="131"/>
-      <c r="P56" s="131"/>
-      <c r="Q56" s="131"/>
-      <c r="R56" s="145"/>
+      <c r="B56" s="41"/>
+      <c r="C56" s="42"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="36"/>
+      <c r="J56" s="36"/>
+      <c r="K56" s="36"/>
+      <c r="L56" s="36"/>
+      <c r="M56" s="36"/>
+      <c r="N56" s="36"/>
+      <c r="O56" s="36"/>
+      <c r="P56" s="36"/>
+      <c r="Q56" s="36"/>
+      <c r="R56" s="37"/>
     </row>
     <row r="57" spans="1:18" s="2" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="128"/>
-      <c r="B57" s="129"/>
-      <c r="C57" s="130"/>
-      <c r="D57" s="132"/>
-      <c r="E57" s="132"/>
-      <c r="F57" s="132"/>
-      <c r="G57" s="132"/>
-      <c r="H57" s="132"/>
-      <c r="I57" s="132"/>
-      <c r="J57" s="132"/>
-      <c r="K57" s="132"/>
-      <c r="L57" s="132"/>
-      <c r="M57" s="132"/>
-      <c r="N57" s="132"/>
-      <c r="O57" s="132"/>
-      <c r="P57" s="132"/>
-      <c r="Q57" s="132"/>
-      <c r="R57" s="146"/>
+      <c r="A57" s="43"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="38"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="38"/>
+      <c r="I57" s="38"/>
+      <c r="J57" s="38"/>
+      <c r="K57" s="38"/>
+      <c r="L57" s="38"/>
+      <c r="M57" s="38"/>
+      <c r="N57" s="38"/>
+      <c r="O57" s="38"/>
+      <c r="P57" s="38"/>
+      <c r="Q57" s="38"/>
+      <c r="R57" s="39"/>
     </row>
     <row r="58" spans="1:18" s="2" customFormat="1" ht="27" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D58" s="73"/>
-      <c r="E58" s="73"/>
-      <c r="F58" s="73"/>
-      <c r="G58" s="73"/>
-      <c r="H58" s="73"/>
-      <c r="I58" s="73"/>
-      <c r="J58" s="73"/>
-      <c r="K58" s="73"/>
-      <c r="L58" s="73"/>
-      <c r="M58" s="73"/>
-      <c r="N58" s="73"/>
-      <c r="O58" s="73"/>
-      <c r="P58" s="73"/>
-      <c r="Q58" s="73"/>
-      <c r="R58" s="73"/>
+      <c r="D58" s="130"/>
+      <c r="E58" s="130"/>
+      <c r="F58" s="130"/>
+      <c r="G58" s="130"/>
+      <c r="H58" s="130"/>
+      <c r="I58" s="130"/>
+      <c r="J58" s="130"/>
+      <c r="K58" s="130"/>
+      <c r="L58" s="130"/>
+      <c r="M58" s="130"/>
+      <c r="N58" s="130"/>
+      <c r="O58" s="130"/>
+      <c r="P58" s="130"/>
+      <c r="Q58" s="130"/>
+      <c r="R58" s="130"/>
     </row>
     <row r="59" spans="1:18" s="2" customFormat="1" ht="30.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D59" s="60" t="str">
+      <c r="D59" s="118" t="str">
         <f>IF(MOD(D58,1000)=0,"千円単位",IF(MOD(D58,100)=0,"百円単位",IF(MOD(D58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="E59" s="60"/>
-      <c r="F59" s="60"/>
-      <c r="G59" s="60"/>
-      <c r="H59" s="60"/>
-      <c r="I59" s="60" t="str">
+      <c r="E59" s="118"/>
+      <c r="F59" s="118"/>
+      <c r="G59" s="118"/>
+      <c r="H59" s="118"/>
+      <c r="I59" s="118" t="str">
         <f>IF(MOD(I58,1000)=0,"千円単位",IF(MOD(I58,100)=0,"百円単位",IF(MOD(I58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="J59" s="60"/>
-      <c r="K59" s="60"/>
-      <c r="L59" s="60"/>
-      <c r="M59" s="60"/>
-      <c r="N59" s="60" t="str">
+      <c r="J59" s="118"/>
+      <c r="K59" s="118"/>
+      <c r="L59" s="118"/>
+      <c r="M59" s="118"/>
+      <c r="N59" s="118" t="str">
         <f>IF(MOD(N58,1000)=0,"千円単位",IF(MOD(N58,100)=0,"百円単位",IF(MOD(N58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="O59" s="60"/>
-      <c r="P59" s="60"/>
-      <c r="Q59" s="60"/>
-      <c r="R59" s="60"/>
+      <c r="O59" s="118"/>
+      <c r="P59" s="118"/>
+      <c r="Q59" s="118"/>
+      <c r="R59" s="118"/>
     </row>
     <row r="60" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="61" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2918,47 +2921,7 @@
     <row r="67" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="N56:R57"/>
-    <mergeCell ref="D54:H55"/>
-    <mergeCell ref="I54:M55"/>
-    <mergeCell ref="N54:R55"/>
-    <mergeCell ref="A54:C55"/>
-    <mergeCell ref="A56:C57"/>
-    <mergeCell ref="D56:H57"/>
-    <mergeCell ref="I56:M57"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="I51:M52"/>
-    <mergeCell ref="D51:H52"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A22:C28"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:R21"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="O22:R28"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="J33:L34"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="M33:R34"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="A43:C44"/>
-    <mergeCell ref="D33:I34"/>
-    <mergeCell ref="O39:R40"/>
-    <mergeCell ref="K43:N44"/>
-    <mergeCell ref="A41:C42"/>
+    <mergeCell ref="H41:J42"/>
     <mergeCell ref="D59:H59"/>
     <mergeCell ref="I59:M59"/>
     <mergeCell ref="N59:R59"/>
@@ -2972,7 +2935,13 @@
     <mergeCell ref="D49:H50"/>
     <mergeCell ref="I53:M53"/>
     <mergeCell ref="I49:M50"/>
-    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="A43:C44"/>
+    <mergeCell ref="D33:I34"/>
+    <mergeCell ref="O39:R40"/>
+    <mergeCell ref="K43:N44"/>
+    <mergeCell ref="A41:C42"/>
     <mergeCell ref="O41:R45"/>
     <mergeCell ref="H39:J40"/>
     <mergeCell ref="D39:G40"/>
@@ -2982,7 +2951,41 @@
     <mergeCell ref="D43:G44"/>
     <mergeCell ref="H43:J44"/>
     <mergeCell ref="D41:G42"/>
-    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="J33:L34"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="M33:R34"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A22:C28"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:R21"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="O22:R28"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="N56:R57"/>
+    <mergeCell ref="D54:H55"/>
+    <mergeCell ref="I54:M55"/>
+    <mergeCell ref="N54:R55"/>
+    <mergeCell ref="A54:C55"/>
+    <mergeCell ref="A56:C57"/>
+    <mergeCell ref="D56:H57"/>
+    <mergeCell ref="I56:M57"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="I51:M52"/>
+    <mergeCell ref="D51:H52"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="D51:R52">
@@ -3036,62 +3039,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="149" t="s">
+      <c r="E2" s="157" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149" t="s">
+      <c r="F2" s="157"/>
+      <c r="G2" s="157" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149" t="s">
+      <c r="H2" s="157"/>
+      <c r="I2" s="157" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149" t="s">
+      <c r="J2" s="157"/>
+      <c r="K2" s="157" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="149"/>
-      <c r="M2" s="149" t="s">
+      <c r="L2" s="157"/>
+      <c r="M2" s="157" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="149"/>
+      <c r="N2" s="157"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="147" t="s">
+      <c r="B3" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="147"/>
+      <c r="C3" s="154"/>
       <c r="D3" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="148"/>
-      <c r="H3" s="148"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
-      <c r="K3" s="147"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="147"/>
-      <c r="N3" s="147"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="154"/>
+      <c r="M3" s="154"/>
+      <c r="N3" s="154"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
+      <c r="B4" s="154"/>
+      <c r="C4" s="154"/>
       <c r="D4" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="147"/>
-      <c r="K4" s="147"/>
-      <c r="L4" s="147"/>
-      <c r="M4" s="147"/>
-      <c r="N4" s="147"/>
+      <c r="E4" s="154"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="154"/>
+      <c r="I4" s="154"/>
+      <c r="J4" s="154"/>
+      <c r="K4" s="154"/>
+      <c r="L4" s="154"/>
+      <c r="M4" s="154"/>
+      <c r="N4" s="154"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -3112,39 +3115,39 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="154" t="s">
+      <c r="E6" s="152" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="155"/>
-      <c r="G6" s="154" t="s">
+      <c r="F6" s="153"/>
+      <c r="G6" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="155"/>
-      <c r="I6" s="154" t="s">
+      <c r="H6" s="153"/>
+      <c r="I6" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="155"/>
-      <c r="K6" s="154" t="s">
+      <c r="J6" s="153"/>
+      <c r="K6" s="152" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="155"/>
-      <c r="M6" s="154" t="s">
+      <c r="L6" s="153"/>
+      <c r="M6" s="152" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="155"/>
+      <c r="N6" s="153"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="147" t="s">
+      <c r="B7" s="154" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="147"/>
+      <c r="C7" s="154"/>
       <c r="D7" s="29" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="150"/>
       <c r="F7" s="151"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="153"/>
+      <c r="G7" s="155"/>
+      <c r="H7" s="156"/>
       <c r="I7" s="150"/>
       <c r="J7" s="151"/>
       <c r="K7" s="150"/>
@@ -3153,8 +3156,8 @@
       <c r="N7" s="151"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="147"/>
-      <c r="C8" s="147"/>
+      <c r="B8" s="154"/>
+      <c r="C8" s="154"/>
       <c r="D8" s="29" t="s">
         <v>30</v>
       </c>
@@ -3188,39 +3191,39 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="154" t="s">
+      <c r="E10" s="152" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="155"/>
-      <c r="G10" s="154" t="s">
+      <c r="F10" s="153"/>
+      <c r="G10" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="155"/>
-      <c r="I10" s="154" t="s">
+      <c r="H10" s="153"/>
+      <c r="I10" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="155"/>
-      <c r="K10" s="154" t="s">
+      <c r="J10" s="153"/>
+      <c r="K10" s="152" t="s">
         <v>26</v>
       </c>
-      <c r="L10" s="155"/>
-      <c r="M10" s="154" t="s">
+      <c r="L10" s="153"/>
+      <c r="M10" s="152" t="s">
         <v>27</v>
       </c>
-      <c r="N10" s="155"/>
+      <c r="N10" s="153"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="147" t="s">
+      <c r="B11" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="147"/>
+      <c r="C11" s="154"/>
       <c r="D11" s="29" t="s">
         <v>29</v>
       </c>
       <c r="E11" s="150"/>
       <c r="F11" s="151"/>
-      <c r="G11" s="152"/>
-      <c r="H11" s="153"/>
+      <c r="G11" s="155"/>
+      <c r="H11" s="156"/>
       <c r="I11" s="150"/>
       <c r="J11" s="151"/>
       <c r="K11" s="150"/>
@@ -3229,8 +3232,8 @@
       <c r="N11" s="151"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="147"/>
-      <c r="C12" s="147"/>
+      <c r="B12" s="154"/>
+      <c r="C12" s="154"/>
       <c r="D12" s="29" t="s">
         <v>30</v>
       </c>
@@ -3279,39 +3282,39 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="154" t="s">
+      <c r="E15" s="152" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="155"/>
-      <c r="G15" s="154" t="s">
+      <c r="F15" s="153"/>
+      <c r="G15" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="155"/>
-      <c r="I15" s="154" t="s">
+      <c r="H15" s="153"/>
+      <c r="I15" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="J15" s="155"/>
-      <c r="K15" s="154" t="s">
+      <c r="J15" s="153"/>
+      <c r="K15" s="152" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="155"/>
-      <c r="M15" s="154" t="s">
+      <c r="L15" s="153"/>
+      <c r="M15" s="152" t="s">
         <v>27</v>
       </c>
-      <c r="N15" s="155"/>
+      <c r="N15" s="153"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="147" t="s">
+      <c r="B16" s="154" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="147"/>
+      <c r="C16" s="154"/>
       <c r="D16" s="29" t="s">
         <v>29</v>
       </c>
       <c r="E16" s="150"/>
       <c r="F16" s="151"/>
-      <c r="G16" s="152"/>
-      <c r="H16" s="153"/>
+      <c r="G16" s="155"/>
+      <c r="H16" s="156"/>
       <c r="I16" s="150"/>
       <c r="J16" s="151"/>
       <c r="K16" s="150"/>
@@ -3320,8 +3323,8 @@
       <c r="N16" s="151"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="147"/>
-      <c r="C17" s="147"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="154"/>
       <c r="D17" s="29" t="s">
         <v>30</v>
       </c>
@@ -3337,97 +3340,173 @@
       <c r="N17" s="151"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B20" s="156"/>
-      <c r="C20" s="156"/>
-      <c r="D20" s="156"/>
-      <c r="E20" s="156" t="s">
+      <c r="B20" s="147"/>
+      <c r="C20" s="147"/>
+      <c r="D20" s="147"/>
+      <c r="E20" s="147" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="156"/>
+      <c r="F20" s="147"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B21" s="156" t="s">
+      <c r="B21" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="156"/>
-      <c r="D21" s="156"/>
-      <c r="E21" s="157"/>
-      <c r="F21" s="157"/>
+      <c r="C21" s="147"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="148"/>
+      <c r="F21" s="148"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B22" s="156" t="s">
+      <c r="B22" s="147" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="156"/>
-      <c r="D22" s="156"/>
-      <c r="E22" s="157"/>
-      <c r="F22" s="157"/>
+      <c r="C22" s="147"/>
+      <c r="D22" s="147"/>
+      <c r="E22" s="148"/>
+      <c r="F22" s="148"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B23" s="156" t="s">
+      <c r="B23" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="156"/>
-      <c r="D23" s="156"/>
-      <c r="E23" s="157"/>
-      <c r="F23" s="157"/>
+      <c r="C23" s="147"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="148"/>
+      <c r="F23" s="148"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B24" s="156" t="s">
+      <c r="B24" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="156"/>
-      <c r="D24" s="156"/>
-      <c r="E24" s="157"/>
-      <c r="F24" s="157"/>
+      <c r="C24" s="147"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="148"/>
+      <c r="F24" s="148"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B25" s="156" t="s">
+      <c r="B25" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="156"/>
-      <c r="D25" s="156"/>
-      <c r="E25" s="157"/>
-      <c r="F25" s="157"/>
+      <c r="C25" s="147"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="148"/>
+      <c r="F25" s="148"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B26" s="156" t="s">
+      <c r="B26" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="156"/>
-      <c r="D26" s="156"/>
-      <c r="E26" s="158"/>
-      <c r="F26" s="158"/>
+      <c r="C26" s="147"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="159"/>
+      <c r="F26" s="159"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B27" s="156" t="s">
+      <c r="B27" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="156"/>
-      <c r="D27" s="156"/>
-      <c r="E27" s="158"/>
-      <c r="F27" s="158"/>
+      <c r="C27" s="147"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="149"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B28" s="156" t="s">
+      <c r="B28" s="147" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="156"/>
-      <c r="D28" s="156"/>
-      <c r="E28" s="157"/>
-      <c r="F28" s="157"/>
+      <c r="C28" s="147"/>
+      <c r="D28" s="147"/>
+      <c r="E28" s="148"/>
+      <c r="F28" s="148"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B29" s="156" t="s">
+      <c r="B29" s="147" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="156"/>
-      <c r="D29" s="156"/>
-      <c r="E29" s="157"/>
-      <c r="F29" s="157"/>
+      <c r="C29" s="147"/>
+      <c r="D29" s="147"/>
+      <c r="E29" s="148"/>
+      <c r="F29" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="84">
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="B26:D26"/>
@@ -3436,82 +3515,6 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\火災見積\テンプレート\new\mark\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\a\estimateTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3BD8DD-30AA-4747-A4C4-359B89C95C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE07382B-29FB-429C-A129-4B904E201F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="30" yWindow="90" windowWidth="28770" windowHeight="15435" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="地震おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -1134,7 +1134,7 @@
     <xf numFmtId="6" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1222,74 +1222,196 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1298,24 +1420,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1394,220 +1498,113 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2010,10 +2007,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="95"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="95"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="28"/>
@@ -2023,16 +2020,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
+      <c r="O3" s="122"/>
+      <c r="P3" s="122"/>
+      <c r="Q3" s="122"/>
+      <c r="R3" s="122"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="86"/>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="86"/>
-      <c r="R4" s="86"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="27"/>
@@ -2095,196 +2092,196 @@
       <c r="R10" s="23"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
+      <c r="B11" s="96"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="96"/>
+      <c r="M11" s="96"/>
+      <c r="N11" s="96"/>
+      <c r="O11" s="96"/>
+      <c r="P11" s="96"/>
+      <c r="Q11" s="96"/>
+      <c r="R11" s="96"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="80" t="s">
+      <c r="A15" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="80"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="80"/>
-      <c r="M15" s="80"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="80"/>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="80"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="116"/>
+      <c r="I15" s="116"/>
+      <c r="J15" s="116"/>
+      <c r="K15" s="116"/>
+      <c r="L15" s="116"/>
+      <c r="M15" s="116"/>
+      <c r="N15" s="116"/>
+      <c r="O15" s="116"/>
+      <c r="P15" s="116"/>
+      <c r="Q15" s="116"/>
+      <c r="R15" s="116"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="81" t="s">
+      <c r="A18" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
-      <c r="M18" s="81"/>
-      <c r="N18" s="81"/>
-      <c r="O18" s="81"/>
-      <c r="P18" s="81"/>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="81"/>
+      <c r="B18" s="117"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="117"/>
+      <c r="P18" s="117"/>
+      <c r="Q18" s="117"/>
+      <c r="R18" s="117"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="62"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="62"/>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="62"/>
-      <c r="R20" s="63"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="98"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="98"/>
+      <c r="K20" s="98"/>
+      <c r="L20" s="98"/>
+      <c r="M20" s="98"/>
+      <c r="N20" s="98"/>
+      <c r="O20" s="98"/>
+      <c r="P20" s="98"/>
+      <c r="Q20" s="98"/>
+      <c r="R20" s="99"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="55"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="65"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="65"/>
-      <c r="M21" s="65"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="65"/>
-      <c r="P21" s="65"/>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="66"/>
+      <c r="A21" s="80"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="101"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="101"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="101"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="101"/>
+      <c r="N21" s="101"/>
+      <c r="O21" s="101"/>
+      <c r="P21" s="101"/>
+      <c r="Q21" s="101"/>
+      <c r="R21" s="102"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="56"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
       <c r="D22" s="22"/>
       <c r="L22" s="21"/>
-      <c r="M22" s="67" t="s">
+      <c r="M22" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="68"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="72"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="73"/>
+      <c r="N22" s="104"/>
+      <c r="O22" s="107"/>
+      <c r="P22" s="108"/>
+      <c r="Q22" s="108"/>
+      <c r="R22" s="109"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="55"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="74"/>
-      <c r="P23" s="75"/>
-      <c r="Q23" s="75"/>
-      <c r="R23" s="76"/>
+      <c r="A23" s="80"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="119"/>
+      <c r="L23" s="120"/>
+      <c r="M23" s="103"/>
+      <c r="N23" s="104"/>
+      <c r="O23" s="110"/>
+      <c r="P23" s="111"/>
+      <c r="Q23" s="111"/>
+      <c r="R23" s="112"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="55"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="85"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="67"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="74"/>
-      <c r="P24" s="75"/>
-      <c r="Q24" s="75"/>
-      <c r="R24" s="76"/>
+      <c r="A24" s="80"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="121"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="119"/>
+      <c r="K24" s="119"/>
+      <c r="L24" s="120"/>
+      <c r="M24" s="103"/>
+      <c r="N24" s="104"/>
+      <c r="O24" s="110"/>
+      <c r="P24" s="111"/>
+      <c r="Q24" s="111"/>
+      <c r="R24" s="112"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="55"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="85"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="83"/>
-      <c r="L25" s="84"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="74"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="76"/>
+      <c r="A25" s="80"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="63"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="119"/>
+      <c r="L25" s="120"/>
+      <c r="M25" s="103"/>
+      <c r="N25" s="104"/>
+      <c r="O25" s="110"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="111"/>
+      <c r="R25" s="112"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="55"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
+      <c r="A26" s="80"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="63"/>
       <c r="D26" s="20"/>
       <c r="E26" s="19"/>
       <c r="F26" s="18"/>
@@ -2294,17 +2291,17 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="16"/>
-      <c r="M26" s="67"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="75"/>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="76"/>
+      <c r="M26" s="103"/>
+      <c r="N26" s="104"/>
+      <c r="O26" s="110"/>
+      <c r="P26" s="111"/>
+      <c r="Q26" s="111"/>
+      <c r="R26" s="112"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="55"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="56"/>
+      <c r="A27" s="80"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="63"/>
       <c r="D27" s="15"/>
       <c r="F27" s="13"/>
       <c r="G27" s="14"/>
@@ -2312,17 +2309,17 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="L27" s="11"/>
-      <c r="M27" s="67"/>
-      <c r="N27" s="68"/>
-      <c r="O27" s="74"/>
-      <c r="P27" s="75"/>
-      <c r="Q27" s="75"/>
-      <c r="R27" s="76"/>
+      <c r="M27" s="103"/>
+      <c r="N27" s="104"/>
+      <c r="O27" s="110"/>
+      <c r="P27" s="111"/>
+      <c r="Q27" s="111"/>
+      <c r="R27" s="112"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="57"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
+      <c r="A28" s="87"/>
+      <c r="B28" s="88"/>
+      <c r="C28" s="88"/>
       <c r="D28" s="10"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -2332,346 +2329,346 @@
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="8"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="70"/>
-      <c r="O28" s="77"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="78"/>
-      <c r="R28" s="79"/>
+      <c r="M28" s="105"/>
+      <c r="N28" s="106"/>
+      <c r="O28" s="113"/>
+      <c r="P28" s="114"/>
+      <c r="Q28" s="114"/>
+      <c r="R28" s="115"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="59" t="s">
+      <c r="A31" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="60"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="92"/>
-      <c r="H31" s="92"/>
-      <c r="I31" s="92"/>
-      <c r="J31" s="60" t="s">
+      <c r="B31" s="61"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="60"/>
-      <c r="L31" s="60"/>
-      <c r="M31" s="92"/>
-      <c r="N31" s="92"/>
-      <c r="O31" s="92"/>
-      <c r="P31" s="92"/>
-      <c r="Q31" s="92"/>
-      <c r="R31" s="93"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="84"/>
+      <c r="O31" s="84"/>
+      <c r="P31" s="84"/>
+      <c r="Q31" s="84"/>
+      <c r="R31" s="85"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="55"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="94"/>
-      <c r="E32" s="94"/>
-      <c r="F32" s="94"/>
-      <c r="G32" s="94"/>
-      <c r="H32" s="94"/>
-      <c r="I32" s="94"/>
-      <c r="J32" s="56"/>
-      <c r="K32" s="56"/>
-      <c r="L32" s="56"/>
-      <c r="M32" s="94"/>
-      <c r="N32" s="94"/>
-      <c r="O32" s="94"/>
-      <c r="P32" s="94"/>
-      <c r="Q32" s="94"/>
-      <c r="R32" s="95"/>
+      <c r="A32" s="80"/>
+      <c r="B32" s="63"/>
+      <c r="C32" s="63"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="63"/>
+      <c r="K32" s="63"/>
+      <c r="L32" s="63"/>
+      <c r="M32" s="60"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="60"/>
+      <c r="R32" s="86"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="94"/>
-      <c r="E33" s="94"/>
-      <c r="F33" s="94"/>
-      <c r="G33" s="94"/>
-      <c r="H33" s="94"/>
-      <c r="I33" s="94"/>
-      <c r="J33" s="56" t="s">
+      <c r="B33" s="63"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="60"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="60"/>
+      <c r="H33" s="60"/>
+      <c r="I33" s="60"/>
+      <c r="J33" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="K33" s="56"/>
-      <c r="L33" s="56"/>
-      <c r="M33" s="94"/>
-      <c r="N33" s="94"/>
-      <c r="O33" s="94"/>
-      <c r="P33" s="94"/>
-      <c r="Q33" s="94"/>
-      <c r="R33" s="95"/>
+      <c r="K33" s="63"/>
+      <c r="L33" s="63"/>
+      <c r="M33" s="60"/>
+      <c r="N33" s="60"/>
+      <c r="O33" s="60"/>
+      <c r="P33" s="60"/>
+      <c r="Q33" s="60"/>
+      <c r="R33" s="86"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="55"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="94"/>
-      <c r="E34" s="94"/>
-      <c r="F34" s="94"/>
-      <c r="G34" s="94"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="94"/>
-      <c r="J34" s="56"/>
-      <c r="K34" s="56"/>
-      <c r="L34" s="56"/>
-      <c r="M34" s="94"/>
-      <c r="N34" s="94"/>
-      <c r="O34" s="94"/>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="95"/>
+      <c r="A34" s="80"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="63"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="63"/>
+      <c r="K34" s="63"/>
+      <c r="L34" s="63"/>
+      <c r="M34" s="60"/>
+      <c r="N34" s="60"/>
+      <c r="O34" s="60"/>
+      <c r="P34" s="60"/>
+      <c r="Q34" s="60"/>
+      <c r="R34" s="86"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="55" t="s">
+      <c r="A35" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="97"/>
-      <c r="F35" s="97"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="97"/>
-      <c r="I35" s="97"/>
-      <c r="J35" s="97"/>
-      <c r="K35" s="97"/>
-      <c r="L35" s="97"/>
-      <c r="M35" s="97"/>
-      <c r="N35" s="97"/>
-      <c r="O35" s="97"/>
-      <c r="P35" s="97"/>
-      <c r="Q35" s="97"/>
-      <c r="R35" s="98"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="89"/>
+      <c r="E35" s="90"/>
+      <c r="F35" s="90"/>
+      <c r="G35" s="90"/>
+      <c r="H35" s="90"/>
+      <c r="I35" s="90"/>
+      <c r="J35" s="90"/>
+      <c r="K35" s="90"/>
+      <c r="L35" s="90"/>
+      <c r="M35" s="90"/>
+      <c r="N35" s="90"/>
+      <c r="O35" s="90"/>
+      <c r="P35" s="90"/>
+      <c r="Q35" s="90"/>
+      <c r="R35" s="91"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="57"/>
-      <c r="B36" s="58"/>
-      <c r="C36" s="58"/>
-      <c r="D36" s="99"/>
-      <c r="E36" s="100"/>
-      <c r="F36" s="100"/>
-      <c r="G36" s="100"/>
-      <c r="H36" s="100"/>
-      <c r="I36" s="100"/>
-      <c r="J36" s="100"/>
-      <c r="K36" s="100"/>
-      <c r="L36" s="100"/>
-      <c r="M36" s="100"/>
-      <c r="N36" s="100"/>
-      <c r="O36" s="100"/>
-      <c r="P36" s="100"/>
-      <c r="Q36" s="100"/>
-      <c r="R36" s="101"/>
+      <c r="A36" s="87"/>
+      <c r="B36" s="88"/>
+      <c r="C36" s="88"/>
+      <c r="D36" s="92"/>
+      <c r="E36" s="93"/>
+      <c r="F36" s="93"/>
+      <c r="G36" s="93"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="93"/>
+      <c r="J36" s="93"/>
+      <c r="K36" s="93"/>
+      <c r="L36" s="93"/>
+      <c r="M36" s="93"/>
+      <c r="N36" s="93"/>
+      <c r="O36" s="93"/>
+      <c r="P36" s="93"/>
+      <c r="Q36" s="93"/>
+      <c r="R36" s="94"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="87"/>
-      <c r="B37" s="88"/>
-      <c r="C37" s="88"/>
-      <c r="D37" s="88"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="88"/>
-      <c r="H37" s="88"/>
-      <c r="I37" s="88"/>
-      <c r="J37" s="88"/>
-      <c r="K37" s="88"/>
-      <c r="L37" s="88"/>
-      <c r="M37" s="88"/>
-      <c r="N37" s="88"/>
-      <c r="O37" s="88"/>
-      <c r="P37" s="88"/>
-      <c r="Q37" s="88"/>
-      <c r="R37" s="88"/>
+      <c r="A37" s="81"/>
+      <c r="B37" s="82"/>
+      <c r="C37" s="82"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="82"/>
+      <c r="K37" s="82"/>
+      <c r="L37" s="82"/>
+      <c r="M37" s="82"/>
+      <c r="N37" s="82"/>
+      <c r="O37" s="82"/>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="82"/>
+      <c r="R37" s="82"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="89"/>
-      <c r="B38" s="89"/>
-      <c r="C38" s="89"/>
-      <c r="D38" s="89"/>
-      <c r="E38" s="89"/>
-      <c r="F38" s="89"/>
-      <c r="G38" s="89"/>
-      <c r="H38" s="89"/>
-      <c r="I38" s="89"/>
-      <c r="J38" s="89"/>
-      <c r="K38" s="89"/>
-      <c r="L38" s="89"/>
-      <c r="M38" s="89"/>
-      <c r="N38" s="89"/>
-      <c r="O38" s="89"/>
-      <c r="P38" s="89"/>
-      <c r="Q38" s="89"/>
-      <c r="R38" s="89"/>
+      <c r="A38" s="83"/>
+      <c r="B38" s="83"/>
+      <c r="C38" s="83"/>
+      <c r="D38" s="83"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="83"/>
+      <c r="I38" s="83"/>
+      <c r="J38" s="83"/>
+      <c r="K38" s="83"/>
+      <c r="L38" s="83"/>
+      <c r="M38" s="83"/>
+      <c r="N38" s="83"/>
+      <c r="O38" s="83"/>
+      <c r="P38" s="83"/>
+      <c r="Q38" s="83"/>
+      <c r="R38" s="83"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="59" t="s">
+      <c r="A39" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="60"/>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60" t="s">
+      <c r="B39" s="61"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="90"/>
-      <c r="H39" s="60" t="s">
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="I39" s="60"/>
-      <c r="J39" s="60"/>
-      <c r="K39" s="60" t="s">
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="L39" s="60"/>
-      <c r="M39" s="60"/>
-      <c r="N39" s="90"/>
-      <c r="O39" s="60" t="s">
+      <c r="L39" s="61"/>
+      <c r="M39" s="61"/>
+      <c r="N39" s="75"/>
+      <c r="O39" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="P39" s="60"/>
-      <c r="Q39" s="60"/>
-      <c r="R39" s="110"/>
+      <c r="P39" s="61"/>
+      <c r="Q39" s="61"/>
+      <c r="R39" s="62"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="55"/>
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="56"/>
-      <c r="K40" s="56"/>
-      <c r="L40" s="56"/>
-      <c r="M40" s="56"/>
-      <c r="N40" s="91"/>
-      <c r="O40" s="56"/>
-      <c r="P40" s="56"/>
-      <c r="Q40" s="56"/>
-      <c r="R40" s="111"/>
+      <c r="A40" s="80"/>
+      <c r="B40" s="63"/>
+      <c r="C40" s="63"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="63"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="63"/>
+      <c r="K40" s="63"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="76"/>
+      <c r="O40" s="63"/>
+      <c r="P40" s="63"/>
+      <c r="Q40" s="63"/>
+      <c r="R40" s="64"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="104" t="s">
+      <c r="A41" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="105"/>
-      <c r="C41" s="106"/>
-      <c r="D41" s="112"/>
-      <c r="E41" s="113"/>
-      <c r="F41" s="113"/>
-      <c r="G41" s="114"/>
-      <c r="H41" s="141" t="s">
+      <c r="B41" s="55"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="142"/>
-      <c r="J41" s="143"/>
-      <c r="K41" s="112"/>
-      <c r="L41" s="113"/>
-      <c r="M41" s="113"/>
-      <c r="N41" s="114"/>
-      <c r="O41" s="133"/>
-      <c r="P41" s="133"/>
-      <c r="Q41" s="133"/>
-      <c r="R41" s="134"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="65"/>
+      <c r="L41" s="66"/>
+      <c r="M41" s="66"/>
+      <c r="N41" s="67"/>
+      <c r="O41" s="71"/>
+      <c r="P41" s="71"/>
+      <c r="Q41" s="71"/>
+      <c r="R41" s="72"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="107"/>
-      <c r="B42" s="108"/>
-      <c r="C42" s="109"/>
-      <c r="D42" s="115"/>
-      <c r="E42" s="116"/>
-      <c r="F42" s="116"/>
-      <c r="G42" s="117"/>
-      <c r="H42" s="144"/>
-      <c r="I42" s="145"/>
-      <c r="J42" s="146"/>
-      <c r="K42" s="115"/>
-      <c r="L42" s="116"/>
-      <c r="M42" s="116"/>
-      <c r="N42" s="117"/>
-      <c r="O42" s="133"/>
-      <c r="P42" s="133"/>
-      <c r="Q42" s="133"/>
-      <c r="R42" s="134"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="58"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="69"/>
+      <c r="F42" s="69"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="68"/>
+      <c r="L42" s="69"/>
+      <c r="M42" s="69"/>
+      <c r="N42" s="70"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="104" t="s">
+      <c r="A43" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="105"/>
-      <c r="C43" s="106"/>
-      <c r="D43" s="112"/>
-      <c r="E43" s="113"/>
-      <c r="F43" s="113"/>
-      <c r="G43" s="114"/>
-      <c r="H43" s="139" t="s">
+      <c r="B43" s="55"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="67"/>
+      <c r="H43" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="105"/>
-      <c r="J43" s="106"/>
-      <c r="K43" s="112"/>
-      <c r="L43" s="113"/>
-      <c r="M43" s="113"/>
-      <c r="N43" s="114"/>
-      <c r="O43" s="133"/>
-      <c r="P43" s="133"/>
-      <c r="Q43" s="133"/>
-      <c r="R43" s="134"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="56"/>
+      <c r="K43" s="65"/>
+      <c r="L43" s="66"/>
+      <c r="M43" s="66"/>
+      <c r="N43" s="67"/>
+      <c r="O43" s="71"/>
+      <c r="P43" s="71"/>
+      <c r="Q43" s="71"/>
+      <c r="R43" s="72"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="107"/>
-      <c r="B44" s="108"/>
-      <c r="C44" s="109"/>
-      <c r="D44" s="115"/>
-      <c r="E44" s="116"/>
-      <c r="F44" s="116"/>
-      <c r="G44" s="117"/>
-      <c r="H44" s="140"/>
-      <c r="I44" s="108"/>
-      <c r="J44" s="109"/>
-      <c r="K44" s="115"/>
-      <c r="L44" s="116"/>
-      <c r="M44" s="116"/>
-      <c r="N44" s="117"/>
-      <c r="O44" s="133"/>
-      <c r="P44" s="133"/>
-      <c r="Q44" s="133"/>
-      <c r="R44" s="134"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="58"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="78"/>
+      <c r="I44" s="58"/>
+      <c r="J44" s="59"/>
+      <c r="K44" s="68"/>
+      <c r="L44" s="69"/>
+      <c r="M44" s="69"/>
+      <c r="N44" s="70"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="102" t="s">
+      <c r="A45" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="103"/>
-      <c r="C45" s="103"/>
-      <c r="D45" s="137"/>
-      <c r="E45" s="137"/>
-      <c r="F45" s="137"/>
-      <c r="G45" s="138"/>
-      <c r="H45" s="103" t="s">
+      <c r="B45" s="53"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="157"/>
+      <c r="E45" s="157"/>
+      <c r="F45" s="157"/>
+      <c r="G45" s="158"/>
+      <c r="H45" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="103"/>
-      <c r="J45" s="103"/>
-      <c r="K45" s="137"/>
-      <c r="L45" s="137"/>
-      <c r="M45" s="137"/>
-      <c r="N45" s="138"/>
-      <c r="O45" s="135"/>
-      <c r="P45" s="135"/>
-      <c r="Q45" s="135"/>
-      <c r="R45" s="136"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="157"/>
+      <c r="L45" s="157"/>
+      <c r="M45" s="157"/>
+      <c r="N45" s="158"/>
+      <c r="O45" s="73"/>
+      <c r="P45" s="73"/>
+      <c r="Q45" s="73"/>
+      <c r="R45" s="74"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2683,233 +2680,233 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="30"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="122"/>
-      <c r="E49" s="123"/>
-      <c r="F49" s="123"/>
-      <c r="G49" s="123"/>
-      <c r="H49" s="131"/>
-      <c r="I49" s="122"/>
-      <c r="J49" s="123"/>
-      <c r="K49" s="123"/>
-      <c r="L49" s="123"/>
-      <c r="M49" s="131"/>
-      <c r="N49" s="122"/>
-      <c r="O49" s="123"/>
-      <c r="P49" s="123"/>
-      <c r="Q49" s="123"/>
-      <c r="R49" s="124"/>
+      <c r="A49" s="123"/>
+      <c r="B49" s="124"/>
+      <c r="C49" s="125"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="50"/>
+      <c r="I49" s="40"/>
+      <c r="J49" s="41"/>
+      <c r="K49" s="41"/>
+      <c r="L49" s="41"/>
+      <c r="M49" s="50"/>
+      <c r="N49" s="40"/>
+      <c r="O49" s="41"/>
+      <c r="P49" s="41"/>
+      <c r="Q49" s="41"/>
+      <c r="R49" s="42"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="33"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="35"/>
-      <c r="D50" s="125"/>
-      <c r="E50" s="126"/>
-      <c r="F50" s="126"/>
-      <c r="G50" s="126"/>
-      <c r="H50" s="132"/>
-      <c r="I50" s="125"/>
-      <c r="J50" s="126"/>
-      <c r="K50" s="126"/>
-      <c r="L50" s="126"/>
-      <c r="M50" s="132"/>
-      <c r="N50" s="125"/>
-      <c r="O50" s="126"/>
-      <c r="P50" s="126"/>
-      <c r="Q50" s="126"/>
-      <c r="R50" s="127"/>
+      <c r="A50" s="126"/>
+      <c r="B50" s="127"/>
+      <c r="C50" s="128"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="51"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44"/>
+      <c r="L50" s="44"/>
+      <c r="M50" s="51"/>
+      <c r="N50" s="43"/>
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="45"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="46" t="s">
+      <c r="A51" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="47"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
-      <c r="G51" s="52"/>
-      <c r="H51" s="52"/>
-      <c r="I51" s="52"/>
-      <c r="J51" s="52"/>
-      <c r="K51" s="52"/>
-      <c r="L51" s="52"/>
-      <c r="M51" s="52"/>
-      <c r="N51" s="52"/>
-      <c r="O51" s="52"/>
-      <c r="P51" s="52"/>
-      <c r="Q51" s="52"/>
-      <c r="R51" s="128"/>
+      <c r="B51" s="140"/>
+      <c r="C51" s="141"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="46"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="46"/>
+      <c r="I51" s="46"/>
+      <c r="J51" s="46"/>
+      <c r="K51" s="46"/>
+      <c r="L51" s="46"/>
+      <c r="M51" s="46"/>
+      <c r="N51" s="46"/>
+      <c r="O51" s="46"/>
+      <c r="P51" s="46"/>
+      <c r="Q51" s="46"/>
+      <c r="R51" s="47"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="49"/>
-      <c r="B52" s="50"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
-      <c r="H52" s="52"/>
-      <c r="I52" s="52"/>
-      <c r="J52" s="52"/>
-      <c r="K52" s="52"/>
-      <c r="L52" s="52"/>
-      <c r="M52" s="52"/>
-      <c r="N52" s="52"/>
-      <c r="O52" s="52"/>
-      <c r="P52" s="52"/>
-      <c r="Q52" s="52"/>
-      <c r="R52" s="128"/>
+      <c r="A52" s="142"/>
+      <c r="B52" s="143"/>
+      <c r="C52" s="144"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="46"/>
+      <c r="I52" s="46"/>
+      <c r="J52" s="46"/>
+      <c r="K52" s="46"/>
+      <c r="L52" s="46"/>
+      <c r="M52" s="46"/>
+      <c r="N52" s="46"/>
+      <c r="O52" s="46"/>
+      <c r="P52" s="46"/>
+      <c r="Q52" s="46"/>
+      <c r="R52" s="47"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
       <c r="B53" s="4"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="119"/>
-      <c r="E53" s="120"/>
-      <c r="F53" s="120"/>
-      <c r="G53" s="120"/>
-      <c r="H53" s="129"/>
-      <c r="I53" s="119"/>
-      <c r="J53" s="120"/>
-      <c r="K53" s="120"/>
-      <c r="L53" s="120"/>
-      <c r="M53" s="129"/>
-      <c r="N53" s="119"/>
-      <c r="O53" s="120"/>
-      <c r="P53" s="120"/>
-      <c r="Q53" s="120"/>
-      <c r="R53" s="121"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="37"/>
+      <c r="J53" s="38"/>
+      <c r="K53" s="38"/>
+      <c r="L53" s="38"/>
+      <c r="M53" s="48"/>
+      <c r="N53" s="37"/>
+      <c r="O53" s="38"/>
+      <c r="P53" s="38"/>
+      <c r="Q53" s="38"/>
+      <c r="R53" s="39"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="40" t="s">
+      <c r="A54" s="133" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="41"/>
-      <c r="C54" s="42"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="36"/>
-      <c r="I54" s="36"/>
-      <c r="J54" s="36"/>
-      <c r="K54" s="36"/>
-      <c r="L54" s="36"/>
-      <c r="M54" s="36"/>
-      <c r="N54" s="36"/>
-      <c r="O54" s="36"/>
-      <c r="P54" s="36"/>
-      <c r="Q54" s="36"/>
-      <c r="R54" s="37"/>
+      <c r="B54" s="134"/>
+      <c r="C54" s="135"/>
+      <c r="D54" s="129"/>
+      <c r="E54" s="129"/>
+      <c r="F54" s="129"/>
+      <c r="G54" s="129"/>
+      <c r="H54" s="129"/>
+      <c r="I54" s="129"/>
+      <c r="J54" s="129"/>
+      <c r="K54" s="129"/>
+      <c r="L54" s="129"/>
+      <c r="M54" s="129"/>
+      <c r="N54" s="129"/>
+      <c r="O54" s="129"/>
+      <c r="P54" s="129"/>
+      <c r="Q54" s="129"/>
+      <c r="R54" s="130"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="43"/>
-      <c r="B55" s="44"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="38"/>
-      <c r="I55" s="38"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="38"/>
-      <c r="L55" s="38"/>
-      <c r="M55" s="38"/>
-      <c r="N55" s="38"/>
-      <c r="O55" s="38"/>
-      <c r="P55" s="38"/>
-      <c r="Q55" s="38"/>
-      <c r="R55" s="39"/>
+      <c r="A55" s="136"/>
+      <c r="B55" s="137"/>
+      <c r="C55" s="138"/>
+      <c r="D55" s="131"/>
+      <c r="E55" s="131"/>
+      <c r="F55" s="131"/>
+      <c r="G55" s="131"/>
+      <c r="H55" s="131"/>
+      <c r="I55" s="131"/>
+      <c r="J55" s="131"/>
+      <c r="K55" s="131"/>
+      <c r="L55" s="131"/>
+      <c r="M55" s="131"/>
+      <c r="N55" s="131"/>
+      <c r="O55" s="131"/>
+      <c r="P55" s="131"/>
+      <c r="Q55" s="131"/>
+      <c r="R55" s="132"/>
     </row>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="40" t="s">
+      <c r="A56" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="B56" s="41"/>
-      <c r="C56" s="42"/>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
-      <c r="H56" s="36"/>
-      <c r="I56" s="36"/>
-      <c r="J56" s="36"/>
-      <c r="K56" s="36"/>
-      <c r="L56" s="36"/>
-      <c r="M56" s="36"/>
-      <c r="N56" s="36"/>
-      <c r="O56" s="36"/>
-      <c r="P56" s="36"/>
-      <c r="Q56" s="36"/>
-      <c r="R56" s="37"/>
+      <c r="B56" s="134"/>
+      <c r="C56" s="135"/>
+      <c r="D56" s="129"/>
+      <c r="E56" s="129"/>
+      <c r="F56" s="129"/>
+      <c r="G56" s="129"/>
+      <c r="H56" s="129"/>
+      <c r="I56" s="129"/>
+      <c r="J56" s="129"/>
+      <c r="K56" s="129"/>
+      <c r="L56" s="129"/>
+      <c r="M56" s="129"/>
+      <c r="N56" s="129"/>
+      <c r="O56" s="129"/>
+      <c r="P56" s="129"/>
+      <c r="Q56" s="129"/>
+      <c r="R56" s="130"/>
     </row>
     <row r="57" spans="1:18" s="2" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="43"/>
-      <c r="B57" s="44"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="38"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="38"/>
-      <c r="L57" s="38"/>
-      <c r="M57" s="38"/>
-      <c r="N57" s="38"/>
-      <c r="O57" s="38"/>
-      <c r="P57" s="38"/>
-      <c r="Q57" s="38"/>
-      <c r="R57" s="39"/>
+      <c r="A57" s="136"/>
+      <c r="B57" s="137"/>
+      <c r="C57" s="138"/>
+      <c r="D57" s="131"/>
+      <c r="E57" s="131"/>
+      <c r="F57" s="131"/>
+      <c r="G57" s="131"/>
+      <c r="H57" s="131"/>
+      <c r="I57" s="131"/>
+      <c r="J57" s="131"/>
+      <c r="K57" s="131"/>
+      <c r="L57" s="131"/>
+      <c r="M57" s="131"/>
+      <c r="N57" s="131"/>
+      <c r="O57" s="131"/>
+      <c r="P57" s="131"/>
+      <c r="Q57" s="131"/>
+      <c r="R57" s="132"/>
     </row>
     <row r="58" spans="1:18" s="2" customFormat="1" ht="27" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D58" s="130"/>
-      <c r="E58" s="130"/>
-      <c r="F58" s="130"/>
-      <c r="G58" s="130"/>
-      <c r="H58" s="130"/>
-      <c r="I58" s="130"/>
-      <c r="J58" s="130"/>
-      <c r="K58" s="130"/>
-      <c r="L58" s="130"/>
-      <c r="M58" s="130"/>
-      <c r="N58" s="130"/>
-      <c r="O58" s="130"/>
-      <c r="P58" s="130"/>
-      <c r="Q58" s="130"/>
-      <c r="R58" s="130"/>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="49"/>
+      <c r="J58" s="49"/>
+      <c r="K58" s="49"/>
+      <c r="L58" s="49"/>
+      <c r="M58" s="49"/>
+      <c r="N58" s="49"/>
+      <c r="O58" s="49"/>
+      <c r="P58" s="49"/>
+      <c r="Q58" s="49"/>
+      <c r="R58" s="49"/>
     </row>
     <row r="59" spans="1:18" s="2" customFormat="1" ht="30.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D59" s="118" t="str">
+      <c r="D59" s="36" t="str">
         <f>IF(MOD(D58,1000)=0,"千円単位",IF(MOD(D58,100)=0,"百円単位",IF(MOD(D58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="E59" s="118"/>
-      <c r="F59" s="118"/>
-      <c r="G59" s="118"/>
-      <c r="H59" s="118"/>
-      <c r="I59" s="118" t="str">
+      <c r="E59" s="36"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="36" t="str">
         <f>IF(MOD(I58,1000)=0,"千円単位",IF(MOD(I58,100)=0,"百円単位",IF(MOD(I58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="J59" s="118"/>
-      <c r="K59" s="118"/>
-      <c r="L59" s="118"/>
-      <c r="M59" s="118"/>
-      <c r="N59" s="118" t="str">
+      <c r="J59" s="36"/>
+      <c r="K59" s="36"/>
+      <c r="L59" s="36"/>
+      <c r="M59" s="36"/>
+      <c r="N59" s="36" t="str">
         <f>IF(MOD(N58,1000)=0,"千円単位",IF(MOD(N58,100)=0,"百円単位",IF(MOD(N58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="O59" s="118"/>
-      <c r="P59" s="118"/>
-      <c r="Q59" s="118"/>
-      <c r="R59" s="118"/>
+      <c r="O59" s="36"/>
+      <c r="P59" s="36"/>
+      <c r="Q59" s="36"/>
+      <c r="R59" s="36"/>
     </row>
     <row r="60" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="61" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2921,20 +2918,41 @@
     <row r="67" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="I59:M59"/>
-    <mergeCell ref="N59:R59"/>
-    <mergeCell ref="N53:R53"/>
-    <mergeCell ref="N49:R50"/>
-    <mergeCell ref="N51:R52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="I58:M58"/>
-    <mergeCell ref="N58:R58"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="I53:M53"/>
-    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="N56:R57"/>
+    <mergeCell ref="D54:H55"/>
+    <mergeCell ref="I54:M55"/>
+    <mergeCell ref="N54:R55"/>
+    <mergeCell ref="A54:C55"/>
+    <mergeCell ref="A56:C57"/>
+    <mergeCell ref="D56:H57"/>
+    <mergeCell ref="I56:M57"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="I51:M52"/>
+    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A22:C28"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:R21"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="O22:R28"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="J33:L34"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="M33:R34"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="D31:I32"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="H45:J45"/>
     <mergeCell ref="A43:C44"/>
@@ -2951,41 +2969,20 @@
     <mergeCell ref="D43:G44"/>
     <mergeCell ref="H43:J44"/>
     <mergeCell ref="D41:G42"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="J33:L34"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="M33:R34"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="D31:I32"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A22:C28"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:R21"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="O22:R28"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="N56:R57"/>
-    <mergeCell ref="D54:H55"/>
-    <mergeCell ref="I54:M55"/>
-    <mergeCell ref="N54:R55"/>
-    <mergeCell ref="A54:C55"/>
-    <mergeCell ref="A56:C57"/>
-    <mergeCell ref="D56:H57"/>
-    <mergeCell ref="I56:M57"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="I51:M52"/>
-    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="I59:M59"/>
+    <mergeCell ref="N59:R59"/>
+    <mergeCell ref="N53:R53"/>
+    <mergeCell ref="N49:R50"/>
+    <mergeCell ref="N51:R52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="I58:M58"/>
+    <mergeCell ref="N58:R58"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="I53:M53"/>
+    <mergeCell ref="I49:M50"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="D51:R52">
@@ -3039,62 +3036,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="157" t="s">
+      <c r="E2" s="147" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157" t="s">
+      <c r="F2" s="147"/>
+      <c r="G2" s="147" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157" t="s">
+      <c r="H2" s="147"/>
+      <c r="I2" s="147" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157" t="s">
+      <c r="J2" s="147"/>
+      <c r="K2" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157" t="s">
+      <c r="L2" s="147"/>
+      <c r="M2" s="147" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="157"/>
+      <c r="N2" s="147"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="154" t="s">
+      <c r="B3" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="154"/>
+      <c r="C3" s="145"/>
       <c r="D3" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="154"/>
-      <c r="F3" s="154"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="154"/>
-      <c r="J3" s="154"/>
-      <c r="K3" s="154"/>
-      <c r="L3" s="154"/>
-      <c r="M3" s="154"/>
-      <c r="N3" s="154"/>
+      <c r="E3" s="145"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="146"/>
+      <c r="I3" s="145"/>
+      <c r="J3" s="145"/>
+      <c r="K3" s="145"/>
+      <c r="L3" s="145"/>
+      <c r="M3" s="145"/>
+      <c r="N3" s="145"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="154"/>
-      <c r="C4" s="154"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="145"/>
       <c r="D4" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="154"/>
-      <c r="F4" s="154"/>
-      <c r="G4" s="154"/>
-      <c r="H4" s="154"/>
-      <c r="I4" s="154"/>
-      <c r="J4" s="154"/>
-      <c r="K4" s="154"/>
-      <c r="L4" s="154"/>
-      <c r="M4" s="154"/>
-      <c r="N4" s="154"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="145"/>
+      <c r="K4" s="145"/>
+      <c r="L4" s="145"/>
+      <c r="M4" s="145"/>
+      <c r="N4" s="145"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -3137,40 +3134,40 @@
       <c r="N6" s="153"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="154" t="s">
+      <c r="B7" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="154"/>
+      <c r="C7" s="145"/>
       <c r="D7" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="150"/>
-      <c r="F7" s="151"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="156"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="151"/>
-      <c r="K7" s="150"/>
-      <c r="L7" s="151"/>
-      <c r="M7" s="150"/>
-      <c r="N7" s="151"/>
+      <c r="E7" s="148"/>
+      <c r="F7" s="149"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="151"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="149"/>
+      <c r="K7" s="148"/>
+      <c r="L7" s="149"/>
+      <c r="M7" s="148"/>
+      <c r="N7" s="149"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="154"/>
-      <c r="C8" s="154"/>
+      <c r="B8" s="145"/>
+      <c r="C8" s="145"/>
       <c r="D8" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="150"/>
-      <c r="F8" s="151"/>
-      <c r="G8" s="150"/>
-      <c r="H8" s="151"/>
-      <c r="I8" s="150"/>
-      <c r="J8" s="151"/>
-      <c r="K8" s="150"/>
-      <c r="L8" s="151"/>
-      <c r="M8" s="150"/>
-      <c r="N8" s="151"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="149"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="149"/>
+      <c r="I8" s="148"/>
+      <c r="J8" s="149"/>
+      <c r="K8" s="148"/>
+      <c r="L8" s="149"/>
+      <c r="M8" s="148"/>
+      <c r="N8" s="149"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
@@ -3213,40 +3210,40 @@
       <c r="N10" s="153"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="154" t="s">
+      <c r="B11" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="154"/>
+      <c r="C11" s="145"/>
       <c r="D11" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="150"/>
-      <c r="F11" s="151"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="156"/>
-      <c r="I11" s="150"/>
-      <c r="J11" s="151"/>
-      <c r="K11" s="150"/>
-      <c r="L11" s="151"/>
-      <c r="M11" s="150"/>
-      <c r="N11" s="151"/>
+      <c r="E11" s="148"/>
+      <c r="F11" s="149"/>
+      <c r="G11" s="150"/>
+      <c r="H11" s="151"/>
+      <c r="I11" s="148"/>
+      <c r="J11" s="149"/>
+      <c r="K11" s="148"/>
+      <c r="L11" s="149"/>
+      <c r="M11" s="148"/>
+      <c r="N11" s="149"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="154"/>
-      <c r="C12" s="154"/>
+      <c r="B12" s="145"/>
+      <c r="C12" s="145"/>
       <c r="D12" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="150"/>
-      <c r="F12" s="151"/>
-      <c r="G12" s="150"/>
-      <c r="H12" s="151"/>
-      <c r="I12" s="150"/>
-      <c r="J12" s="151"/>
-      <c r="K12" s="150"/>
-      <c r="L12" s="151"/>
-      <c r="M12" s="150"/>
-      <c r="N12" s="151"/>
+      <c r="E12" s="148"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="148"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="148"/>
+      <c r="J12" s="149"/>
+      <c r="K12" s="148"/>
+      <c r="L12" s="149"/>
+      <c r="M12" s="148"/>
+      <c r="N12" s="149"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
@@ -3304,209 +3301,133 @@
       <c r="N15" s="153"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="154" t="s">
+      <c r="B16" s="145" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="154"/>
+      <c r="C16" s="145"/>
       <c r="D16" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="150"/>
-      <c r="F16" s="151"/>
-      <c r="G16" s="155"/>
-      <c r="H16" s="156"/>
-      <c r="I16" s="150"/>
-      <c r="J16" s="151"/>
-      <c r="K16" s="150"/>
-      <c r="L16" s="151"/>
-      <c r="M16" s="150"/>
-      <c r="N16" s="151"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="149"/>
+      <c r="G16" s="150"/>
+      <c r="H16" s="151"/>
+      <c r="I16" s="148"/>
+      <c r="J16" s="149"/>
+      <c r="K16" s="148"/>
+      <c r="L16" s="149"/>
+      <c r="M16" s="148"/>
+      <c r="N16" s="149"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="154"/>
-      <c r="C17" s="154"/>
+      <c r="B17" s="145"/>
+      <c r="C17" s="145"/>
       <c r="D17" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="150"/>
-      <c r="F17" s="151"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="150"/>
-      <c r="J17" s="151"/>
-      <c r="K17" s="150"/>
-      <c r="L17" s="151"/>
-      <c r="M17" s="150"/>
-      <c r="N17" s="151"/>
+      <c r="E17" s="148"/>
+      <c r="F17" s="149"/>
+      <c r="G17" s="148"/>
+      <c r="H17" s="149"/>
+      <c r="I17" s="148"/>
+      <c r="J17" s="149"/>
+      <c r="K17" s="148"/>
+      <c r="L17" s="149"/>
+      <c r="M17" s="148"/>
+      <c r="N17" s="149"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B20" s="147"/>
-      <c r="C20" s="147"/>
-      <c r="D20" s="147"/>
-      <c r="E20" s="147" t="s">
+      <c r="B20" s="154"/>
+      <c r="C20" s="154"/>
+      <c r="D20" s="154"/>
+      <c r="E20" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="147"/>
+      <c r="F20" s="154"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B21" s="147" t="s">
+      <c r="B21" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="147"/>
-      <c r="D21" s="147"/>
-      <c r="E21" s="148"/>
-      <c r="F21" s="148"/>
+      <c r="C21" s="154"/>
+      <c r="D21" s="154"/>
+      <c r="E21" s="155"/>
+      <c r="F21" s="155"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B22" s="147" t="s">
+      <c r="B22" s="154" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="147"/>
-      <c r="D22" s="147"/>
-      <c r="E22" s="148"/>
-      <c r="F22" s="148"/>
+      <c r="C22" s="154"/>
+      <c r="D22" s="154"/>
+      <c r="E22" s="155"/>
+      <c r="F22" s="155"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B23" s="147" t="s">
+      <c r="B23" s="154" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="147"/>
-      <c r="D23" s="147"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="148"/>
+      <c r="C23" s="154"/>
+      <c r="D23" s="154"/>
+      <c r="E23" s="155"/>
+      <c r="F23" s="155"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B24" s="147" t="s">
+      <c r="B24" s="154" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="147"/>
-      <c r="D24" s="147"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="148"/>
+      <c r="C24" s="154"/>
+      <c r="D24" s="154"/>
+      <c r="E24" s="155"/>
+      <c r="F24" s="155"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B25" s="147" t="s">
+      <c r="B25" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="147"/>
-      <c r="D25" s="147"/>
-      <c r="E25" s="148"/>
-      <c r="F25" s="148"/>
+      <c r="C25" s="154"/>
+      <c r="D25" s="154"/>
+      <c r="E25" s="155"/>
+      <c r="F25" s="155"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B26" s="147" t="s">
+      <c r="B26" s="154" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="147"/>
-      <c r="D26" s="147"/>
-      <c r="E26" s="159"/>
-      <c r="F26" s="159"/>
+      <c r="C26" s="154"/>
+      <c r="D26" s="154"/>
+      <c r="E26" s="155"/>
+      <c r="F26" s="155"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B27" s="147" t="s">
+      <c r="B27" s="154" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="147"/>
-      <c r="D27" s="147"/>
-      <c r="E27" s="149"/>
-      <c r="F27" s="149"/>
+      <c r="C27" s="154"/>
+      <c r="D27" s="154"/>
+      <c r="E27" s="156"/>
+      <c r="F27" s="156"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B28" s="147" t="s">
+      <c r="B28" s="154" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="147"/>
-      <c r="D28" s="147"/>
-      <c r="E28" s="148"/>
-      <c r="F28" s="148"/>
+      <c r="C28" s="154"/>
+      <c r="D28" s="154"/>
+      <c r="E28" s="155"/>
+      <c r="F28" s="155"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B29" s="147" t="s">
+      <c r="B29" s="154" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="147"/>
-      <c r="D29" s="147"/>
-      <c r="E29" s="148"/>
-      <c r="F29" s="148"/>
+      <c r="C29" s="154"/>
+      <c r="D29" s="154"/>
+      <c r="E29" s="155"/>
+      <c r="F29" s="155"/>
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="B26:D26"/>
@@ -3515,6 +3436,82 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\a\estimateTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.100.1\エルフル事務局\yokoyama\火災見積システム(mitumo)\新mitumo\見積書Excelテンプレート\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE07382B-29FB-429C-A129-4B904E201F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBB7D0B-D169-441C-B30D-DF807286D6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="90" windowWidth="28770" windowHeight="15435" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="地震おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="45">
   <si>
     <t>御　　見　　積　　書</t>
     <rPh sb="0" eb="1">
@@ -460,6 +460,19 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>ケイスウ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>長期年払割引</t>
+    <rPh sb="0" eb="2">
+      <t>チョウキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ネンハラ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ワリビキ</t>
     </rPh>
     <phoneticPr fontId="19"/>
   </si>
@@ -1222,196 +1235,74 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
     <xf numFmtId="179" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1420,6 +1311,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1498,106 +1407,109 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1605,6 +1517,107 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2007,10 +2020,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="95"/>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="95"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="28"/>
@@ -2020,16 +2033,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
-      <c r="O3" s="122"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="122"/>
-      <c r="R3" s="122"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+      <c r="R3" s="86"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="122"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="122"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="86"/>
+      <c r="Q4" s="86"/>
+      <c r="R4" s="86"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="27"/>
@@ -2092,196 +2105,196 @@
       <c r="R10" s="23"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="96" t="s">
+      <c r="A11" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="96"/>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="116"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="116"/>
-      <c r="H15" s="116"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="116"/>
-      <c r="K15" s="116"/>
-      <c r="L15" s="116"/>
-      <c r="M15" s="116"/>
-      <c r="N15" s="116"/>
-      <c r="O15" s="116"/>
-      <c r="P15" s="116"/>
-      <c r="Q15" s="116"/>
-      <c r="R15" s="116"/>
+      <c r="B15" s="80"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="80"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="117" t="s">
+      <c r="A18" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="117"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="117"/>
-      <c r="P18" s="117"/>
-      <c r="Q18" s="117"/>
-      <c r="R18" s="117"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="81"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="79" t="s">
+      <c r="A20" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="61"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="98"/>
-      <c r="H20" s="98"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="98"/>
-      <c r="K20" s="98"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="98"/>
-      <c r="N20" s="98"/>
-      <c r="O20" s="98"/>
-      <c r="P20" s="98"/>
-      <c r="Q20" s="98"/>
-      <c r="R20" s="99"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="63"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="80"/>
-      <c r="B21" s="63"/>
-      <c r="C21" s="63"/>
-      <c r="D21" s="100"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="101"/>
-      <c r="G21" s="101"/>
-      <c r="H21" s="101"/>
-      <c r="I21" s="101"/>
-      <c r="J21" s="101"/>
-      <c r="K21" s="101"/>
-      <c r="L21" s="101"/>
-      <c r="M21" s="101"/>
-      <c r="N21" s="101"/>
-      <c r="O21" s="101"/>
-      <c r="P21" s="101"/>
-      <c r="Q21" s="101"/>
-      <c r="R21" s="102"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="65"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="66"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="80" t="s">
+      <c r="A22" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="22"/>
       <c r="L22" s="21"/>
-      <c r="M22" s="103" t="s">
+      <c r="M22" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="104"/>
-      <c r="O22" s="107"/>
-      <c r="P22" s="108"/>
-      <c r="Q22" s="108"/>
-      <c r="R22" s="109"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="80"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="119"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="119"/>
-      <c r="J23" s="119"/>
-      <c r="K23" s="119"/>
-      <c r="L23" s="120"/>
-      <c r="M23" s="103"/>
-      <c r="N23" s="104"/>
-      <c r="O23" s="110"/>
-      <c r="P23" s="111"/>
-      <c r="Q23" s="111"/>
-      <c r="R23" s="112"/>
+      <c r="A23" s="55"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="83"/>
+      <c r="J23" s="83"/>
+      <c r="K23" s="83"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="74"/>
+      <c r="P23" s="75"/>
+      <c r="Q23" s="75"/>
+      <c r="R23" s="76"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="80"/>
-      <c r="B24" s="63"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="121"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="119"/>
-      <c r="G24" s="119"/>
-      <c r="H24" s="119"/>
-      <c r="I24" s="119"/>
-      <c r="J24" s="119"/>
-      <c r="K24" s="119"/>
-      <c r="L24" s="120"/>
-      <c r="M24" s="103"/>
-      <c r="N24" s="104"/>
-      <c r="O24" s="110"/>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="111"/>
-      <c r="R24" s="112"/>
+      <c r="A24" s="55"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="85"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="83"/>
+      <c r="J24" s="83"/>
+      <c r="K24" s="83"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="74"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="76"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="80"/>
-      <c r="B25" s="63"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="119"/>
-      <c r="H25" s="119"/>
-      <c r="I25" s="119"/>
-      <c r="J25" s="119"/>
-      <c r="K25" s="119"/>
-      <c r="L25" s="120"/>
-      <c r="M25" s="103"/>
-      <c r="N25" s="104"/>
-      <c r="O25" s="110"/>
-      <c r="P25" s="111"/>
-      <c r="Q25" s="111"/>
-      <c r="R25" s="112"/>
+      <c r="A25" s="55"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="83"/>
+      <c r="J25" s="83"/>
+      <c r="K25" s="83"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="74"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="76"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="80"/>
-      <c r="B26" s="63"/>
-      <c r="C26" s="63"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="56"/>
       <c r="D26" s="20"/>
       <c r="E26" s="19"/>
       <c r="F26" s="18"/>
@@ -2291,17 +2304,17 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="16"/>
-      <c r="M26" s="103"/>
-      <c r="N26" s="104"/>
-      <c r="O26" s="110"/>
-      <c r="P26" s="111"/>
-      <c r="Q26" s="111"/>
-      <c r="R26" s="112"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="75"/>
+      <c r="R26" s="76"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="80"/>
-      <c r="B27" s="63"/>
-      <c r="C27" s="63"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
       <c r="D27" s="15"/>
       <c r="F27" s="13"/>
       <c r="G27" s="14"/>
@@ -2309,17 +2322,17 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="L27" s="11"/>
-      <c r="M27" s="103"/>
-      <c r="N27" s="104"/>
-      <c r="O27" s="110"/>
-      <c r="P27" s="111"/>
-      <c r="Q27" s="111"/>
-      <c r="R27" s="112"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="68"/>
+      <c r="O27" s="74"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="75"/>
+      <c r="R27" s="76"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="87"/>
-      <c r="B28" s="88"/>
-      <c r="C28" s="88"/>
+      <c r="A28" s="57"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="58"/>
       <c r="D28" s="10"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -2329,346 +2342,346 @@
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="8"/>
-      <c r="M28" s="105"/>
-      <c r="N28" s="106"/>
-      <c r="O28" s="113"/>
-      <c r="P28" s="114"/>
-      <c r="Q28" s="114"/>
-      <c r="R28" s="115"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="70"/>
+      <c r="O28" s="77"/>
+      <c r="P28" s="78"/>
+      <c r="Q28" s="78"/>
+      <c r="R28" s="79"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="79" t="s">
+      <c r="A31" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="84"/>
-      <c r="E31" s="84"/>
-      <c r="F31" s="84"/>
-      <c r="G31" s="84"/>
-      <c r="H31" s="84"/>
-      <c r="I31" s="84"/>
-      <c r="J31" s="61" t="s">
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="92"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="61"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="84"/>
-      <c r="N31" s="84"/>
-      <c r="O31" s="84"/>
-      <c r="P31" s="84"/>
-      <c r="Q31" s="84"/>
-      <c r="R31" s="85"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="92"/>
+      <c r="O31" s="92"/>
+      <c r="P31" s="92"/>
+      <c r="Q31" s="92"/>
+      <c r="R31" s="93"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="80"/>
-      <c r="B32" s="63"/>
-      <c r="C32" s="63"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="63"/>
-      <c r="K32" s="63"/>
-      <c r="L32" s="63"/>
-      <c r="M32" s="60"/>
-      <c r="N32" s="60"/>
-      <c r="O32" s="60"/>
-      <c r="P32" s="60"/>
-      <c r="Q32" s="60"/>
-      <c r="R32" s="86"/>
+      <c r="A32" s="55"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
+      <c r="F32" s="94"/>
+      <c r="G32" s="94"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="94"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="94"/>
+      <c r="N32" s="94"/>
+      <c r="O32" s="94"/>
+      <c r="P32" s="94"/>
+      <c r="Q32" s="94"/>
+      <c r="R32" s="95"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="80" t="s">
+      <c r="A33" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="63"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="60"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="60"/>
-      <c r="I33" s="60"/>
-      <c r="J33" s="63" t="s">
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="94"/>
+      <c r="F33" s="94"/>
+      <c r="G33" s="94"/>
+      <c r="H33" s="94"/>
+      <c r="I33" s="94"/>
+      <c r="J33" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="K33" s="63"/>
-      <c r="L33" s="63"/>
-      <c r="M33" s="60"/>
-      <c r="N33" s="60"/>
-      <c r="O33" s="60"/>
-      <c r="P33" s="60"/>
-      <c r="Q33" s="60"/>
-      <c r="R33" s="86"/>
+      <c r="K33" s="56"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="94"/>
+      <c r="N33" s="94"/>
+      <c r="O33" s="94"/>
+      <c r="P33" s="94"/>
+      <c r="Q33" s="94"/>
+      <c r="R33" s="95"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="80"/>
-      <c r="B34" s="63"/>
-      <c r="C34" s="63"/>
-      <c r="D34" s="60"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="60"/>
-      <c r="G34" s="60"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="60"/>
-      <c r="J34" s="63"/>
-      <c r="K34" s="63"/>
-      <c r="L34" s="63"/>
-      <c r="M34" s="60"/>
-      <c r="N34" s="60"/>
-      <c r="O34" s="60"/>
-      <c r="P34" s="60"/>
-      <c r="Q34" s="60"/>
-      <c r="R34" s="86"/>
+      <c r="A34" s="55"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="94"/>
+      <c r="G34" s="94"/>
+      <c r="H34" s="94"/>
+      <c r="I34" s="94"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="94"/>
+      <c r="N34" s="94"/>
+      <c r="O34" s="94"/>
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="95"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="80" t="s">
+      <c r="A35" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="63"/>
-      <c r="C35" s="63"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="90"/>
-      <c r="F35" s="90"/>
-      <c r="G35" s="90"/>
-      <c r="H35" s="90"/>
-      <c r="I35" s="90"/>
-      <c r="J35" s="90"/>
-      <c r="K35" s="90"/>
-      <c r="L35" s="90"/>
-      <c r="M35" s="90"/>
-      <c r="N35" s="90"/>
-      <c r="O35" s="90"/>
-      <c r="P35" s="90"/>
-      <c r="Q35" s="90"/>
-      <c r="R35" s="91"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="97"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="97"/>
+      <c r="I35" s="97"/>
+      <c r="J35" s="97"/>
+      <c r="K35" s="97"/>
+      <c r="L35" s="97"/>
+      <c r="M35" s="97"/>
+      <c r="N35" s="97"/>
+      <c r="O35" s="97"/>
+      <c r="P35" s="97"/>
+      <c r="Q35" s="97"/>
+      <c r="R35" s="98"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="87"/>
-      <c r="B36" s="88"/>
-      <c r="C36" s="88"/>
-      <c r="D36" s="92"/>
-      <c r="E36" s="93"/>
-      <c r="F36" s="93"/>
-      <c r="G36" s="93"/>
-      <c r="H36" s="93"/>
-      <c r="I36" s="93"/>
-      <c r="J36" s="93"/>
-      <c r="K36" s="93"/>
-      <c r="L36" s="93"/>
-      <c r="M36" s="93"/>
-      <c r="N36" s="93"/>
-      <c r="O36" s="93"/>
-      <c r="P36" s="93"/>
-      <c r="Q36" s="93"/>
-      <c r="R36" s="94"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="99"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="100"/>
+      <c r="G36" s="100"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="100"/>
+      <c r="J36" s="100"/>
+      <c r="K36" s="100"/>
+      <c r="L36" s="100"/>
+      <c r="M36" s="100"/>
+      <c r="N36" s="100"/>
+      <c r="O36" s="100"/>
+      <c r="P36" s="100"/>
+      <c r="Q36" s="100"/>
+      <c r="R36" s="101"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="81"/>
-      <c r="B37" s="82"/>
-      <c r="C37" s="82"/>
-      <c r="D37" s="82"/>
-      <c r="E37" s="82"/>
-      <c r="F37" s="82"/>
-      <c r="G37" s="82"/>
-      <c r="H37" s="82"/>
-      <c r="I37" s="82"/>
-      <c r="J37" s="82"/>
-      <c r="K37" s="82"/>
-      <c r="L37" s="82"/>
-      <c r="M37" s="82"/>
-      <c r="N37" s="82"/>
-      <c r="O37" s="82"/>
-      <c r="P37" s="82"/>
-      <c r="Q37" s="82"/>
-      <c r="R37" s="82"/>
+      <c r="A37" s="87"/>
+      <c r="B37" s="88"/>
+      <c r="C37" s="88"/>
+      <c r="D37" s="88"/>
+      <c r="E37" s="88"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="88"/>
+      <c r="I37" s="88"/>
+      <c r="J37" s="88"/>
+      <c r="K37" s="88"/>
+      <c r="L37" s="88"/>
+      <c r="M37" s="88"/>
+      <c r="N37" s="88"/>
+      <c r="O37" s="88"/>
+      <c r="P37" s="88"/>
+      <c r="Q37" s="88"/>
+      <c r="R37" s="88"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="83"/>
-      <c r="B38" s="83"/>
-      <c r="C38" s="83"/>
-      <c r="D38" s="83"/>
-      <c r="E38" s="83"/>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="83"/>
-      <c r="L38" s="83"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
-      <c r="O38" s="83"/>
-      <c r="P38" s="83"/>
-      <c r="Q38" s="83"/>
-      <c r="R38" s="83"/>
+      <c r="A38" s="89"/>
+      <c r="B38" s="89"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="89"/>
+      <c r="H38" s="89"/>
+      <c r="I38" s="89"/>
+      <c r="J38" s="89"/>
+      <c r="K38" s="89"/>
+      <c r="L38" s="89"/>
+      <c r="M38" s="89"/>
+      <c r="N38" s="89"/>
+      <c r="O38" s="89"/>
+      <c r="P38" s="89"/>
+      <c r="Q38" s="89"/>
+      <c r="R38" s="89"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="79" t="s">
+      <c r="A39" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="61"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61" t="s">
+      <c r="B39" s="60"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="61" t="s">
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="90"/>
+      <c r="H39" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="I39" s="61"/>
-      <c r="J39" s="61"/>
-      <c r="K39" s="61" t="s">
+      <c r="I39" s="60"/>
+      <c r="J39" s="60"/>
+      <c r="K39" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="L39" s="61"/>
-      <c r="M39" s="61"/>
-      <c r="N39" s="75"/>
-      <c r="O39" s="61" t="s">
+      <c r="L39" s="60"/>
+      <c r="M39" s="60"/>
+      <c r="N39" s="90"/>
+      <c r="O39" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="P39" s="61"/>
-      <c r="Q39" s="61"/>
-      <c r="R39" s="62"/>
+      <c r="P39" s="60"/>
+      <c r="Q39" s="60"/>
+      <c r="R39" s="110"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="80"/>
-      <c r="B40" s="63"/>
-      <c r="C40" s="63"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="63"/>
-      <c r="G40" s="76"/>
-      <c r="H40" s="63"/>
-      <c r="I40" s="63"/>
-      <c r="J40" s="63"/>
-      <c r="K40" s="63"/>
-      <c r="L40" s="63"/>
-      <c r="M40" s="63"/>
-      <c r="N40" s="76"/>
-      <c r="O40" s="63"/>
-      <c r="P40" s="63"/>
-      <c r="Q40" s="63"/>
-      <c r="R40" s="64"/>
+      <c r="A40" s="55"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="56"/>
+      <c r="N40" s="91"/>
+      <c r="O40" s="56"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="56"/>
+      <c r="R40" s="111"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="54" t="s">
+      <c r="A41" s="104" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="55"/>
-      <c r="C41" s="56"/>
-      <c r="D41" s="65"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="30" t="s">
+      <c r="B41" s="105"/>
+      <c r="C41" s="106"/>
+      <c r="D41" s="112"/>
+      <c r="E41" s="113"/>
+      <c r="F41" s="113"/>
+      <c r="G41" s="114"/>
+      <c r="H41" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="31"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="65"/>
-      <c r="L41" s="66"/>
-      <c r="M41" s="66"/>
-      <c r="N41" s="67"/>
-      <c r="O41" s="71"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="71"/>
-      <c r="R41" s="72"/>
+      <c r="I41" s="127"/>
+      <c r="J41" s="128"/>
+      <c r="K41" s="112"/>
+      <c r="L41" s="113"/>
+      <c r="M41" s="113"/>
+      <c r="N41" s="114"/>
+      <c r="O41" s="118"/>
+      <c r="P41" s="118"/>
+      <c r="Q41" s="118"/>
+      <c r="R41" s="119"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="57"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="59"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="69"/>
-      <c r="F42" s="69"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="68"/>
-      <c r="L42" s="69"/>
-      <c r="M42" s="69"/>
-      <c r="N42" s="70"/>
-      <c r="O42" s="71"/>
-      <c r="P42" s="71"/>
-      <c r="Q42" s="71"/>
-      <c r="R42" s="72"/>
+      <c r="A42" s="107"/>
+      <c r="B42" s="108"/>
+      <c r="C42" s="109"/>
+      <c r="D42" s="115"/>
+      <c r="E42" s="116"/>
+      <c r="F42" s="116"/>
+      <c r="G42" s="117"/>
+      <c r="H42" s="129"/>
+      <c r="I42" s="130"/>
+      <c r="J42" s="131"/>
+      <c r="K42" s="115"/>
+      <c r="L42" s="116"/>
+      <c r="M42" s="116"/>
+      <c r="N42" s="117"/>
+      <c r="O42" s="118"/>
+      <c r="P42" s="118"/>
+      <c r="Q42" s="118"/>
+      <c r="R42" s="119"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="54" t="s">
+      <c r="A43" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="55"/>
-      <c r="C43" s="56"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="66"/>
-      <c r="G43" s="67"/>
-      <c r="H43" s="77" t="s">
+      <c r="B43" s="105"/>
+      <c r="C43" s="106"/>
+      <c r="D43" s="112"/>
+      <c r="E43" s="113"/>
+      <c r="F43" s="113"/>
+      <c r="G43" s="114"/>
+      <c r="H43" s="124" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="55"/>
-      <c r="J43" s="56"/>
-      <c r="K43" s="65"/>
-      <c r="L43" s="66"/>
-      <c r="M43" s="66"/>
-      <c r="N43" s="67"/>
-      <c r="O43" s="71"/>
-      <c r="P43" s="71"/>
-      <c r="Q43" s="71"/>
-      <c r="R43" s="72"/>
+      <c r="I43" s="105"/>
+      <c r="J43" s="106"/>
+      <c r="K43" s="112"/>
+      <c r="L43" s="113"/>
+      <c r="M43" s="113"/>
+      <c r="N43" s="114"/>
+      <c r="O43" s="118"/>
+      <c r="P43" s="118"/>
+      <c r="Q43" s="118"/>
+      <c r="R43" s="119"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="57"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="59"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="70"/>
-      <c r="H44" s="78"/>
-      <c r="I44" s="58"/>
-      <c r="J44" s="59"/>
-      <c r="K44" s="68"/>
-      <c r="L44" s="69"/>
-      <c r="M44" s="69"/>
-      <c r="N44" s="70"/>
-      <c r="O44" s="71"/>
-      <c r="P44" s="71"/>
-      <c r="Q44" s="71"/>
-      <c r="R44" s="72"/>
+      <c r="A44" s="107"/>
+      <c r="B44" s="108"/>
+      <c r="C44" s="109"/>
+      <c r="D44" s="115"/>
+      <c r="E44" s="116"/>
+      <c r="F44" s="116"/>
+      <c r="G44" s="117"/>
+      <c r="H44" s="125"/>
+      <c r="I44" s="108"/>
+      <c r="J44" s="109"/>
+      <c r="K44" s="115"/>
+      <c r="L44" s="116"/>
+      <c r="M44" s="116"/>
+      <c r="N44" s="117"/>
+      <c r="O44" s="118"/>
+      <c r="P44" s="118"/>
+      <c r="Q44" s="118"/>
+      <c r="R44" s="119"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="52" t="s">
+      <c r="A45" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="53"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="157"/>
-      <c r="E45" s="157"/>
-      <c r="F45" s="157"/>
-      <c r="G45" s="158"/>
-      <c r="H45" s="53" t="s">
+      <c r="B45" s="103"/>
+      <c r="C45" s="103"/>
+      <c r="D45" s="122"/>
+      <c r="E45" s="122"/>
+      <c r="F45" s="122"/>
+      <c r="G45" s="123"/>
+      <c r="H45" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="53"/>
-      <c r="J45" s="53"/>
-      <c r="K45" s="157"/>
-      <c r="L45" s="157"/>
-      <c r="M45" s="157"/>
-      <c r="N45" s="158"/>
-      <c r="O45" s="73"/>
-      <c r="P45" s="73"/>
-      <c r="Q45" s="73"/>
-      <c r="R45" s="74"/>
+      <c r="I45" s="103"/>
+      <c r="J45" s="103"/>
+      <c r="K45" s="122"/>
+      <c r="L45" s="122"/>
+      <c r="M45" s="122"/>
+      <c r="N45" s="123"/>
+      <c r="O45" s="120"/>
+      <c r="P45" s="120"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="121"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2680,233 +2693,233 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="123"/>
-      <c r="B49" s="124"/>
-      <c r="C49" s="125"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="50"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
-      <c r="M49" s="50"/>
-      <c r="N49" s="40"/>
-      <c r="O49" s="41"/>
-      <c r="P49" s="41"/>
-      <c r="Q49" s="41"/>
-      <c r="R49" s="42"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="136"/>
+      <c r="E49" s="137"/>
+      <c r="F49" s="137"/>
+      <c r="G49" s="137"/>
+      <c r="H49" s="145"/>
+      <c r="I49" s="136"/>
+      <c r="J49" s="137"/>
+      <c r="K49" s="137"/>
+      <c r="L49" s="137"/>
+      <c r="M49" s="145"/>
+      <c r="N49" s="136"/>
+      <c r="O49" s="137"/>
+      <c r="P49" s="137"/>
+      <c r="Q49" s="137"/>
+      <c r="R49" s="138"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="126"/>
-      <c r="B50" s="127"/>
-      <c r="C50" s="128"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="44"/>
-      <c r="F50" s="44"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="43"/>
-      <c r="J50" s="44"/>
-      <c r="K50" s="44"/>
-      <c r="L50" s="44"/>
-      <c r="M50" s="51"/>
-      <c r="N50" s="43"/>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
-      <c r="R50" s="45"/>
+      <c r="A50" s="33"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="139"/>
+      <c r="E50" s="140"/>
+      <c r="F50" s="140"/>
+      <c r="G50" s="140"/>
+      <c r="H50" s="146"/>
+      <c r="I50" s="139"/>
+      <c r="J50" s="140"/>
+      <c r="K50" s="140"/>
+      <c r="L50" s="140"/>
+      <c r="M50" s="146"/>
+      <c r="N50" s="139"/>
+      <c r="O50" s="140"/>
+      <c r="P50" s="140"/>
+      <c r="Q50" s="140"/>
+      <c r="R50" s="141"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="139" t="s">
+      <c r="A51" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="140"/>
-      <c r="C51" s="141"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="46"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="46"/>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46"/>
-      <c r="O51" s="46"/>
-      <c r="P51" s="46"/>
-      <c r="Q51" s="46"/>
-      <c r="R51" s="47"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="52"/>
+      <c r="J51" s="52"/>
+      <c r="K51" s="52"/>
+      <c r="L51" s="52"/>
+      <c r="M51" s="52"/>
+      <c r="N51" s="52"/>
+      <c r="O51" s="52"/>
+      <c r="P51" s="52"/>
+      <c r="Q51" s="52"/>
+      <c r="R51" s="142"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="142"/>
-      <c r="B52" s="143"/>
-      <c r="C52" s="144"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="46"/>
-      <c r="L52" s="46"/>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
-      <c r="O52" s="46"/>
-      <c r="P52" s="46"/>
-      <c r="Q52" s="46"/>
-      <c r="R52" s="47"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="50"/>
+      <c r="C52" s="51"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
+      <c r="G52" s="52"/>
+      <c r="H52" s="52"/>
+      <c r="I52" s="52"/>
+      <c r="J52" s="52"/>
+      <c r="K52" s="52"/>
+      <c r="L52" s="52"/>
+      <c r="M52" s="52"/>
+      <c r="N52" s="52"/>
+      <c r="O52" s="52"/>
+      <c r="P52" s="52"/>
+      <c r="Q52" s="52"/>
+      <c r="R52" s="142"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
       <c r="B53" s="4"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="37"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
-      <c r="L53" s="38"/>
-      <c r="M53" s="48"/>
-      <c r="N53" s="37"/>
-      <c r="O53" s="38"/>
-      <c r="P53" s="38"/>
-      <c r="Q53" s="38"/>
-      <c r="R53" s="39"/>
+      <c r="D53" s="133"/>
+      <c r="E53" s="134"/>
+      <c r="F53" s="134"/>
+      <c r="G53" s="134"/>
+      <c r="H53" s="143"/>
+      <c r="I53" s="133"/>
+      <c r="J53" s="134"/>
+      <c r="K53" s="134"/>
+      <c r="L53" s="134"/>
+      <c r="M53" s="143"/>
+      <c r="N53" s="133"/>
+      <c r="O53" s="134"/>
+      <c r="P53" s="134"/>
+      <c r="Q53" s="134"/>
+      <c r="R53" s="135"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="133" t="s">
+      <c r="A54" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="134"/>
-      <c r="C54" s="135"/>
-      <c r="D54" s="129"/>
-      <c r="E54" s="129"/>
-      <c r="F54" s="129"/>
-      <c r="G54" s="129"/>
-      <c r="H54" s="129"/>
-      <c r="I54" s="129"/>
-      <c r="J54" s="129"/>
-      <c r="K54" s="129"/>
-      <c r="L54" s="129"/>
-      <c r="M54" s="129"/>
-      <c r="N54" s="129"/>
-      <c r="O54" s="129"/>
-      <c r="P54" s="129"/>
-      <c r="Q54" s="129"/>
-      <c r="R54" s="130"/>
+      <c r="B54" s="41"/>
+      <c r="C54" s="42"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="36"/>
+      <c r="I54" s="36"/>
+      <c r="J54" s="36"/>
+      <c r="K54" s="36"/>
+      <c r="L54" s="36"/>
+      <c r="M54" s="36"/>
+      <c r="N54" s="36"/>
+      <c r="O54" s="36"/>
+      <c r="P54" s="36"/>
+      <c r="Q54" s="36"/>
+      <c r="R54" s="37"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="136"/>
-      <c r="B55" s="137"/>
-      <c r="C55" s="138"/>
-      <c r="D55" s="131"/>
-      <c r="E55" s="131"/>
-      <c r="F55" s="131"/>
-      <c r="G55" s="131"/>
-      <c r="H55" s="131"/>
-      <c r="I55" s="131"/>
-      <c r="J55" s="131"/>
-      <c r="K55" s="131"/>
-      <c r="L55" s="131"/>
-      <c r="M55" s="131"/>
-      <c r="N55" s="131"/>
-      <c r="O55" s="131"/>
-      <c r="P55" s="131"/>
-      <c r="Q55" s="131"/>
-      <c r="R55" s="132"/>
+      <c r="A55" s="43"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="38"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="38"/>
+      <c r="G55" s="38"/>
+      <c r="H55" s="38"/>
+      <c r="I55" s="38"/>
+      <c r="J55" s="38"/>
+      <c r="K55" s="38"/>
+      <c r="L55" s="38"/>
+      <c r="M55" s="38"/>
+      <c r="N55" s="38"/>
+      <c r="O55" s="38"/>
+      <c r="P55" s="38"/>
+      <c r="Q55" s="38"/>
+      <c r="R55" s="39"/>
     </row>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="133" t="s">
+      <c r="A56" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="B56" s="134"/>
-      <c r="C56" s="135"/>
-      <c r="D56" s="129"/>
-      <c r="E56" s="129"/>
-      <c r="F56" s="129"/>
-      <c r="G56" s="129"/>
-      <c r="H56" s="129"/>
-      <c r="I56" s="129"/>
-      <c r="J56" s="129"/>
-      <c r="K56" s="129"/>
-      <c r="L56" s="129"/>
-      <c r="M56" s="129"/>
-      <c r="N56" s="129"/>
-      <c r="O56" s="129"/>
-      <c r="P56" s="129"/>
-      <c r="Q56" s="129"/>
-      <c r="R56" s="130"/>
+      <c r="B56" s="41"/>
+      <c r="C56" s="42"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="36"/>
+      <c r="J56" s="36"/>
+      <c r="K56" s="36"/>
+      <c r="L56" s="36"/>
+      <c r="M56" s="36"/>
+      <c r="N56" s="36"/>
+      <c r="O56" s="36"/>
+      <c r="P56" s="36"/>
+      <c r="Q56" s="36"/>
+      <c r="R56" s="37"/>
     </row>
     <row r="57" spans="1:18" s="2" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="136"/>
-      <c r="B57" s="137"/>
-      <c r="C57" s="138"/>
-      <c r="D57" s="131"/>
-      <c r="E57" s="131"/>
-      <c r="F57" s="131"/>
-      <c r="G57" s="131"/>
-      <c r="H57" s="131"/>
-      <c r="I57" s="131"/>
-      <c r="J57" s="131"/>
-      <c r="K57" s="131"/>
-      <c r="L57" s="131"/>
-      <c r="M57" s="131"/>
-      <c r="N57" s="131"/>
-      <c r="O57" s="131"/>
-      <c r="P57" s="131"/>
-      <c r="Q57" s="131"/>
-      <c r="R57" s="132"/>
+      <c r="A57" s="43"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="38"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="38"/>
+      <c r="I57" s="38"/>
+      <c r="J57" s="38"/>
+      <c r="K57" s="38"/>
+      <c r="L57" s="38"/>
+      <c r="M57" s="38"/>
+      <c r="N57" s="38"/>
+      <c r="O57" s="38"/>
+      <c r="P57" s="38"/>
+      <c r="Q57" s="38"/>
+      <c r="R57" s="39"/>
     </row>
     <row r="58" spans="1:18" s="2" customFormat="1" ht="27" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D58" s="49"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="49"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="49"/>
-      <c r="J58" s="49"/>
-      <c r="K58" s="49"/>
-      <c r="L58" s="49"/>
-      <c r="M58" s="49"/>
-      <c r="N58" s="49"/>
-      <c r="O58" s="49"/>
-      <c r="P58" s="49"/>
-      <c r="Q58" s="49"/>
-      <c r="R58" s="49"/>
+      <c r="D58" s="144"/>
+      <c r="E58" s="144"/>
+      <c r="F58" s="144"/>
+      <c r="G58" s="144"/>
+      <c r="H58" s="144"/>
+      <c r="I58" s="144"/>
+      <c r="J58" s="144"/>
+      <c r="K58" s="144"/>
+      <c r="L58" s="144"/>
+      <c r="M58" s="144"/>
+      <c r="N58" s="144"/>
+      <c r="O58" s="144"/>
+      <c r="P58" s="144"/>
+      <c r="Q58" s="144"/>
+      <c r="R58" s="144"/>
     </row>
     <row r="59" spans="1:18" s="2" customFormat="1" ht="30.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D59" s="36" t="str">
+      <c r="D59" s="132" t="str">
         <f>IF(MOD(D58,1000)=0,"千円単位",IF(MOD(D58,100)=0,"百円単位",IF(MOD(D58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
-      <c r="H59" s="36"/>
-      <c r="I59" s="36" t="str">
+      <c r="E59" s="132"/>
+      <c r="F59" s="132"/>
+      <c r="G59" s="132"/>
+      <c r="H59" s="132"/>
+      <c r="I59" s="132" t="str">
         <f>IF(MOD(I58,1000)=0,"千円単位",IF(MOD(I58,100)=0,"百円単位",IF(MOD(I58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="J59" s="36"/>
-      <c r="K59" s="36"/>
-      <c r="L59" s="36"/>
-      <c r="M59" s="36"/>
-      <c r="N59" s="36" t="str">
+      <c r="J59" s="132"/>
+      <c r="K59" s="132"/>
+      <c r="L59" s="132"/>
+      <c r="M59" s="132"/>
+      <c r="N59" s="132" t="str">
         <f>IF(MOD(N58,1000)=0,"千円単位",IF(MOD(N58,100)=0,"百円単位",IF(MOD(N58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="O59" s="36"/>
-      <c r="P59" s="36"/>
-      <c r="Q59" s="36"/>
-      <c r="R59" s="36"/>
+      <c r="O59" s="132"/>
+      <c r="P59" s="132"/>
+      <c r="Q59" s="132"/>
+      <c r="R59" s="132"/>
     </row>
     <row r="60" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="61" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2918,41 +2931,20 @@
     <row r="67" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="N56:R57"/>
-    <mergeCell ref="D54:H55"/>
-    <mergeCell ref="I54:M55"/>
-    <mergeCell ref="N54:R55"/>
-    <mergeCell ref="A54:C55"/>
-    <mergeCell ref="A56:C57"/>
-    <mergeCell ref="D56:H57"/>
-    <mergeCell ref="I56:M57"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="I51:M52"/>
-    <mergeCell ref="D51:H52"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A22:C28"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:R21"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="O22:R28"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="J33:L34"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="M33:R34"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="I59:M59"/>
+    <mergeCell ref="N59:R59"/>
+    <mergeCell ref="N53:R53"/>
+    <mergeCell ref="N49:R50"/>
+    <mergeCell ref="N51:R52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="I58:M58"/>
+    <mergeCell ref="N58:R58"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="I53:M53"/>
+    <mergeCell ref="I49:M50"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="H45:J45"/>
     <mergeCell ref="A43:C44"/>
@@ -2969,20 +2961,41 @@
     <mergeCell ref="D43:G44"/>
     <mergeCell ref="H43:J44"/>
     <mergeCell ref="D41:G42"/>
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="I59:M59"/>
-    <mergeCell ref="N59:R59"/>
-    <mergeCell ref="N53:R53"/>
-    <mergeCell ref="N49:R50"/>
-    <mergeCell ref="N51:R52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="I58:M58"/>
-    <mergeCell ref="N58:R58"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="I53:M53"/>
-    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="J33:L34"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="M33:R34"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A22:C28"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:R21"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="O22:R28"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="N56:R57"/>
+    <mergeCell ref="D54:H55"/>
+    <mergeCell ref="I54:M55"/>
+    <mergeCell ref="N54:R55"/>
+    <mergeCell ref="A54:C55"/>
+    <mergeCell ref="A56:C57"/>
+    <mergeCell ref="D56:H57"/>
+    <mergeCell ref="I56:M57"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="I51:M52"/>
+    <mergeCell ref="D51:H52"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="D51:R52">
@@ -3026,7 +3039,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D737899-3511-4F7A-96FD-F5F4470F525C}">
-  <dimension ref="B2:N29"/>
+  <dimension ref="B2:N30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="15" width="4.625" customWidth="1"/>
@@ -3036,62 +3049,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="147" t="s">
+      <c r="E2" s="157" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147" t="s">
+      <c r="F2" s="157"/>
+      <c r="G2" s="157" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147" t="s">
+      <c r="H2" s="157"/>
+      <c r="I2" s="157" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147" t="s">
+      <c r="J2" s="157"/>
+      <c r="K2" s="157" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147" t="s">
+      <c r="L2" s="157"/>
+      <c r="M2" s="157" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="147"/>
+      <c r="N2" s="157"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="145"/>
+      <c r="C3" s="154"/>
       <c r="D3" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="145"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="146"/>
-      <c r="I3" s="145"/>
-      <c r="J3" s="145"/>
-      <c r="K3" s="145"/>
-      <c r="L3" s="145"/>
-      <c r="M3" s="145"/>
-      <c r="N3" s="145"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="154"/>
+      <c r="M3" s="154"/>
+      <c r="N3" s="154"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="145"/>
-      <c r="C4" s="145"/>
+      <c r="B4" s="154"/>
+      <c r="C4" s="154"/>
       <c r="D4" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="145"/>
-      <c r="L4" s="145"/>
-      <c r="M4" s="145"/>
-      <c r="N4" s="145"/>
+      <c r="E4" s="154"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="154"/>
+      <c r="I4" s="154"/>
+      <c r="J4" s="154"/>
+      <c r="K4" s="154"/>
+      <c r="L4" s="154"/>
+      <c r="M4" s="154"/>
+      <c r="N4" s="154"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -3134,40 +3147,40 @@
       <c r="N6" s="153"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="145" t="s">
+      <c r="B7" s="154" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="145"/>
+      <c r="C7" s="154"/>
       <c r="D7" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="148"/>
-      <c r="F7" s="149"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="151"/>
-      <c r="I7" s="148"/>
-      <c r="J7" s="149"/>
-      <c r="K7" s="148"/>
-      <c r="L7" s="149"/>
-      <c r="M7" s="148"/>
-      <c r="N7" s="149"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="151"/>
+      <c r="G7" s="155"/>
+      <c r="H7" s="156"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="151"/>
+      <c r="K7" s="150"/>
+      <c r="L7" s="151"/>
+      <c r="M7" s="150"/>
+      <c r="N7" s="151"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="145"/>
-      <c r="C8" s="145"/>
+      <c r="B8" s="154"/>
+      <c r="C8" s="154"/>
       <c r="D8" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="148"/>
-      <c r="F8" s="149"/>
-      <c r="G8" s="148"/>
-      <c r="H8" s="149"/>
-      <c r="I8" s="148"/>
-      <c r="J8" s="149"/>
-      <c r="K8" s="148"/>
-      <c r="L8" s="149"/>
-      <c r="M8" s="148"/>
-      <c r="N8" s="149"/>
+      <c r="E8" s="150"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="150"/>
+      <c r="H8" s="151"/>
+      <c r="I8" s="150"/>
+      <c r="J8" s="151"/>
+      <c r="K8" s="150"/>
+      <c r="L8" s="151"/>
+      <c r="M8" s="150"/>
+      <c r="N8" s="151"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
@@ -3210,40 +3223,40 @@
       <c r="N10" s="153"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="145" t="s">
+      <c r="B11" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="145"/>
+      <c r="C11" s="154"/>
       <c r="D11" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="148"/>
-      <c r="F11" s="149"/>
-      <c r="G11" s="150"/>
-      <c r="H11" s="151"/>
-      <c r="I11" s="148"/>
-      <c r="J11" s="149"/>
-      <c r="K11" s="148"/>
-      <c r="L11" s="149"/>
-      <c r="M11" s="148"/>
-      <c r="N11" s="149"/>
+      <c r="E11" s="150"/>
+      <c r="F11" s="151"/>
+      <c r="G11" s="155"/>
+      <c r="H11" s="156"/>
+      <c r="I11" s="150"/>
+      <c r="J11" s="151"/>
+      <c r="K11" s="150"/>
+      <c r="L11" s="151"/>
+      <c r="M11" s="150"/>
+      <c r="N11" s="151"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="145"/>
-      <c r="C12" s="145"/>
+      <c r="B12" s="154"/>
+      <c r="C12" s="154"/>
       <c r="D12" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="148"/>
-      <c r="F12" s="149"/>
-      <c r="G12" s="148"/>
-      <c r="H12" s="149"/>
-      <c r="I12" s="148"/>
-      <c r="J12" s="149"/>
-      <c r="K12" s="148"/>
-      <c r="L12" s="149"/>
-      <c r="M12" s="148"/>
-      <c r="N12" s="149"/>
+      <c r="E12" s="150"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="150"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="150"/>
+      <c r="J12" s="151"/>
+      <c r="K12" s="150"/>
+      <c r="L12" s="151"/>
+      <c r="M12" s="150"/>
+      <c r="N12" s="151"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
@@ -3301,133 +3314,220 @@
       <c r="N15" s="153"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="145" t="s">
+      <c r="B16" s="154" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="145"/>
+      <c r="C16" s="154"/>
       <c r="D16" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="148"/>
-      <c r="F16" s="149"/>
-      <c r="G16" s="150"/>
-      <c r="H16" s="151"/>
-      <c r="I16" s="148"/>
-      <c r="J16" s="149"/>
-      <c r="K16" s="148"/>
-      <c r="L16" s="149"/>
-      <c r="M16" s="148"/>
-      <c r="N16" s="149"/>
+      <c r="E16" s="150"/>
+      <c r="F16" s="151"/>
+      <c r="G16" s="155"/>
+      <c r="H16" s="156"/>
+      <c r="I16" s="150"/>
+      <c r="J16" s="151"/>
+      <c r="K16" s="150"/>
+      <c r="L16" s="151"/>
+      <c r="M16" s="150"/>
+      <c r="N16" s="151"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="145"/>
-      <c r="C17" s="145"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="154"/>
       <c r="D17" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="148"/>
-      <c r="F17" s="149"/>
-      <c r="G17" s="148"/>
-      <c r="H17" s="149"/>
-      <c r="I17" s="148"/>
-      <c r="J17" s="149"/>
-      <c r="K17" s="148"/>
-      <c r="L17" s="149"/>
-      <c r="M17" s="148"/>
-      <c r="N17" s="149"/>
+      <c r="E17" s="150"/>
+      <c r="F17" s="151"/>
+      <c r="G17" s="150"/>
+      <c r="H17" s="151"/>
+      <c r="I17" s="150"/>
+      <c r="J17" s="151"/>
+      <c r="K17" s="150"/>
+      <c r="L17" s="151"/>
+      <c r="M17" s="150"/>
+      <c r="N17" s="151"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B20" s="154"/>
-      <c r="C20" s="154"/>
-      <c r="D20" s="154"/>
-      <c r="E20" s="154" t="s">
+      <c r="B20" s="147"/>
+      <c r="C20" s="147"/>
+      <c r="D20" s="147"/>
+      <c r="E20" s="147" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="154"/>
+      <c r="F20" s="147"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B21" s="154" t="s">
+      <c r="B21" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="154"/>
-      <c r="D21" s="154"/>
-      <c r="E21" s="155"/>
-      <c r="F21" s="155"/>
+      <c r="C21" s="147"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="148"/>
+      <c r="F21" s="148"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B22" s="154" t="s">
+      <c r="B22" s="147" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="154"/>
-      <c r="D22" s="154"/>
-      <c r="E22" s="155"/>
-      <c r="F22" s="155"/>
+      <c r="C22" s="147"/>
+      <c r="D22" s="147"/>
+      <c r="E22" s="148"/>
+      <c r="F22" s="148"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B23" s="154" t="s">
+      <c r="B23" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="154"/>
-      <c r="D23" s="154"/>
-      <c r="E23" s="155"/>
-      <c r="F23" s="155"/>
+      <c r="C23" s="147"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="148"/>
+      <c r="F23" s="148"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B24" s="154" t="s">
+      <c r="B24" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="154"/>
-      <c r="D24" s="154"/>
-      <c r="E24" s="155"/>
-      <c r="F24" s="155"/>
+      <c r="C24" s="147"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="148"/>
+      <c r="F24" s="148"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B25" s="154" t="s">
+      <c r="B25" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="154"/>
-      <c r="D25" s="154"/>
-      <c r="E25" s="155"/>
-      <c r="F25" s="155"/>
+      <c r="C25" s="147"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="148"/>
+      <c r="F25" s="148"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B26" s="154" t="s">
+      <c r="B26" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="154"/>
-      <c r="D26" s="154"/>
-      <c r="E26" s="155"/>
-      <c r="F26" s="155"/>
+      <c r="C26" s="147"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="148"/>
+      <c r="F26" s="148"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B27" s="154" t="s">
+      <c r="B27" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="154"/>
-      <c r="D27" s="154"/>
-      <c r="E27" s="156"/>
-      <c r="F27" s="156"/>
+      <c r="C27" s="147"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="149"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B28" s="154" t="s">
+      <c r="B28" s="147" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="154"/>
-      <c r="D28" s="154"/>
-      <c r="E28" s="155"/>
-      <c r="F28" s="155"/>
+      <c r="C28" s="147"/>
+      <c r="D28" s="147"/>
+      <c r="E28" s="148"/>
+      <c r="F28" s="148"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B29" s="154" t="s">
+      <c r="B29" s="147" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="154"/>
-      <c r="D29" s="154"/>
-      <c r="E29" s="155"/>
-      <c r="F29" s="155"/>
+      <c r="C29" s="147"/>
+      <c r="D29" s="147"/>
+      <c r="E29" s="148"/>
+      <c r="F29" s="148"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B30" s="147" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="147"/>
+      <c r="D30" s="147"/>
+      <c r="E30" s="148"/>
+      <c r="F30" s="148"/>
     </row>
   </sheetData>
-  <mergeCells count="84">
+  <mergeCells count="86">
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="B26:D26"/>
@@ -3436,82 +3536,6 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.100.1\エルフル事務局\yokoyama\火災見積システム(mitumo)\新mitumo\見積書Excelテンプレート\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBB7D0B-D169-441C-B30D-DF807286D6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8205FDE-FC89-4B6F-8EA1-DA5765B3A235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="49">
   <si>
     <t>御　　見　　積　　書</t>
     <rPh sb="0" eb="1">
@@ -472,6 +472,49 @@
       <t>ネンハラ</t>
     </rPh>
     <rPh sb="4" eb="6">
+      <t>ワリビキ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>消火設備割引</t>
+    <rPh sb="0" eb="4">
+      <t>ショウカセツビ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ワリビキ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>セキュリティ割引</t>
+    <rPh sb="6" eb="8">
+      <t>ワリビキ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>公有物件等割引</t>
+    <rPh sb="0" eb="2">
+      <t>コウユウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブッケン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ワリビキ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>リスク評価割引</t>
+    <rPh sb="3" eb="5">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
       <t>ワリビキ</t>
     </rPh>
     <phoneticPr fontId="19"/>
@@ -1235,74 +1278,202 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1311,24 +1482,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1407,181 +1560,71 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1589,34 +1632,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2020,10 +2063,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="28"/>
@@ -2033,16 +2076,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="124"/>
+      <c r="Q3" s="124"/>
+      <c r="R3" s="124"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="86"/>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="86"/>
-      <c r="R4" s="86"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="124"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="27"/>
@@ -2105,196 +2148,196 @@
       <c r="R10" s="23"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="98"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="98"/>
+      <c r="K11" s="98"/>
+      <c r="L11" s="98"/>
+      <c r="M11" s="98"/>
+      <c r="N11" s="98"/>
+      <c r="O11" s="98"/>
+      <c r="P11" s="98"/>
+      <c r="Q11" s="98"/>
+      <c r="R11" s="98"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="80" t="s">
+      <c r="A15" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="80"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="80"/>
-      <c r="M15" s="80"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="80"/>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="80"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
+      <c r="K15" s="118"/>
+      <c r="L15" s="118"/>
+      <c r="M15" s="118"/>
+      <c r="N15" s="118"/>
+      <c r="O15" s="118"/>
+      <c r="P15" s="118"/>
+      <c r="Q15" s="118"/>
+      <c r="R15" s="118"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="81" t="s">
+      <c r="A18" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
-      <c r="M18" s="81"/>
-      <c r="N18" s="81"/>
-      <c r="O18" s="81"/>
-      <c r="P18" s="81"/>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="81"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="119"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="119"/>
+      <c r="K18" s="119"/>
+      <c r="L18" s="119"/>
+      <c r="M18" s="119"/>
+      <c r="N18" s="119"/>
+      <c r="O18" s="119"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="62"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="62"/>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="62"/>
-      <c r="R20" s="63"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="100"/>
+      <c r="N20" s="100"/>
+      <c r="O20" s="100"/>
+      <c r="P20" s="100"/>
+      <c r="Q20" s="100"/>
+      <c r="R20" s="101"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="55"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="65"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="65"/>
-      <c r="M21" s="65"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="65"/>
-      <c r="P21" s="65"/>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="66"/>
+      <c r="A21" s="82"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="103"/>
+      <c r="J21" s="103"/>
+      <c r="K21" s="103"/>
+      <c r="L21" s="103"/>
+      <c r="M21" s="103"/>
+      <c r="N21" s="103"/>
+      <c r="O21" s="103"/>
+      <c r="P21" s="103"/>
+      <c r="Q21" s="103"/>
+      <c r="R21" s="104"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="56"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
       <c r="D22" s="22"/>
       <c r="L22" s="21"/>
-      <c r="M22" s="67" t="s">
+      <c r="M22" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="68"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="72"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="73"/>
+      <c r="N22" s="106"/>
+      <c r="O22" s="109"/>
+      <c r="P22" s="110"/>
+      <c r="Q22" s="110"/>
+      <c r="R22" s="111"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="55"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="74"/>
-      <c r="P23" s="75"/>
-      <c r="Q23" s="75"/>
-      <c r="R23" s="76"/>
+      <c r="A23" s="82"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="121"/>
+      <c r="H23" s="121"/>
+      <c r="I23" s="121"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="121"/>
+      <c r="L23" s="122"/>
+      <c r="M23" s="105"/>
+      <c r="N23" s="106"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="113"/>
+      <c r="Q23" s="113"/>
+      <c r="R23" s="114"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="55"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="85"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="67"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="74"/>
-      <c r="P24" s="75"/>
-      <c r="Q24" s="75"/>
-      <c r="R24" s="76"/>
+      <c r="A24" s="82"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="121"/>
+      <c r="H24" s="121"/>
+      <c r="I24" s="121"/>
+      <c r="J24" s="121"/>
+      <c r="K24" s="121"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="105"/>
+      <c r="N24" s="106"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="113"/>
+      <c r="Q24" s="113"/>
+      <c r="R24" s="114"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="55"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="85"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="83"/>
-      <c r="L25" s="84"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="74"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="76"/>
+      <c r="A25" s="82"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="63"/>
+      <c r="D25" s="123"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="121"/>
+      <c r="H25" s="121"/>
+      <c r="I25" s="121"/>
+      <c r="J25" s="121"/>
+      <c r="K25" s="121"/>
+      <c r="L25" s="122"/>
+      <c r="M25" s="105"/>
+      <c r="N25" s="106"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="113"/>
+      <c r="Q25" s="113"/>
+      <c r="R25" s="114"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="55"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
+      <c r="A26" s="82"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="63"/>
       <c r="D26" s="20"/>
       <c r="E26" s="19"/>
       <c r="F26" s="18"/>
@@ -2304,17 +2347,17 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="16"/>
-      <c r="M26" s="67"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="75"/>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="76"/>
+      <c r="M26" s="105"/>
+      <c r="N26" s="106"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="113"/>
+      <c r="Q26" s="113"/>
+      <c r="R26" s="114"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="55"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="56"/>
+      <c r="A27" s="82"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="63"/>
       <c r="D27" s="15"/>
       <c r="F27" s="13"/>
       <c r="G27" s="14"/>
@@ -2322,17 +2365,17 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="L27" s="11"/>
-      <c r="M27" s="67"/>
-      <c r="N27" s="68"/>
-      <c r="O27" s="74"/>
-      <c r="P27" s="75"/>
-      <c r="Q27" s="75"/>
-      <c r="R27" s="76"/>
+      <c r="M27" s="105"/>
+      <c r="N27" s="106"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="113"/>
+      <c r="Q27" s="113"/>
+      <c r="R27" s="114"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="57"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
+      <c r="A28" s="89"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
       <c r="D28" s="10"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -2342,346 +2385,346 @@
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="8"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="70"/>
-      <c r="O28" s="77"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="78"/>
-      <c r="R28" s="79"/>
+      <c r="M28" s="107"/>
+      <c r="N28" s="108"/>
+      <c r="O28" s="115"/>
+      <c r="P28" s="116"/>
+      <c r="Q28" s="116"/>
+      <c r="R28" s="117"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="59" t="s">
+      <c r="A31" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="60"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="92"/>
-      <c r="H31" s="92"/>
-      <c r="I31" s="92"/>
-      <c r="J31" s="60" t="s">
+      <c r="B31" s="61"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="86"/>
+      <c r="F31" s="86"/>
+      <c r="G31" s="86"/>
+      <c r="H31" s="86"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="60"/>
-      <c r="L31" s="60"/>
-      <c r="M31" s="92"/>
-      <c r="N31" s="92"/>
-      <c r="O31" s="92"/>
-      <c r="P31" s="92"/>
-      <c r="Q31" s="92"/>
-      <c r="R31" s="93"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="86"/>
+      <c r="N31" s="86"/>
+      <c r="O31" s="86"/>
+      <c r="P31" s="86"/>
+      <c r="Q31" s="86"/>
+      <c r="R31" s="87"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="55"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="94"/>
-      <c r="E32" s="94"/>
-      <c r="F32" s="94"/>
-      <c r="G32" s="94"/>
-      <c r="H32" s="94"/>
-      <c r="I32" s="94"/>
-      <c r="J32" s="56"/>
-      <c r="K32" s="56"/>
-      <c r="L32" s="56"/>
-      <c r="M32" s="94"/>
-      <c r="N32" s="94"/>
-      <c r="O32" s="94"/>
-      <c r="P32" s="94"/>
-      <c r="Q32" s="94"/>
-      <c r="R32" s="95"/>
+      <c r="A32" s="82"/>
+      <c r="B32" s="63"/>
+      <c r="C32" s="63"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="63"/>
+      <c r="K32" s="63"/>
+      <c r="L32" s="63"/>
+      <c r="M32" s="60"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="60"/>
+      <c r="R32" s="88"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="94"/>
-      <c r="E33" s="94"/>
-      <c r="F33" s="94"/>
-      <c r="G33" s="94"/>
-      <c r="H33" s="94"/>
-      <c r="I33" s="94"/>
-      <c r="J33" s="56" t="s">
+      <c r="B33" s="63"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="60"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="60"/>
+      <c r="H33" s="60"/>
+      <c r="I33" s="60"/>
+      <c r="J33" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="K33" s="56"/>
-      <c r="L33" s="56"/>
-      <c r="M33" s="94"/>
-      <c r="N33" s="94"/>
-      <c r="O33" s="94"/>
-      <c r="P33" s="94"/>
-      <c r="Q33" s="94"/>
-      <c r="R33" s="95"/>
+      <c r="K33" s="63"/>
+      <c r="L33" s="63"/>
+      <c r="M33" s="60"/>
+      <c r="N33" s="60"/>
+      <c r="O33" s="60"/>
+      <c r="P33" s="60"/>
+      <c r="Q33" s="60"/>
+      <c r="R33" s="88"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="55"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="94"/>
-      <c r="E34" s="94"/>
-      <c r="F34" s="94"/>
-      <c r="G34" s="94"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="94"/>
-      <c r="J34" s="56"/>
-      <c r="K34" s="56"/>
-      <c r="L34" s="56"/>
-      <c r="M34" s="94"/>
-      <c r="N34" s="94"/>
-      <c r="O34" s="94"/>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="95"/>
+      <c r="A34" s="82"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="63"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="63"/>
+      <c r="K34" s="63"/>
+      <c r="L34" s="63"/>
+      <c r="M34" s="60"/>
+      <c r="N34" s="60"/>
+      <c r="O34" s="60"/>
+      <c r="P34" s="60"/>
+      <c r="Q34" s="60"/>
+      <c r="R34" s="88"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="55" t="s">
+      <c r="A35" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="97"/>
-      <c r="F35" s="97"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="97"/>
-      <c r="I35" s="97"/>
-      <c r="J35" s="97"/>
-      <c r="K35" s="97"/>
-      <c r="L35" s="97"/>
-      <c r="M35" s="97"/>
-      <c r="N35" s="97"/>
-      <c r="O35" s="97"/>
-      <c r="P35" s="97"/>
-      <c r="Q35" s="97"/>
-      <c r="R35" s="98"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="91"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="92"/>
+      <c r="H35" s="92"/>
+      <c r="I35" s="92"/>
+      <c r="J35" s="92"/>
+      <c r="K35" s="92"/>
+      <c r="L35" s="92"/>
+      <c r="M35" s="92"/>
+      <c r="N35" s="92"/>
+      <c r="O35" s="92"/>
+      <c r="P35" s="92"/>
+      <c r="Q35" s="92"/>
+      <c r="R35" s="93"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="57"/>
-      <c r="B36" s="58"/>
-      <c r="C36" s="58"/>
-      <c r="D36" s="99"/>
-      <c r="E36" s="100"/>
-      <c r="F36" s="100"/>
-      <c r="G36" s="100"/>
-      <c r="H36" s="100"/>
-      <c r="I36" s="100"/>
-      <c r="J36" s="100"/>
-      <c r="K36" s="100"/>
-      <c r="L36" s="100"/>
-      <c r="M36" s="100"/>
-      <c r="N36" s="100"/>
-      <c r="O36" s="100"/>
-      <c r="P36" s="100"/>
-      <c r="Q36" s="100"/>
-      <c r="R36" s="101"/>
+      <c r="A36" s="89"/>
+      <c r="B36" s="90"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="94"/>
+      <c r="E36" s="95"/>
+      <c r="F36" s="95"/>
+      <c r="G36" s="95"/>
+      <c r="H36" s="95"/>
+      <c r="I36" s="95"/>
+      <c r="J36" s="95"/>
+      <c r="K36" s="95"/>
+      <c r="L36" s="95"/>
+      <c r="M36" s="95"/>
+      <c r="N36" s="95"/>
+      <c r="O36" s="95"/>
+      <c r="P36" s="95"/>
+      <c r="Q36" s="95"/>
+      <c r="R36" s="96"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="87"/>
-      <c r="B37" s="88"/>
-      <c r="C37" s="88"/>
-      <c r="D37" s="88"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="88"/>
-      <c r="H37" s="88"/>
-      <c r="I37" s="88"/>
-      <c r="J37" s="88"/>
-      <c r="K37" s="88"/>
-      <c r="L37" s="88"/>
-      <c r="M37" s="88"/>
-      <c r="N37" s="88"/>
-      <c r="O37" s="88"/>
-      <c r="P37" s="88"/>
-      <c r="Q37" s="88"/>
-      <c r="R37" s="88"/>
+      <c r="A37" s="83"/>
+      <c r="B37" s="84"/>
+      <c r="C37" s="84"/>
+      <c r="D37" s="84"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="84"/>
+      <c r="I37" s="84"/>
+      <c r="J37" s="84"/>
+      <c r="K37" s="84"/>
+      <c r="L37" s="84"/>
+      <c r="M37" s="84"/>
+      <c r="N37" s="84"/>
+      <c r="O37" s="84"/>
+      <c r="P37" s="84"/>
+      <c r="Q37" s="84"/>
+      <c r="R37" s="84"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="89"/>
-      <c r="B38" s="89"/>
-      <c r="C38" s="89"/>
-      <c r="D38" s="89"/>
-      <c r="E38" s="89"/>
-      <c r="F38" s="89"/>
-      <c r="G38" s="89"/>
-      <c r="H38" s="89"/>
-      <c r="I38" s="89"/>
-      <c r="J38" s="89"/>
-      <c r="K38" s="89"/>
-      <c r="L38" s="89"/>
-      <c r="M38" s="89"/>
-      <c r="N38" s="89"/>
-      <c r="O38" s="89"/>
-      <c r="P38" s="89"/>
-      <c r="Q38" s="89"/>
-      <c r="R38" s="89"/>
+      <c r="A38" s="85"/>
+      <c r="B38" s="85"/>
+      <c r="C38" s="85"/>
+      <c r="D38" s="85"/>
+      <c r="E38" s="85"/>
+      <c r="F38" s="85"/>
+      <c r="G38" s="85"/>
+      <c r="H38" s="85"/>
+      <c r="I38" s="85"/>
+      <c r="J38" s="85"/>
+      <c r="K38" s="85"/>
+      <c r="L38" s="85"/>
+      <c r="M38" s="85"/>
+      <c r="N38" s="85"/>
+      <c r="O38" s="85"/>
+      <c r="P38" s="85"/>
+      <c r="Q38" s="85"/>
+      <c r="R38" s="85"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="59" t="s">
+      <c r="A39" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="60"/>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60" t="s">
+      <c r="B39" s="61"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="90"/>
-      <c r="H39" s="60" t="s">
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="I39" s="60"/>
-      <c r="J39" s="60"/>
-      <c r="K39" s="60" t="s">
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="L39" s="60"/>
-      <c r="M39" s="60"/>
-      <c r="N39" s="90"/>
-      <c r="O39" s="60" t="s">
+      <c r="L39" s="61"/>
+      <c r="M39" s="61"/>
+      <c r="N39" s="75"/>
+      <c r="O39" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="P39" s="60"/>
-      <c r="Q39" s="60"/>
-      <c r="R39" s="110"/>
+      <c r="P39" s="61"/>
+      <c r="Q39" s="61"/>
+      <c r="R39" s="62"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="55"/>
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="56"/>
-      <c r="K40" s="56"/>
-      <c r="L40" s="56"/>
-      <c r="M40" s="56"/>
-      <c r="N40" s="91"/>
-      <c r="O40" s="56"/>
-      <c r="P40" s="56"/>
-      <c r="Q40" s="56"/>
-      <c r="R40" s="111"/>
+      <c r="A40" s="82"/>
+      <c r="B40" s="63"/>
+      <c r="C40" s="63"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="63"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="63"/>
+      <c r="K40" s="63"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="76"/>
+      <c r="O40" s="63"/>
+      <c r="P40" s="63"/>
+      <c r="Q40" s="63"/>
+      <c r="R40" s="64"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="104" t="s">
+      <c r="A41" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="105"/>
-      <c r="C41" s="106"/>
-      <c r="D41" s="112"/>
-      <c r="E41" s="113"/>
-      <c r="F41" s="113"/>
-      <c r="G41" s="114"/>
-      <c r="H41" s="126" t="s">
+      <c r="B41" s="55"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="127"/>
-      <c r="J41" s="128"/>
-      <c r="K41" s="112"/>
-      <c r="L41" s="113"/>
-      <c r="M41" s="113"/>
-      <c r="N41" s="114"/>
-      <c r="O41" s="118"/>
-      <c r="P41" s="118"/>
-      <c r="Q41" s="118"/>
-      <c r="R41" s="119"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="65"/>
+      <c r="L41" s="66"/>
+      <c r="M41" s="66"/>
+      <c r="N41" s="67"/>
+      <c r="O41" s="71"/>
+      <c r="P41" s="71"/>
+      <c r="Q41" s="71"/>
+      <c r="R41" s="72"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="107"/>
-      <c r="B42" s="108"/>
-      <c r="C42" s="109"/>
-      <c r="D42" s="115"/>
-      <c r="E42" s="116"/>
-      <c r="F42" s="116"/>
-      <c r="G42" s="117"/>
-      <c r="H42" s="129"/>
-      <c r="I42" s="130"/>
-      <c r="J42" s="131"/>
-      <c r="K42" s="115"/>
-      <c r="L42" s="116"/>
-      <c r="M42" s="116"/>
-      <c r="N42" s="117"/>
-      <c r="O42" s="118"/>
-      <c r="P42" s="118"/>
-      <c r="Q42" s="118"/>
-      <c r="R42" s="119"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="58"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="69"/>
+      <c r="F42" s="69"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="68"/>
+      <c r="L42" s="69"/>
+      <c r="M42" s="69"/>
+      <c r="N42" s="70"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="104" t="s">
+      <c r="A43" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="105"/>
-      <c r="C43" s="106"/>
-      <c r="D43" s="112"/>
-      <c r="E43" s="113"/>
-      <c r="F43" s="113"/>
-      <c r="G43" s="114"/>
-      <c r="H43" s="124" t="s">
+      <c r="B43" s="55"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="67"/>
+      <c r="H43" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="105"/>
-      <c r="J43" s="106"/>
-      <c r="K43" s="112"/>
-      <c r="L43" s="113"/>
-      <c r="M43" s="113"/>
-      <c r="N43" s="114"/>
-      <c r="O43" s="118"/>
-      <c r="P43" s="118"/>
-      <c r="Q43" s="118"/>
-      <c r="R43" s="119"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="56"/>
+      <c r="K43" s="65"/>
+      <c r="L43" s="66"/>
+      <c r="M43" s="66"/>
+      <c r="N43" s="67"/>
+      <c r="O43" s="71"/>
+      <c r="P43" s="71"/>
+      <c r="Q43" s="71"/>
+      <c r="R43" s="72"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="107"/>
-      <c r="B44" s="108"/>
-      <c r="C44" s="109"/>
-      <c r="D44" s="115"/>
-      <c r="E44" s="116"/>
-      <c r="F44" s="116"/>
-      <c r="G44" s="117"/>
-      <c r="H44" s="125"/>
-      <c r="I44" s="108"/>
-      <c r="J44" s="109"/>
-      <c r="K44" s="115"/>
-      <c r="L44" s="116"/>
-      <c r="M44" s="116"/>
-      <c r="N44" s="117"/>
-      <c r="O44" s="118"/>
-      <c r="P44" s="118"/>
-      <c r="Q44" s="118"/>
-      <c r="R44" s="119"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="58"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="80"/>
+      <c r="I44" s="58"/>
+      <c r="J44" s="59"/>
+      <c r="K44" s="68"/>
+      <c r="L44" s="69"/>
+      <c r="M44" s="69"/>
+      <c r="N44" s="70"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="102" t="s">
+      <c r="A45" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="103"/>
-      <c r="C45" s="103"/>
-      <c r="D45" s="122"/>
-      <c r="E45" s="122"/>
-      <c r="F45" s="122"/>
-      <c r="G45" s="123"/>
-      <c r="H45" s="103" t="s">
+      <c r="B45" s="53"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="77"/>
+      <c r="F45" s="77"/>
+      <c r="G45" s="78"/>
+      <c r="H45" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="103"/>
-      <c r="J45" s="103"/>
-      <c r="K45" s="122"/>
-      <c r="L45" s="122"/>
-      <c r="M45" s="122"/>
-      <c r="N45" s="123"/>
-      <c r="O45" s="120"/>
-      <c r="P45" s="120"/>
-      <c r="Q45" s="120"/>
-      <c r="R45" s="121"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="77"/>
+      <c r="L45" s="77"/>
+      <c r="M45" s="77"/>
+      <c r="N45" s="78"/>
+      <c r="O45" s="73"/>
+      <c r="P45" s="73"/>
+      <c r="Q45" s="73"/>
+      <c r="R45" s="74"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2693,233 +2736,233 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="30"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="136"/>
-      <c r="E49" s="137"/>
-      <c r="F49" s="137"/>
-      <c r="G49" s="137"/>
-      <c r="H49" s="145"/>
-      <c r="I49" s="136"/>
-      <c r="J49" s="137"/>
-      <c r="K49" s="137"/>
-      <c r="L49" s="137"/>
-      <c r="M49" s="145"/>
-      <c r="N49" s="136"/>
-      <c r="O49" s="137"/>
-      <c r="P49" s="137"/>
-      <c r="Q49" s="137"/>
-      <c r="R49" s="138"/>
+      <c r="A49" s="125"/>
+      <c r="B49" s="126"/>
+      <c r="C49" s="127"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="50"/>
+      <c r="I49" s="40"/>
+      <c r="J49" s="41"/>
+      <c r="K49" s="41"/>
+      <c r="L49" s="41"/>
+      <c r="M49" s="50"/>
+      <c r="N49" s="40"/>
+      <c r="O49" s="41"/>
+      <c r="P49" s="41"/>
+      <c r="Q49" s="41"/>
+      <c r="R49" s="42"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="33"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="35"/>
-      <c r="D50" s="139"/>
-      <c r="E50" s="140"/>
-      <c r="F50" s="140"/>
-      <c r="G50" s="140"/>
-      <c r="H50" s="146"/>
-      <c r="I50" s="139"/>
-      <c r="J50" s="140"/>
-      <c r="K50" s="140"/>
-      <c r="L50" s="140"/>
-      <c r="M50" s="146"/>
-      <c r="N50" s="139"/>
-      <c r="O50" s="140"/>
-      <c r="P50" s="140"/>
-      <c r="Q50" s="140"/>
-      <c r="R50" s="141"/>
+      <c r="A50" s="128"/>
+      <c r="B50" s="129"/>
+      <c r="C50" s="130"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="51"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44"/>
+      <c r="L50" s="44"/>
+      <c r="M50" s="51"/>
+      <c r="N50" s="43"/>
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="45"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="46" t="s">
+      <c r="A51" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="47"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
-      <c r="G51" s="52"/>
-      <c r="H51" s="52"/>
-      <c r="I51" s="52"/>
-      <c r="J51" s="52"/>
-      <c r="K51" s="52"/>
-      <c r="L51" s="52"/>
-      <c r="M51" s="52"/>
-      <c r="N51" s="52"/>
-      <c r="O51" s="52"/>
-      <c r="P51" s="52"/>
-      <c r="Q51" s="52"/>
-      <c r="R51" s="142"/>
+      <c r="B51" s="142"/>
+      <c r="C51" s="143"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="46"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="46"/>
+      <c r="I51" s="46"/>
+      <c r="J51" s="46"/>
+      <c r="K51" s="46"/>
+      <c r="L51" s="46"/>
+      <c r="M51" s="46"/>
+      <c r="N51" s="46"/>
+      <c r="O51" s="46"/>
+      <c r="P51" s="46"/>
+      <c r="Q51" s="46"/>
+      <c r="R51" s="47"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="49"/>
-      <c r="B52" s="50"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
-      <c r="H52" s="52"/>
-      <c r="I52" s="52"/>
-      <c r="J52" s="52"/>
-      <c r="K52" s="52"/>
-      <c r="L52" s="52"/>
-      <c r="M52" s="52"/>
-      <c r="N52" s="52"/>
-      <c r="O52" s="52"/>
-      <c r="P52" s="52"/>
-      <c r="Q52" s="52"/>
-      <c r="R52" s="142"/>
+      <c r="A52" s="144"/>
+      <c r="B52" s="145"/>
+      <c r="C52" s="146"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="46"/>
+      <c r="I52" s="46"/>
+      <c r="J52" s="46"/>
+      <c r="K52" s="46"/>
+      <c r="L52" s="46"/>
+      <c r="M52" s="46"/>
+      <c r="N52" s="46"/>
+      <c r="O52" s="46"/>
+      <c r="P52" s="46"/>
+      <c r="Q52" s="46"/>
+      <c r="R52" s="47"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
       <c r="B53" s="4"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="133"/>
-      <c r="E53" s="134"/>
-      <c r="F53" s="134"/>
-      <c r="G53" s="134"/>
-      <c r="H53" s="143"/>
-      <c r="I53" s="133"/>
-      <c r="J53" s="134"/>
-      <c r="K53" s="134"/>
-      <c r="L53" s="134"/>
-      <c r="M53" s="143"/>
-      <c r="N53" s="133"/>
-      <c r="O53" s="134"/>
-      <c r="P53" s="134"/>
-      <c r="Q53" s="134"/>
-      <c r="R53" s="135"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="37"/>
+      <c r="J53" s="38"/>
+      <c r="K53" s="38"/>
+      <c r="L53" s="38"/>
+      <c r="M53" s="48"/>
+      <c r="N53" s="37"/>
+      <c r="O53" s="38"/>
+      <c r="P53" s="38"/>
+      <c r="Q53" s="38"/>
+      <c r="R53" s="39"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="40" t="s">
+      <c r="A54" s="135" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="41"/>
-      <c r="C54" s="42"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="36"/>
-      <c r="I54" s="36"/>
-      <c r="J54" s="36"/>
-      <c r="K54" s="36"/>
-      <c r="L54" s="36"/>
-      <c r="M54" s="36"/>
-      <c r="N54" s="36"/>
-      <c r="O54" s="36"/>
-      <c r="P54" s="36"/>
-      <c r="Q54" s="36"/>
-      <c r="R54" s="37"/>
+      <c r="B54" s="136"/>
+      <c r="C54" s="137"/>
+      <c r="D54" s="131"/>
+      <c r="E54" s="131"/>
+      <c r="F54" s="131"/>
+      <c r="G54" s="131"/>
+      <c r="H54" s="131"/>
+      <c r="I54" s="131"/>
+      <c r="J54" s="131"/>
+      <c r="K54" s="131"/>
+      <c r="L54" s="131"/>
+      <c r="M54" s="131"/>
+      <c r="N54" s="131"/>
+      <c r="O54" s="131"/>
+      <c r="P54" s="131"/>
+      <c r="Q54" s="131"/>
+      <c r="R54" s="132"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="43"/>
-      <c r="B55" s="44"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="38"/>
-      <c r="I55" s="38"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="38"/>
-      <c r="L55" s="38"/>
-      <c r="M55" s="38"/>
-      <c r="N55" s="38"/>
-      <c r="O55" s="38"/>
-      <c r="P55" s="38"/>
-      <c r="Q55" s="38"/>
-      <c r="R55" s="39"/>
+      <c r="A55" s="138"/>
+      <c r="B55" s="139"/>
+      <c r="C55" s="140"/>
+      <c r="D55" s="133"/>
+      <c r="E55" s="133"/>
+      <c r="F55" s="133"/>
+      <c r="G55" s="133"/>
+      <c r="H55" s="133"/>
+      <c r="I55" s="133"/>
+      <c r="J55" s="133"/>
+      <c r="K55" s="133"/>
+      <c r="L55" s="133"/>
+      <c r="M55" s="133"/>
+      <c r="N55" s="133"/>
+      <c r="O55" s="133"/>
+      <c r="P55" s="133"/>
+      <c r="Q55" s="133"/>
+      <c r="R55" s="134"/>
     </row>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="40" t="s">
+      <c r="A56" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="B56" s="41"/>
-      <c r="C56" s="42"/>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
-      <c r="H56" s="36"/>
-      <c r="I56" s="36"/>
-      <c r="J56" s="36"/>
-      <c r="K56" s="36"/>
-      <c r="L56" s="36"/>
-      <c r="M56" s="36"/>
-      <c r="N56" s="36"/>
-      <c r="O56" s="36"/>
-      <c r="P56" s="36"/>
-      <c r="Q56" s="36"/>
-      <c r="R56" s="37"/>
+      <c r="B56" s="136"/>
+      <c r="C56" s="137"/>
+      <c r="D56" s="131"/>
+      <c r="E56" s="131"/>
+      <c r="F56" s="131"/>
+      <c r="G56" s="131"/>
+      <c r="H56" s="131"/>
+      <c r="I56" s="131"/>
+      <c r="J56" s="131"/>
+      <c r="K56" s="131"/>
+      <c r="L56" s="131"/>
+      <c r="M56" s="131"/>
+      <c r="N56" s="131"/>
+      <c r="O56" s="131"/>
+      <c r="P56" s="131"/>
+      <c r="Q56" s="131"/>
+      <c r="R56" s="132"/>
     </row>
     <row r="57" spans="1:18" s="2" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="43"/>
-      <c r="B57" s="44"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="38"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="38"/>
-      <c r="L57" s="38"/>
-      <c r="M57" s="38"/>
-      <c r="N57" s="38"/>
-      <c r="O57" s="38"/>
-      <c r="P57" s="38"/>
-      <c r="Q57" s="38"/>
-      <c r="R57" s="39"/>
+      <c r="A57" s="138"/>
+      <c r="B57" s="139"/>
+      <c r="C57" s="140"/>
+      <c r="D57" s="133"/>
+      <c r="E57" s="133"/>
+      <c r="F57" s="133"/>
+      <c r="G57" s="133"/>
+      <c r="H57" s="133"/>
+      <c r="I57" s="133"/>
+      <c r="J57" s="133"/>
+      <c r="K57" s="133"/>
+      <c r="L57" s="133"/>
+      <c r="M57" s="133"/>
+      <c r="N57" s="133"/>
+      <c r="O57" s="133"/>
+      <c r="P57" s="133"/>
+      <c r="Q57" s="133"/>
+      <c r="R57" s="134"/>
     </row>
     <row r="58" spans="1:18" s="2" customFormat="1" ht="27" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D58" s="144"/>
-      <c r="E58" s="144"/>
-      <c r="F58" s="144"/>
-      <c r="G58" s="144"/>
-      <c r="H58" s="144"/>
-      <c r="I58" s="144"/>
-      <c r="J58" s="144"/>
-      <c r="K58" s="144"/>
-      <c r="L58" s="144"/>
-      <c r="M58" s="144"/>
-      <c r="N58" s="144"/>
-      <c r="O58" s="144"/>
-      <c r="P58" s="144"/>
-      <c r="Q58" s="144"/>
-      <c r="R58" s="144"/>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="49"/>
+      <c r="J58" s="49"/>
+      <c r="K58" s="49"/>
+      <c r="L58" s="49"/>
+      <c r="M58" s="49"/>
+      <c r="N58" s="49"/>
+      <c r="O58" s="49"/>
+      <c r="P58" s="49"/>
+      <c r="Q58" s="49"/>
+      <c r="R58" s="49"/>
     </row>
     <row r="59" spans="1:18" s="2" customFormat="1" ht="30.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D59" s="132" t="str">
+      <c r="D59" s="36" t="str">
         <f>IF(MOD(D58,1000)=0,"千円単位",IF(MOD(D58,100)=0,"百円単位",IF(MOD(D58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="E59" s="132"/>
-      <c r="F59" s="132"/>
-      <c r="G59" s="132"/>
-      <c r="H59" s="132"/>
-      <c r="I59" s="132" t="str">
+      <c r="E59" s="36"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="36" t="str">
         <f>IF(MOD(I58,1000)=0,"千円単位",IF(MOD(I58,100)=0,"百円単位",IF(MOD(I58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="J59" s="132"/>
-      <c r="K59" s="132"/>
-      <c r="L59" s="132"/>
-      <c r="M59" s="132"/>
-      <c r="N59" s="132" t="str">
+      <c r="J59" s="36"/>
+      <c r="K59" s="36"/>
+      <c r="L59" s="36"/>
+      <c r="M59" s="36"/>
+      <c r="N59" s="36" t="str">
         <f>IF(MOD(N58,1000)=0,"千円単位",IF(MOD(N58,100)=0,"百円単位",IF(MOD(N58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="O59" s="132"/>
-      <c r="P59" s="132"/>
-      <c r="Q59" s="132"/>
-      <c r="R59" s="132"/>
+      <c r="O59" s="36"/>
+      <c r="P59" s="36"/>
+      <c r="Q59" s="36"/>
+      <c r="R59" s="36"/>
     </row>
     <row r="60" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="61" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2931,20 +2974,41 @@
     <row r="67" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="I59:M59"/>
-    <mergeCell ref="N59:R59"/>
-    <mergeCell ref="N53:R53"/>
-    <mergeCell ref="N49:R50"/>
-    <mergeCell ref="N51:R52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="I58:M58"/>
-    <mergeCell ref="N58:R58"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="I53:M53"/>
-    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="N56:R57"/>
+    <mergeCell ref="D54:H55"/>
+    <mergeCell ref="I54:M55"/>
+    <mergeCell ref="N54:R55"/>
+    <mergeCell ref="A54:C55"/>
+    <mergeCell ref="A56:C57"/>
+    <mergeCell ref="D56:H57"/>
+    <mergeCell ref="I56:M57"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="I51:M52"/>
+    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A22:C28"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:R21"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="O22:R28"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="J33:L34"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="M33:R34"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="D31:I32"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="H45:J45"/>
     <mergeCell ref="A43:C44"/>
@@ -2961,41 +3025,20 @@
     <mergeCell ref="D43:G44"/>
     <mergeCell ref="H43:J44"/>
     <mergeCell ref="D41:G42"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="J33:L34"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="M33:R34"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="D31:I32"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A22:C28"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:R21"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="O22:R28"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="N56:R57"/>
-    <mergeCell ref="D54:H55"/>
-    <mergeCell ref="I54:M55"/>
-    <mergeCell ref="N54:R55"/>
-    <mergeCell ref="A54:C55"/>
-    <mergeCell ref="A56:C57"/>
-    <mergeCell ref="D56:H57"/>
-    <mergeCell ref="I56:M57"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="I51:M52"/>
-    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="I59:M59"/>
+    <mergeCell ref="N59:R59"/>
+    <mergeCell ref="N53:R53"/>
+    <mergeCell ref="N49:R50"/>
+    <mergeCell ref="N51:R52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="I58:M58"/>
+    <mergeCell ref="N58:R58"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="I53:M53"/>
+    <mergeCell ref="I49:M50"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="D51:R52">
@@ -3049,62 +3092,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="157" t="s">
+      <c r="E2" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157" t="s">
+      <c r="F2" s="151"/>
+      <c r="G2" s="151" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157" t="s">
+      <c r="H2" s="151"/>
+      <c r="I2" s="151" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157" t="s">
+      <c r="J2" s="151"/>
+      <c r="K2" s="151" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157" t="s">
+      <c r="L2" s="151"/>
+      <c r="M2" s="151" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="157"/>
+      <c r="N2" s="151"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="154" t="s">
+      <c r="B3" s="149" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="154"/>
+      <c r="C3" s="149"/>
       <c r="D3" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="154"/>
-      <c r="F3" s="154"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="154"/>
-      <c r="J3" s="154"/>
-      <c r="K3" s="154"/>
-      <c r="L3" s="154"/>
-      <c r="M3" s="154"/>
-      <c r="N3" s="154"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="149"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
+      <c r="K3" s="149"/>
+      <c r="L3" s="149"/>
+      <c r="M3" s="149"/>
+      <c r="N3" s="149"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="154"/>
-      <c r="C4" s="154"/>
+      <c r="B4" s="149"/>
+      <c r="C4" s="149"/>
       <c r="D4" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="154"/>
-      <c r="F4" s="154"/>
-      <c r="G4" s="154"/>
-      <c r="H4" s="154"/>
-      <c r="I4" s="154"/>
-      <c r="J4" s="154"/>
-      <c r="K4" s="154"/>
-      <c r="L4" s="154"/>
-      <c r="M4" s="154"/>
-      <c r="N4" s="154"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="149"/>
+      <c r="N4" s="149"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -3125,62 +3168,62 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="152" t="s">
+      <c r="E6" s="156" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="153"/>
-      <c r="G6" s="152" t="s">
+      <c r="F6" s="157"/>
+      <c r="G6" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="153"/>
-      <c r="I6" s="152" t="s">
+      <c r="H6" s="157"/>
+      <c r="I6" s="156" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="153"/>
-      <c r="K6" s="152" t="s">
+      <c r="J6" s="157"/>
+      <c r="K6" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="153"/>
-      <c r="M6" s="152" t="s">
+      <c r="L6" s="157"/>
+      <c r="M6" s="156" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="153"/>
+      <c r="N6" s="157"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="154" t="s">
+      <c r="B7" s="149" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="154"/>
+      <c r="C7" s="149"/>
       <c r="D7" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="150"/>
-      <c r="F7" s="151"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="156"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="151"/>
-      <c r="K7" s="150"/>
-      <c r="L7" s="151"/>
-      <c r="M7" s="150"/>
-      <c r="N7" s="151"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="154"/>
+      <c r="H7" s="155"/>
+      <c r="I7" s="152"/>
+      <c r="J7" s="153"/>
+      <c r="K7" s="152"/>
+      <c r="L7" s="153"/>
+      <c r="M7" s="152"/>
+      <c r="N7" s="153"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="154"/>
-      <c r="C8" s="154"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="149"/>
       <c r="D8" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="150"/>
-      <c r="F8" s="151"/>
-      <c r="G8" s="150"/>
-      <c r="H8" s="151"/>
-      <c r="I8" s="150"/>
-      <c r="J8" s="151"/>
-      <c r="K8" s="150"/>
-      <c r="L8" s="151"/>
-      <c r="M8" s="150"/>
-      <c r="N8" s="151"/>
+      <c r="E8" s="152"/>
+      <c r="F8" s="153"/>
+      <c r="G8" s="152"/>
+      <c r="H8" s="153"/>
+      <c r="I8" s="152"/>
+      <c r="J8" s="153"/>
+      <c r="K8" s="152"/>
+      <c r="L8" s="153"/>
+      <c r="M8" s="152"/>
+      <c r="N8" s="153"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
@@ -3201,62 +3244,62 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="152" t="s">
+      <c r="E10" s="156" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="153"/>
-      <c r="G10" s="152" t="s">
+      <c r="F10" s="157"/>
+      <c r="G10" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="153"/>
-      <c r="I10" s="152" t="s">
+      <c r="H10" s="157"/>
+      <c r="I10" s="156" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="153"/>
-      <c r="K10" s="152" t="s">
+      <c r="J10" s="157"/>
+      <c r="K10" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="L10" s="153"/>
-      <c r="M10" s="152" t="s">
+      <c r="L10" s="157"/>
+      <c r="M10" s="156" t="s">
         <v>27</v>
       </c>
-      <c r="N10" s="153"/>
+      <c r="N10" s="157"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="154" t="s">
+      <c r="B11" s="149" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="154"/>
+      <c r="C11" s="149"/>
       <c r="D11" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="150"/>
-      <c r="F11" s="151"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="156"/>
-      <c r="I11" s="150"/>
-      <c r="J11" s="151"/>
-      <c r="K11" s="150"/>
-      <c r="L11" s="151"/>
-      <c r="M11" s="150"/>
-      <c r="N11" s="151"/>
+      <c r="E11" s="152"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="154"/>
+      <c r="H11" s="155"/>
+      <c r="I11" s="152"/>
+      <c r="J11" s="153"/>
+      <c r="K11" s="152"/>
+      <c r="L11" s="153"/>
+      <c r="M11" s="152"/>
+      <c r="N11" s="153"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="154"/>
-      <c r="C12" s="154"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="149"/>
       <c r="D12" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="150"/>
-      <c r="F12" s="151"/>
-      <c r="G12" s="150"/>
-      <c r="H12" s="151"/>
-      <c r="I12" s="150"/>
-      <c r="J12" s="151"/>
-      <c r="K12" s="150"/>
-      <c r="L12" s="151"/>
-      <c r="M12" s="150"/>
-      <c r="N12" s="151"/>
+      <c r="E12" s="152"/>
+      <c r="F12" s="153"/>
+      <c r="G12" s="152"/>
+      <c r="H12" s="153"/>
+      <c r="I12" s="152"/>
+      <c r="J12" s="153"/>
+      <c r="K12" s="152"/>
+      <c r="L12" s="153"/>
+      <c r="M12" s="152"/>
+      <c r="N12" s="153"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
@@ -3292,62 +3335,62 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="152" t="s">
+      <c r="E15" s="156" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="153"/>
-      <c r="G15" s="152" t="s">
+      <c r="F15" s="157"/>
+      <c r="G15" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="153"/>
-      <c r="I15" s="152" t="s">
+      <c r="H15" s="157"/>
+      <c r="I15" s="156" t="s">
         <v>25</v>
       </c>
-      <c r="J15" s="153"/>
-      <c r="K15" s="152" t="s">
+      <c r="J15" s="157"/>
+      <c r="K15" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="153"/>
-      <c r="M15" s="152" t="s">
+      <c r="L15" s="157"/>
+      <c r="M15" s="156" t="s">
         <v>27</v>
       </c>
-      <c r="N15" s="153"/>
+      <c r="N15" s="157"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="154" t="s">
+      <c r="B16" s="149" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="154"/>
+      <c r="C16" s="149"/>
       <c r="D16" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="150"/>
-      <c r="F16" s="151"/>
-      <c r="G16" s="155"/>
-      <c r="H16" s="156"/>
-      <c r="I16" s="150"/>
-      <c r="J16" s="151"/>
-      <c r="K16" s="150"/>
-      <c r="L16" s="151"/>
-      <c r="M16" s="150"/>
-      <c r="N16" s="151"/>
+      <c r="E16" s="152"/>
+      <c r="F16" s="153"/>
+      <c r="G16" s="154"/>
+      <c r="H16" s="155"/>
+      <c r="I16" s="152"/>
+      <c r="J16" s="153"/>
+      <c r="K16" s="152"/>
+      <c r="L16" s="153"/>
+      <c r="M16" s="152"/>
+      <c r="N16" s="153"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="154"/>
-      <c r="C17" s="154"/>
+      <c r="B17" s="149"/>
+      <c r="C17" s="149"/>
       <c r="D17" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="150"/>
-      <c r="F17" s="151"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="150"/>
-      <c r="J17" s="151"/>
-      <c r="K17" s="150"/>
-      <c r="L17" s="151"/>
-      <c r="M17" s="150"/>
-      <c r="N17" s="151"/>
+      <c r="E17" s="152"/>
+      <c r="F17" s="153"/>
+      <c r="G17" s="152"/>
+      <c r="H17" s="153"/>
+      <c r="I17" s="152"/>
+      <c r="J17" s="153"/>
+      <c r="K17" s="152"/>
+      <c r="L17" s="153"/>
+      <c r="M17" s="152"/>
+      <c r="N17" s="153"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B20" s="147"/>
@@ -3357,6 +3400,13 @@
         <v>34</v>
       </c>
       <c r="F20" s="147"/>
+      <c r="I20" s="147"/>
+      <c r="J20" s="147"/>
+      <c r="K20" s="147"/>
+      <c r="L20" s="147" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" s="147"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B21" s="147" t="s">
@@ -3366,6 +3416,13 @@
       <c r="D21" s="147"/>
       <c r="E21" s="148"/>
       <c r="F21" s="148"/>
+      <c r="I21" s="147" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21" s="147"/>
+      <c r="K21" s="147"/>
+      <c r="L21" s="148"/>
+      <c r="M21" s="148"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B22" s="147" t="s">
@@ -3375,6 +3432,13 @@
       <c r="D22" s="147"/>
       <c r="E22" s="148"/>
       <c r="F22" s="148"/>
+      <c r="I22" s="147" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="147"/>
+      <c r="K22" s="147"/>
+      <c r="L22" s="148"/>
+      <c r="M22" s="148"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B23" s="147" t="s">
@@ -3384,6 +3448,13 @@
       <c r="D23" s="147"/>
       <c r="E23" s="148"/>
       <c r="F23" s="148"/>
+      <c r="I23" s="147" t="s">
+        <v>47</v>
+      </c>
+      <c r="J23" s="147"/>
+      <c r="K23" s="147"/>
+      <c r="L23" s="148"/>
+      <c r="M23" s="148"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B24" s="147" t="s">
@@ -3393,6 +3464,13 @@
       <c r="D24" s="147"/>
       <c r="E24" s="148"/>
       <c r="F24" s="148"/>
+      <c r="I24" s="147" t="s">
+        <v>48</v>
+      </c>
+      <c r="J24" s="147"/>
+      <c r="K24" s="147"/>
+      <c r="L24" s="148"/>
+      <c r="M24" s="148"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B25" s="147" t="s">
@@ -3418,8 +3496,8 @@
       </c>
       <c r="C27" s="147"/>
       <c r="D27" s="147"/>
-      <c r="E27" s="149"/>
-      <c r="F27" s="149"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="158"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B28" s="147" t="s">
@@ -3449,81 +3527,17 @@
       <c r="F30" s="148"/>
     </row>
   </sheetData>
-  <mergeCells count="86">
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
+  <mergeCells count="96">
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:M22"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="B25:D25"/>
@@ -3536,6 +3550,80 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.100.1\エルフル事務局\yokoyama\火災見積システム(mitumo)\新mitumo\見積書Excelテンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\estimateTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8205FDE-FC89-4B6F-8EA1-DA5765B3A235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF1F301-8CCF-4D28-AE4A-A0E69AE56248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="地震おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="48">
   <si>
     <t>御　　見　　積　　書</t>
     <rPh sb="0" eb="1">
@@ -136,19 +136,6 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>ホウホウ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>地域（等地）</t>
-    <rPh sb="0" eb="2">
-      <t>チイキ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>チ</t>
     </rPh>
     <phoneticPr fontId="5"/>
   </si>
@@ -1190,7 +1177,7 @@
     <xf numFmtId="6" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1278,202 +1265,74 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
     <xf numFmtId="179" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1482,6 +1341,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1560,71 +1437,181 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1632,34 +1619,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2063,10 +2068,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="28"/>
@@ -2076,16 +2081,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
-      <c r="O3" s="124"/>
-      <c r="P3" s="124"/>
-      <c r="Q3" s="124"/>
-      <c r="R3" s="124"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+      <c r="R3" s="86"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="124"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="124"/>
-      <c r="R4" s="124"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="86"/>
+      <c r="Q4" s="86"/>
+      <c r="R4" s="86"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="27"/>
@@ -2148,196 +2153,196 @@
       <c r="R10" s="23"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="98" t="s">
+      <c r="A11" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="98"/>
-      <c r="M11" s="98"/>
-      <c r="N11" s="98"/>
-      <c r="O11" s="98"/>
-      <c r="P11" s="98"/>
-      <c r="Q11" s="98"/>
-      <c r="R11" s="98"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="118"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="118"/>
-      <c r="L15" s="118"/>
-      <c r="M15" s="118"/>
-      <c r="N15" s="118"/>
-      <c r="O15" s="118"/>
-      <c r="P15" s="118"/>
-      <c r="Q15" s="118"/>
-      <c r="R15" s="118"/>
+      <c r="B15" s="80"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="80"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="119" t="s">
+      <c r="A18" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="119"/>
-      <c r="C18" s="119"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="119"/>
-      <c r="H18" s="119"/>
-      <c r="I18" s="119"/>
-      <c r="J18" s="119"/>
-      <c r="K18" s="119"/>
-      <c r="L18" s="119"/>
-      <c r="M18" s="119"/>
-      <c r="N18" s="119"/>
-      <c r="O18" s="119"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="81"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="61"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="99"/>
-      <c r="E20" s="100"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="100"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="100"/>
-      <c r="L20" s="100"/>
-      <c r="M20" s="100"/>
-      <c r="N20" s="100"/>
-      <c r="O20" s="100"/>
-      <c r="P20" s="100"/>
-      <c r="Q20" s="100"/>
-      <c r="R20" s="101"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="63"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="82"/>
-      <c r="B21" s="63"/>
-      <c r="C21" s="63"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="103"/>
-      <c r="K21" s="103"/>
-      <c r="L21" s="103"/>
-      <c r="M21" s="103"/>
-      <c r="N21" s="103"/>
-      <c r="O21" s="103"/>
-      <c r="P21" s="103"/>
-      <c r="Q21" s="103"/>
-      <c r="R21" s="104"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="65"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="66"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="82" t="s">
+      <c r="A22" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="22"/>
       <c r="L22" s="21"/>
-      <c r="M22" s="105" t="s">
+      <c r="M22" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="106"/>
-      <c r="O22" s="109"/>
-      <c r="P22" s="110"/>
-      <c r="Q22" s="110"/>
-      <c r="R22" s="111"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="82"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="120"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="121"/>
-      <c r="G23" s="121"/>
-      <c r="H23" s="121"/>
-      <c r="I23" s="121"/>
-      <c r="J23" s="121"/>
-      <c r="K23" s="121"/>
-      <c r="L23" s="122"/>
-      <c r="M23" s="105"/>
-      <c r="N23" s="106"/>
-      <c r="O23" s="112"/>
-      <c r="P23" s="113"/>
-      <c r="Q23" s="113"/>
-      <c r="R23" s="114"/>
+      <c r="A23" s="55"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="83"/>
+      <c r="J23" s="83"/>
+      <c r="K23" s="83"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="74"/>
+      <c r="P23" s="75"/>
+      <c r="Q23" s="75"/>
+      <c r="R23" s="76"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="82"/>
-      <c r="B24" s="63"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="123"/>
-      <c r="E24" s="121"/>
-      <c r="F24" s="121"/>
-      <c r="G24" s="121"/>
-      <c r="H24" s="121"/>
-      <c r="I24" s="121"/>
-      <c r="J24" s="121"/>
-      <c r="K24" s="121"/>
-      <c r="L24" s="122"/>
-      <c r="M24" s="105"/>
-      <c r="N24" s="106"/>
-      <c r="O24" s="112"/>
-      <c r="P24" s="113"/>
-      <c r="Q24" s="113"/>
-      <c r="R24" s="114"/>
+      <c r="A24" s="55"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="85"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="83"/>
+      <c r="J24" s="83"/>
+      <c r="K24" s="83"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="74"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="76"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="82"/>
-      <c r="B25" s="63"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="123"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="121"/>
-      <c r="G25" s="121"/>
-      <c r="H25" s="121"/>
-      <c r="I25" s="121"/>
-      <c r="J25" s="121"/>
-      <c r="K25" s="121"/>
-      <c r="L25" s="122"/>
-      <c r="M25" s="105"/>
-      <c r="N25" s="106"/>
-      <c r="O25" s="112"/>
-      <c r="P25" s="113"/>
-      <c r="Q25" s="113"/>
-      <c r="R25" s="114"/>
+      <c r="A25" s="55"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="83"/>
+      <c r="J25" s="83"/>
+      <c r="K25" s="83"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="74"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="76"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="82"/>
-      <c r="B26" s="63"/>
-      <c r="C26" s="63"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="56"/>
       <c r="D26" s="20"/>
       <c r="E26" s="19"/>
       <c r="F26" s="18"/>
@@ -2347,17 +2352,17 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="16"/>
-      <c r="M26" s="105"/>
-      <c r="N26" s="106"/>
-      <c r="O26" s="112"/>
-      <c r="P26" s="113"/>
-      <c r="Q26" s="113"/>
-      <c r="R26" s="114"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="75"/>
+      <c r="R26" s="76"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="82"/>
-      <c r="B27" s="63"/>
-      <c r="C27" s="63"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
       <c r="D27" s="15"/>
       <c r="F27" s="13"/>
       <c r="G27" s="14"/>
@@ -2365,17 +2370,17 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="L27" s="11"/>
-      <c r="M27" s="105"/>
-      <c r="N27" s="106"/>
-      <c r="O27" s="112"/>
-      <c r="P27" s="113"/>
-      <c r="Q27" s="113"/>
-      <c r="R27" s="114"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="68"/>
+      <c r="O27" s="74"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="75"/>
+      <c r="R27" s="76"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="89"/>
-      <c r="B28" s="90"/>
-      <c r="C28" s="90"/>
+      <c r="A28" s="57"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="58"/>
       <c r="D28" s="10"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -2385,346 +2390,344 @@
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="8"/>
-      <c r="M28" s="107"/>
-      <c r="N28" s="108"/>
-      <c r="O28" s="115"/>
-      <c r="P28" s="116"/>
-      <c r="Q28" s="116"/>
-      <c r="R28" s="117"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="70"/>
+      <c r="O28" s="77"/>
+      <c r="P28" s="78"/>
+      <c r="Q28" s="78"/>
+      <c r="R28" s="79"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="81" t="s">
+      <c r="A31" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="86"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="86"/>
-      <c r="G31" s="86"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="86"/>
-      <c r="J31" s="61" t="s">
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="92"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="61"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="86"/>
-      <c r="N31" s="86"/>
-      <c r="O31" s="86"/>
-      <c r="P31" s="86"/>
-      <c r="Q31" s="86"/>
-      <c r="R31" s="87"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="92"/>
+      <c r="O31" s="92"/>
+      <c r="P31" s="92"/>
+      <c r="Q31" s="92"/>
+      <c r="R31" s="93"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="82"/>
-      <c r="B32" s="63"/>
-      <c r="C32" s="63"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="63"/>
-      <c r="K32" s="63"/>
-      <c r="L32" s="63"/>
-      <c r="M32" s="60"/>
-      <c r="N32" s="60"/>
-      <c r="O32" s="60"/>
-      <c r="P32" s="60"/>
-      <c r="Q32" s="60"/>
-      <c r="R32" s="88"/>
+      <c r="A32" s="55"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
+      <c r="F32" s="94"/>
+      <c r="G32" s="94"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="94"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="94"/>
+      <c r="N32" s="94"/>
+      <c r="O32" s="94"/>
+      <c r="P32" s="94"/>
+      <c r="Q32" s="94"/>
+      <c r="R32" s="95"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="82" t="s">
+      <c r="A33" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="63"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="60"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="60"/>
-      <c r="I33" s="60"/>
-      <c r="J33" s="63" t="s">
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="159"/>
+      <c r="E33" s="160"/>
+      <c r="F33" s="160"/>
+      <c r="G33" s="160"/>
+      <c r="H33" s="160"/>
+      <c r="I33" s="160"/>
+      <c r="J33" s="160"/>
+      <c r="K33" s="160"/>
+      <c r="L33" s="160"/>
+      <c r="M33" s="160"/>
+      <c r="N33" s="160"/>
+      <c r="O33" s="160"/>
+      <c r="P33" s="160"/>
+      <c r="Q33" s="160"/>
+      <c r="R33" s="161"/>
+    </row>
+    <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="55"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="162"/>
+      <c r="E34" s="163"/>
+      <c r="F34" s="163"/>
+      <c r="G34" s="163"/>
+      <c r="H34" s="163"/>
+      <c r="I34" s="163"/>
+      <c r="J34" s="163"/>
+      <c r="K34" s="163"/>
+      <c r="L34" s="163"/>
+      <c r="M34" s="163"/>
+      <c r="N34" s="163"/>
+      <c r="O34" s="163"/>
+      <c r="P34" s="163"/>
+      <c r="Q34" s="163"/>
+      <c r="R34" s="164"/>
+    </row>
+    <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="K33" s="63"/>
-      <c r="L33" s="63"/>
-      <c r="M33" s="60"/>
-      <c r="N33" s="60"/>
-      <c r="O33" s="60"/>
-      <c r="P33" s="60"/>
-      <c r="Q33" s="60"/>
-      <c r="R33" s="88"/>
-    </row>
-    <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="82"/>
-      <c r="B34" s="63"/>
-      <c r="C34" s="63"/>
-      <c r="D34" s="60"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="60"/>
-      <c r="G34" s="60"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="60"/>
-      <c r="J34" s="63"/>
-      <c r="K34" s="63"/>
-      <c r="L34" s="63"/>
-      <c r="M34" s="60"/>
-      <c r="N34" s="60"/>
-      <c r="O34" s="60"/>
-      <c r="P34" s="60"/>
-      <c r="Q34" s="60"/>
-      <c r="R34" s="88"/>
-    </row>
-    <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="82" t="s">
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="97"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="97"/>
+      <c r="I35" s="97"/>
+      <c r="J35" s="97"/>
+      <c r="K35" s="97"/>
+      <c r="L35" s="97"/>
+      <c r="M35" s="97"/>
+      <c r="N35" s="97"/>
+      <c r="O35" s="97"/>
+      <c r="P35" s="97"/>
+      <c r="Q35" s="97"/>
+      <c r="R35" s="98"/>
+    </row>
+    <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="57"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="99"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="100"/>
+      <c r="G36" s="100"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="100"/>
+      <c r="J36" s="100"/>
+      <c r="K36" s="100"/>
+      <c r="L36" s="100"/>
+      <c r="M36" s="100"/>
+      <c r="N36" s="100"/>
+      <c r="O36" s="100"/>
+      <c r="P36" s="100"/>
+      <c r="Q36" s="100"/>
+      <c r="R36" s="101"/>
+    </row>
+    <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="87"/>
+      <c r="B37" s="88"/>
+      <c r="C37" s="88"/>
+      <c r="D37" s="88"/>
+      <c r="E37" s="88"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="88"/>
+      <c r="I37" s="88"/>
+      <c r="J37" s="88"/>
+      <c r="K37" s="88"/>
+      <c r="L37" s="88"/>
+      <c r="M37" s="88"/>
+      <c r="N37" s="88"/>
+      <c r="O37" s="88"/>
+      <c r="P37" s="88"/>
+      <c r="Q37" s="88"/>
+      <c r="R37" s="88"/>
+    </row>
+    <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="89"/>
+      <c r="B38" s="89"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="89"/>
+      <c r="H38" s="89"/>
+      <c r="I38" s="89"/>
+      <c r="J38" s="89"/>
+      <c r="K38" s="89"/>
+      <c r="L38" s="89"/>
+      <c r="M38" s="89"/>
+      <c r="N38" s="89"/>
+      <c r="O38" s="89"/>
+      <c r="P38" s="89"/>
+      <c r="Q38" s="89"/>
+      <c r="R38" s="89"/>
+    </row>
+    <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="63"/>
-      <c r="C35" s="63"/>
-      <c r="D35" s="91"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="92"/>
-      <c r="H35" s="92"/>
-      <c r="I35" s="92"/>
-      <c r="J35" s="92"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="92"/>
-      <c r="M35" s="92"/>
-      <c r="N35" s="92"/>
-      <c r="O35" s="92"/>
-      <c r="P35" s="92"/>
-      <c r="Q35" s="92"/>
-      <c r="R35" s="93"/>
-    </row>
-    <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="89"/>
-      <c r="B36" s="90"/>
-      <c r="C36" s="90"/>
-      <c r="D36" s="94"/>
-      <c r="E36" s="95"/>
-      <c r="F36" s="95"/>
-      <c r="G36" s="95"/>
-      <c r="H36" s="95"/>
-      <c r="I36" s="95"/>
-      <c r="J36" s="95"/>
-      <c r="K36" s="95"/>
-      <c r="L36" s="95"/>
-      <c r="M36" s="95"/>
-      <c r="N36" s="95"/>
-      <c r="O36" s="95"/>
-      <c r="P36" s="95"/>
-      <c r="Q36" s="95"/>
-      <c r="R36" s="96"/>
-    </row>
-    <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="83"/>
-      <c r="B37" s="84"/>
-      <c r="C37" s="84"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="84"/>
-      <c r="G37" s="84"/>
-      <c r="H37" s="84"/>
-      <c r="I37" s="84"/>
-      <c r="J37" s="84"/>
-      <c r="K37" s="84"/>
-      <c r="L37" s="84"/>
-      <c r="M37" s="84"/>
-      <c r="N37" s="84"/>
-      <c r="O37" s="84"/>
-      <c r="P37" s="84"/>
-      <c r="Q37" s="84"/>
-      <c r="R37" s="84"/>
-    </row>
-    <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="85"/>
-      <c r="B38" s="85"/>
-      <c r="C38" s="85"/>
-      <c r="D38" s="85"/>
-      <c r="E38" s="85"/>
-      <c r="F38" s="85"/>
-      <c r="G38" s="85"/>
-      <c r="H38" s="85"/>
-      <c r="I38" s="85"/>
-      <c r="J38" s="85"/>
-      <c r="K38" s="85"/>
-      <c r="L38" s="85"/>
-      <c r="M38" s="85"/>
-      <c r="N38" s="85"/>
-      <c r="O38" s="85"/>
-      <c r="P38" s="85"/>
-      <c r="Q38" s="85"/>
-      <c r="R38" s="85"/>
-    </row>
-    <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="81" t="s">
+      <c r="B39" s="60"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="61"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61" t="s">
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="90"/>
+      <c r="H39" s="60" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" s="60"/>
+      <c r="J39" s="60"/>
+      <c r="K39" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="L39" s="60"/>
+      <c r="M39" s="60"/>
+      <c r="N39" s="90"/>
+      <c r="O39" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="P39" s="60"/>
+      <c r="Q39" s="60"/>
+      <c r="R39" s="110"/>
+    </row>
+    <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="55"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="56"/>
+      <c r="N40" s="91"/>
+      <c r="O40" s="56"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="56"/>
+      <c r="R40" s="111"/>
+    </row>
+    <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="I39" s="61"/>
-      <c r="J39" s="61"/>
-      <c r="K39" s="61" t="s">
-        <v>12</v>
-      </c>
-      <c r="L39" s="61"/>
-      <c r="M39" s="61"/>
-      <c r="N39" s="75"/>
-      <c r="O39" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="P39" s="61"/>
-      <c r="Q39" s="61"/>
-      <c r="R39" s="62"/>
-    </row>
-    <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="82"/>
-      <c r="B40" s="63"/>
-      <c r="C40" s="63"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="63"/>
-      <c r="G40" s="76"/>
-      <c r="H40" s="63"/>
-      <c r="I40" s="63"/>
-      <c r="J40" s="63"/>
-      <c r="K40" s="63"/>
-      <c r="L40" s="63"/>
-      <c r="M40" s="63"/>
-      <c r="N40" s="76"/>
-      <c r="O40" s="63"/>
-      <c r="P40" s="63"/>
-      <c r="Q40" s="63"/>
-      <c r="R40" s="64"/>
-    </row>
-    <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="54" t="s">
+      <c r="B41" s="105"/>
+      <c r="C41" s="106"/>
+      <c r="D41" s="112"/>
+      <c r="E41" s="113"/>
+      <c r="F41" s="113"/>
+      <c r="G41" s="114"/>
+      <c r="H41" s="126" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="55"/>
-      <c r="C41" s="56"/>
-      <c r="D41" s="65"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="30" t="s">
+      <c r="I41" s="127"/>
+      <c r="J41" s="128"/>
+      <c r="K41" s="112"/>
+      <c r="L41" s="113"/>
+      <c r="M41" s="113"/>
+      <c r="N41" s="114"/>
+      <c r="O41" s="118"/>
+      <c r="P41" s="118"/>
+      <c r="Q41" s="118"/>
+      <c r="R41" s="119"/>
+    </row>
+    <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="107"/>
+      <c r="B42" s="108"/>
+      <c r="C42" s="109"/>
+      <c r="D42" s="115"/>
+      <c r="E42" s="116"/>
+      <c r="F42" s="116"/>
+      <c r="G42" s="117"/>
+      <c r="H42" s="129"/>
+      <c r="I42" s="130"/>
+      <c r="J42" s="131"/>
+      <c r="K42" s="115"/>
+      <c r="L42" s="116"/>
+      <c r="M42" s="116"/>
+      <c r="N42" s="117"/>
+      <c r="O42" s="118"/>
+      <c r="P42" s="118"/>
+      <c r="Q42" s="118"/>
+      <c r="R42" s="119"/>
+    </row>
+    <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="104" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="31"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="65"/>
-      <c r="L41" s="66"/>
-      <c r="M41" s="66"/>
-      <c r="N41" s="67"/>
-      <c r="O41" s="71"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="71"/>
-      <c r="R41" s="72"/>
-    </row>
-    <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="57"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="59"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="69"/>
-      <c r="F42" s="69"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="68"/>
-      <c r="L42" s="69"/>
-      <c r="M42" s="69"/>
-      <c r="N42" s="70"/>
-      <c r="O42" s="71"/>
-      <c r="P42" s="71"/>
-      <c r="Q42" s="71"/>
-      <c r="R42" s="72"/>
-    </row>
-    <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="54" t="s">
+      <c r="B43" s="105"/>
+      <c r="C43" s="106"/>
+      <c r="D43" s="112"/>
+      <c r="E43" s="113"/>
+      <c r="F43" s="113"/>
+      <c r="G43" s="114"/>
+      <c r="H43" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="55"/>
-      <c r="C43" s="56"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="66"/>
-      <c r="G43" s="67"/>
-      <c r="H43" s="79" t="s">
+      <c r="I43" s="105"/>
+      <c r="J43" s="106"/>
+      <c r="K43" s="112"/>
+      <c r="L43" s="113"/>
+      <c r="M43" s="113"/>
+      <c r="N43" s="114"/>
+      <c r="O43" s="118"/>
+      <c r="P43" s="118"/>
+      <c r="Q43" s="118"/>
+      <c r="R43" s="119"/>
+    </row>
+    <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="107"/>
+      <c r="B44" s="108"/>
+      <c r="C44" s="109"/>
+      <c r="D44" s="115"/>
+      <c r="E44" s="116"/>
+      <c r="F44" s="116"/>
+      <c r="G44" s="117"/>
+      <c r="H44" s="125"/>
+      <c r="I44" s="108"/>
+      <c r="J44" s="109"/>
+      <c r="K44" s="115"/>
+      <c r="L44" s="116"/>
+      <c r="M44" s="116"/>
+      <c r="N44" s="117"/>
+      <c r="O44" s="118"/>
+      <c r="P44" s="118"/>
+      <c r="Q44" s="118"/>
+      <c r="R44" s="119"/>
+    </row>
+    <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="55"/>
-      <c r="J43" s="56"/>
-      <c r="K43" s="65"/>
-      <c r="L43" s="66"/>
-      <c r="M43" s="66"/>
-      <c r="N43" s="67"/>
-      <c r="O43" s="71"/>
-      <c r="P43" s="71"/>
-      <c r="Q43" s="71"/>
-      <c r="R43" s="72"/>
-    </row>
-    <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="57"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="59"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="70"/>
-      <c r="H44" s="80"/>
-      <c r="I44" s="58"/>
-      <c r="J44" s="59"/>
-      <c r="K44" s="68"/>
-      <c r="L44" s="69"/>
-      <c r="M44" s="69"/>
-      <c r="N44" s="70"/>
-      <c r="O44" s="71"/>
-      <c r="P44" s="71"/>
-      <c r="Q44" s="71"/>
-      <c r="R44" s="72"/>
-    </row>
-    <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="B45" s="53"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="77"/>
-      <c r="G45" s="78"/>
-      <c r="H45" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I45" s="53"/>
-      <c r="J45" s="53"/>
-      <c r="K45" s="77"/>
-      <c r="L45" s="77"/>
-      <c r="M45" s="77"/>
-      <c r="N45" s="78"/>
-      <c r="O45" s="73"/>
-      <c r="P45" s="73"/>
-      <c r="Q45" s="73"/>
-      <c r="R45" s="74"/>
+      <c r="B45" s="103"/>
+      <c r="C45" s="103"/>
+      <c r="D45" s="122"/>
+      <c r="E45" s="122"/>
+      <c r="F45" s="122"/>
+      <c r="G45" s="123"/>
+      <c r="H45" s="103" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="103"/>
+      <c r="J45" s="103"/>
+      <c r="K45" s="122"/>
+      <c r="L45" s="122"/>
+      <c r="M45" s="122"/>
+      <c r="N45" s="123"/>
+      <c r="O45" s="120"/>
+      <c r="P45" s="120"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="121"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2732,237 +2735,237 @@
     </row>
     <row r="48" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A48" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="30"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="136"/>
+      <c r="E49" s="137"/>
+      <c r="F49" s="137"/>
+      <c r="G49" s="137"/>
+      <c r="H49" s="145"/>
+      <c r="I49" s="136"/>
+      <c r="J49" s="137"/>
+      <c r="K49" s="137"/>
+      <c r="L49" s="137"/>
+      <c r="M49" s="145"/>
+      <c r="N49" s="136"/>
+      <c r="O49" s="137"/>
+      <c r="P49" s="137"/>
+      <c r="Q49" s="137"/>
+      <c r="R49" s="138"/>
+    </row>
+    <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="33"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="139"/>
+      <c r="E50" s="140"/>
+      <c r="F50" s="140"/>
+      <c r="G50" s="140"/>
+      <c r="H50" s="146"/>
+      <c r="I50" s="139"/>
+      <c r="J50" s="140"/>
+      <c r="K50" s="140"/>
+      <c r="L50" s="140"/>
+      <c r="M50" s="146"/>
+      <c r="N50" s="139"/>
+      <c r="O50" s="140"/>
+      <c r="P50" s="140"/>
+      <c r="Q50" s="140"/>
+      <c r="R50" s="141"/>
+    </row>
+    <row r="51" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="46" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="125"/>
-      <c r="B49" s="126"/>
-      <c r="C49" s="127"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="50"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
-      <c r="M49" s="50"/>
-      <c r="N49" s="40"/>
-      <c r="O49" s="41"/>
-      <c r="P49" s="41"/>
-      <c r="Q49" s="41"/>
-      <c r="R49" s="42"/>
-    </row>
-    <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="128"/>
-      <c r="B50" s="129"/>
-      <c r="C50" s="130"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="44"/>
-      <c r="F50" s="44"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="43"/>
-      <c r="J50" s="44"/>
-      <c r="K50" s="44"/>
-      <c r="L50" s="44"/>
-      <c r="M50" s="51"/>
-      <c r="N50" s="43"/>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
-      <c r="R50" s="45"/>
-    </row>
-    <row r="51" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="141" t="s">
-        <v>19</v>
-      </c>
-      <c r="B51" s="142"/>
-      <c r="C51" s="143"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="46"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="46"/>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46"/>
-      <c r="O51" s="46"/>
-      <c r="P51" s="46"/>
-      <c r="Q51" s="46"/>
-      <c r="R51" s="47"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="52"/>
+      <c r="J51" s="52"/>
+      <c r="K51" s="52"/>
+      <c r="L51" s="52"/>
+      <c r="M51" s="52"/>
+      <c r="N51" s="52"/>
+      <c r="O51" s="52"/>
+      <c r="P51" s="52"/>
+      <c r="Q51" s="52"/>
+      <c r="R51" s="142"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="144"/>
-      <c r="B52" s="145"/>
-      <c r="C52" s="146"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="46"/>
-      <c r="L52" s="46"/>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
-      <c r="O52" s="46"/>
-      <c r="P52" s="46"/>
-      <c r="Q52" s="46"/>
-      <c r="R52" s="47"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="50"/>
+      <c r="C52" s="51"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
+      <c r="G52" s="52"/>
+      <c r="H52" s="52"/>
+      <c r="I52" s="52"/>
+      <c r="J52" s="52"/>
+      <c r="K52" s="52"/>
+      <c r="L52" s="52"/>
+      <c r="M52" s="52"/>
+      <c r="N52" s="52"/>
+      <c r="O52" s="52"/>
+      <c r="P52" s="52"/>
+      <c r="Q52" s="52"/>
+      <c r="R52" s="142"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
       <c r="B53" s="4"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="37"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
-      <c r="L53" s="38"/>
-      <c r="M53" s="48"/>
-      <c r="N53" s="37"/>
-      <c r="O53" s="38"/>
-      <c r="P53" s="38"/>
-      <c r="Q53" s="38"/>
-      <c r="R53" s="39"/>
+      <c r="D53" s="133"/>
+      <c r="E53" s="134"/>
+      <c r="F53" s="134"/>
+      <c r="G53" s="134"/>
+      <c r="H53" s="143"/>
+      <c r="I53" s="133"/>
+      <c r="J53" s="134"/>
+      <c r="K53" s="134"/>
+      <c r="L53" s="134"/>
+      <c r="M53" s="143"/>
+      <c r="N53" s="133"/>
+      <c r="O53" s="134"/>
+      <c r="P53" s="134"/>
+      <c r="Q53" s="134"/>
+      <c r="R53" s="135"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="135" t="s">
+      <c r="A54" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B54" s="41"/>
+      <c r="C54" s="42"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="36"/>
+      <c r="I54" s="36"/>
+      <c r="J54" s="36"/>
+      <c r="K54" s="36"/>
+      <c r="L54" s="36"/>
+      <c r="M54" s="36"/>
+      <c r="N54" s="36"/>
+      <c r="O54" s="36"/>
+      <c r="P54" s="36"/>
+      <c r="Q54" s="36"/>
+      <c r="R54" s="37"/>
+    </row>
+    <row r="55" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="43"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="38"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="38"/>
+      <c r="G55" s="38"/>
+      <c r="H55" s="38"/>
+      <c r="I55" s="38"/>
+      <c r="J55" s="38"/>
+      <c r="K55" s="38"/>
+      <c r="L55" s="38"/>
+      <c r="M55" s="38"/>
+      <c r="N55" s="38"/>
+      <c r="O55" s="38"/>
+      <c r="P55" s="38"/>
+      <c r="Q55" s="38"/>
+      <c r="R55" s="39"/>
+    </row>
+    <row r="56" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="136"/>
-      <c r="C54" s="137"/>
-      <c r="D54" s="131"/>
-      <c r="E54" s="131"/>
-      <c r="F54" s="131"/>
-      <c r="G54" s="131"/>
-      <c r="H54" s="131"/>
-      <c r="I54" s="131"/>
-      <c r="J54" s="131"/>
-      <c r="K54" s="131"/>
-      <c r="L54" s="131"/>
-      <c r="M54" s="131"/>
-      <c r="N54" s="131"/>
-      <c r="O54" s="131"/>
-      <c r="P54" s="131"/>
-      <c r="Q54" s="131"/>
-      <c r="R54" s="132"/>
-    </row>
-    <row r="55" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="138"/>
-      <c r="B55" s="139"/>
-      <c r="C55" s="140"/>
-      <c r="D55" s="133"/>
-      <c r="E55" s="133"/>
-      <c r="F55" s="133"/>
-      <c r="G55" s="133"/>
-      <c r="H55" s="133"/>
-      <c r="I55" s="133"/>
-      <c r="J55" s="133"/>
-      <c r="K55" s="133"/>
-      <c r="L55" s="133"/>
-      <c r="M55" s="133"/>
-      <c r="N55" s="133"/>
-      <c r="O55" s="133"/>
-      <c r="P55" s="133"/>
-      <c r="Q55" s="133"/>
-      <c r="R55" s="134"/>
-    </row>
-    <row r="56" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="135" t="s">
-        <v>21</v>
-      </c>
-      <c r="B56" s="136"/>
-      <c r="C56" s="137"/>
-      <c r="D56" s="131"/>
-      <c r="E56" s="131"/>
-      <c r="F56" s="131"/>
-      <c r="G56" s="131"/>
-      <c r="H56" s="131"/>
-      <c r="I56" s="131"/>
-      <c r="J56" s="131"/>
-      <c r="K56" s="131"/>
-      <c r="L56" s="131"/>
-      <c r="M56" s="131"/>
-      <c r="N56" s="131"/>
-      <c r="O56" s="131"/>
-      <c r="P56" s="131"/>
-      <c r="Q56" s="131"/>
-      <c r="R56" s="132"/>
+      <c r="B56" s="41"/>
+      <c r="C56" s="42"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="36"/>
+      <c r="J56" s="36"/>
+      <c r="K56" s="36"/>
+      <c r="L56" s="36"/>
+      <c r="M56" s="36"/>
+      <c r="N56" s="36"/>
+      <c r="O56" s="36"/>
+      <c r="P56" s="36"/>
+      <c r="Q56" s="36"/>
+      <c r="R56" s="37"/>
     </row>
     <row r="57" spans="1:18" s="2" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="138"/>
-      <c r="B57" s="139"/>
-      <c r="C57" s="140"/>
-      <c r="D57" s="133"/>
-      <c r="E57" s="133"/>
-      <c r="F57" s="133"/>
-      <c r="G57" s="133"/>
-      <c r="H57" s="133"/>
-      <c r="I57" s="133"/>
-      <c r="J57" s="133"/>
-      <c r="K57" s="133"/>
-      <c r="L57" s="133"/>
-      <c r="M57" s="133"/>
-      <c r="N57" s="133"/>
-      <c r="O57" s="133"/>
-      <c r="P57" s="133"/>
-      <c r="Q57" s="133"/>
-      <c r="R57" s="134"/>
+      <c r="A57" s="43"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="38"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="38"/>
+      <c r="I57" s="38"/>
+      <c r="J57" s="38"/>
+      <c r="K57" s="38"/>
+      <c r="L57" s="38"/>
+      <c r="M57" s="38"/>
+      <c r="N57" s="38"/>
+      <c r="O57" s="38"/>
+      <c r="P57" s="38"/>
+      <c r="Q57" s="38"/>
+      <c r="R57" s="39"/>
     </row>
     <row r="58" spans="1:18" s="2" customFormat="1" ht="27" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D58" s="49"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="49"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="49"/>
-      <c r="J58" s="49"/>
-      <c r="K58" s="49"/>
-      <c r="L58" s="49"/>
-      <c r="M58" s="49"/>
-      <c r="N58" s="49"/>
-      <c r="O58" s="49"/>
-      <c r="P58" s="49"/>
-      <c r="Q58" s="49"/>
-      <c r="R58" s="49"/>
+      <c r="D58" s="144"/>
+      <c r="E58" s="144"/>
+      <c r="F58" s="144"/>
+      <c r="G58" s="144"/>
+      <c r="H58" s="144"/>
+      <c r="I58" s="144"/>
+      <c r="J58" s="144"/>
+      <c r="K58" s="144"/>
+      <c r="L58" s="144"/>
+      <c r="M58" s="144"/>
+      <c r="N58" s="144"/>
+      <c r="O58" s="144"/>
+      <c r="P58" s="144"/>
+      <c r="Q58" s="144"/>
+      <c r="R58" s="144"/>
     </row>
     <row r="59" spans="1:18" s="2" customFormat="1" ht="30.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D59" s="36" t="str">
+      <c r="D59" s="132" t="str">
         <f>IF(MOD(D58,1000)=0,"千円単位",IF(MOD(D58,100)=0,"百円単位",IF(MOD(D58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
-      <c r="H59" s="36"/>
-      <c r="I59" s="36" t="str">
+      <c r="E59" s="132"/>
+      <c r="F59" s="132"/>
+      <c r="G59" s="132"/>
+      <c r="H59" s="132"/>
+      <c r="I59" s="132" t="str">
         <f>IF(MOD(I58,1000)=0,"千円単位",IF(MOD(I58,100)=0,"百円単位",IF(MOD(I58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="J59" s="36"/>
-      <c r="K59" s="36"/>
-      <c r="L59" s="36"/>
-      <c r="M59" s="36"/>
-      <c r="N59" s="36" t="str">
+      <c r="J59" s="132"/>
+      <c r="K59" s="132"/>
+      <c r="L59" s="132"/>
+      <c r="M59" s="132"/>
+      <c r="N59" s="132" t="str">
         <f>IF(MOD(N58,1000)=0,"千円単位",IF(MOD(N58,100)=0,"百円単位",IF(MOD(N58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="O59" s="36"/>
-      <c r="P59" s="36"/>
-      <c r="Q59" s="36"/>
-      <c r="R59" s="36"/>
+      <c r="O59" s="132"/>
+      <c r="P59" s="132"/>
+      <c r="Q59" s="132"/>
+      <c r="R59" s="132"/>
     </row>
     <row r="60" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="61" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2973,58 +2976,7 @@
     <row r="66" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15"/>
     <row r="67" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <mergeCells count="65">
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="N56:R57"/>
-    <mergeCell ref="D54:H55"/>
-    <mergeCell ref="I54:M55"/>
-    <mergeCell ref="N54:R55"/>
-    <mergeCell ref="A54:C55"/>
-    <mergeCell ref="A56:C57"/>
-    <mergeCell ref="D56:H57"/>
-    <mergeCell ref="I56:M57"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="I51:M52"/>
-    <mergeCell ref="D51:H52"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A22:C28"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:R21"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="O22:R28"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="J33:L34"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="M33:R34"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="D31:I32"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="A43:C44"/>
-    <mergeCell ref="D33:I34"/>
-    <mergeCell ref="O39:R40"/>
-    <mergeCell ref="K43:N44"/>
-    <mergeCell ref="A41:C42"/>
-    <mergeCell ref="O41:R45"/>
-    <mergeCell ref="H39:J40"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="K41:N42"/>
-    <mergeCell ref="K45:N45"/>
-    <mergeCell ref="D43:G44"/>
-    <mergeCell ref="H43:J44"/>
-    <mergeCell ref="D41:G42"/>
+  <mergeCells count="63">
     <mergeCell ref="H41:J42"/>
     <mergeCell ref="D59:H59"/>
     <mergeCell ref="I59:M59"/>
@@ -3039,6 +2991,55 @@
     <mergeCell ref="D49:H50"/>
     <mergeCell ref="I53:M53"/>
     <mergeCell ref="I49:M50"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="A43:C44"/>
+    <mergeCell ref="O39:R40"/>
+    <mergeCell ref="K43:N44"/>
+    <mergeCell ref="A41:C42"/>
+    <mergeCell ref="O41:R45"/>
+    <mergeCell ref="H39:J40"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="K41:N42"/>
+    <mergeCell ref="K45:N45"/>
+    <mergeCell ref="D43:G44"/>
+    <mergeCell ref="H43:J44"/>
+    <mergeCell ref="D41:G42"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="D33:R34"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A22:C28"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:R21"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="O22:R28"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="N56:R57"/>
+    <mergeCell ref="D54:H55"/>
+    <mergeCell ref="I54:M55"/>
+    <mergeCell ref="N54:R55"/>
+    <mergeCell ref="A54:C55"/>
+    <mergeCell ref="A56:C57"/>
+    <mergeCell ref="D56:H57"/>
+    <mergeCell ref="I56:M57"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="I51:M52"/>
+    <mergeCell ref="D51:H52"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="D51:R52">
@@ -3092,62 +3093,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="151" t="s">
+      <c r="E2" s="154" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151" t="s">
+      <c r="H2" s="154"/>
+      <c r="I2" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="151"/>
-      <c r="I2" s="151" t="s">
+      <c r="J2" s="154"/>
+      <c r="K2" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="151"/>
-      <c r="K2" s="151" t="s">
+      <c r="L2" s="154"/>
+      <c r="M2" s="154" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="151"/>
-      <c r="M2" s="151" t="s">
+      <c r="N2" s="154"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B3" s="155" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="151"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="149" t="s">
+      <c r="C3" s="155"/>
+      <c r="D3" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="149"/>
-      <c r="D3" s="29" t="s">
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+      <c r="L3" s="155"/>
+      <c r="M3" s="155"/>
+      <c r="N3" s="155"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B4" s="155"/>
+      <c r="C4" s="155"/>
+      <c r="D4" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="149"/>
-      <c r="F3" s="149"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="149"/>
-      <c r="K3" s="149"/>
-      <c r="L3" s="149"/>
-      <c r="M3" s="149"/>
-      <c r="N3" s="149"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="149"/>
-      <c r="C4" s="149"/>
-      <c r="D4" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="149"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="149"/>
-      <c r="I4" s="149"/>
-      <c r="J4" s="149"/>
-      <c r="K4" s="149"/>
-      <c r="L4" s="149"/>
-      <c r="M4" s="149"/>
-      <c r="N4" s="149"/>
+      <c r="E4" s="155"/>
+      <c r="F4" s="155"/>
+      <c r="G4" s="155"/>
+      <c r="H4" s="155"/>
+      <c r="I4" s="155"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="155"/>
+      <c r="L4" s="155"/>
+      <c r="M4" s="155"/>
+      <c r="N4" s="155"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -3168,39 +3169,39 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="156" t="s">
+      <c r="E6" s="150" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="151"/>
+      <c r="G6" s="150" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="157"/>
-      <c r="G6" s="156" t="s">
+      <c r="H6" s="151"/>
+      <c r="I6" s="150" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="157"/>
-      <c r="I6" s="156" t="s">
+      <c r="J6" s="151"/>
+      <c r="K6" s="150" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="157"/>
-      <c r="K6" s="156" t="s">
+      <c r="L6" s="151"/>
+      <c r="M6" s="150" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="157"/>
-      <c r="M6" s="156" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="157"/>
+      <c r="N6" s="151"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="149" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="149"/>
+      <c r="B7" s="155" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="155"/>
       <c r="D7" s="29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" s="152"/>
       <c r="F7" s="153"/>
-      <c r="G7" s="154"/>
-      <c r="H7" s="155"/>
+      <c r="G7" s="157"/>
+      <c r="H7" s="158"/>
       <c r="I7" s="152"/>
       <c r="J7" s="153"/>
       <c r="K7" s="152"/>
@@ -3209,10 +3210,10 @@
       <c r="N7" s="153"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="149"/>
-      <c r="C8" s="149"/>
+      <c r="B8" s="155"/>
+      <c r="C8" s="155"/>
       <c r="D8" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" s="152"/>
       <c r="F8" s="153"/>
@@ -3244,39 +3245,39 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="156" t="s">
+      <c r="E10" s="150" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="151"/>
+      <c r="G10" s="150" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="157"/>
-      <c r="G10" s="156" t="s">
+      <c r="H10" s="151"/>
+      <c r="I10" s="150" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="157"/>
-      <c r="I10" s="156" t="s">
+      <c r="J10" s="151"/>
+      <c r="K10" s="150" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="157"/>
-      <c r="K10" s="156" t="s">
+      <c r="L10" s="151"/>
+      <c r="M10" s="150" t="s">
         <v>26</v>
       </c>
-      <c r="L10" s="157"/>
-      <c r="M10" s="156" t="s">
-        <v>27</v>
-      </c>
-      <c r="N10" s="157"/>
+      <c r="N10" s="151"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="149" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="149"/>
+      <c r="B11" s="155" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="155"/>
       <c r="D11" s="29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" s="152"/>
       <c r="F11" s="153"/>
-      <c r="G11" s="154"/>
-      <c r="H11" s="155"/>
+      <c r="G11" s="157"/>
+      <c r="H11" s="158"/>
       <c r="I11" s="152"/>
       <c r="J11" s="153"/>
       <c r="K11" s="152"/>
@@ -3285,10 +3286,10 @@
       <c r="N11" s="153"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="149"/>
-      <c r="C12" s="149"/>
+      <c r="B12" s="155"/>
+      <c r="C12" s="155"/>
       <c r="D12" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="152"/>
       <c r="F12" s="153"/>
@@ -3335,39 +3336,39 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="156" t="s">
+      <c r="E15" s="150" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="151"/>
+      <c r="G15" s="150" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="157"/>
-      <c r="G15" s="156" t="s">
+      <c r="H15" s="151"/>
+      <c r="I15" s="150" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="157"/>
-      <c r="I15" s="156" t="s">
+      <c r="J15" s="151"/>
+      <c r="K15" s="150" t="s">
         <v>25</v>
       </c>
-      <c r="J15" s="157"/>
-      <c r="K15" s="156" t="s">
+      <c r="L15" s="151"/>
+      <c r="M15" s="150" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="157"/>
-      <c r="M15" s="156" t="s">
-        <v>27</v>
-      </c>
-      <c r="N15" s="157"/>
+      <c r="N15" s="151"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="149" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="149"/>
+      <c r="B16" s="155" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="155"/>
       <c r="D16" s="29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E16" s="152"/>
       <c r="F16" s="153"/>
-      <c r="G16" s="154"/>
-      <c r="H16" s="155"/>
+      <c r="G16" s="157"/>
+      <c r="H16" s="158"/>
       <c r="I16" s="152"/>
       <c r="J16" s="153"/>
       <c r="K16" s="152"/>
@@ -3376,10 +3377,10 @@
       <c r="N16" s="153"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="149"/>
-      <c r="C17" s="149"/>
+      <c r="B17" s="155"/>
+      <c r="C17" s="155"/>
       <c r="D17" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" s="152"/>
       <c r="F17" s="153"/>
@@ -3397,27 +3398,27 @@
       <c r="C20" s="147"/>
       <c r="D20" s="147"/>
       <c r="E20" s="147" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F20" s="147"/>
       <c r="I20" s="147"/>
       <c r="J20" s="147"/>
       <c r="K20" s="147"/>
       <c r="L20" s="147" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M20" s="147"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B21" s="147" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21" s="147"/>
       <c r="D21" s="147"/>
       <c r="E21" s="148"/>
       <c r="F21" s="148"/>
       <c r="I21" s="147" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J21" s="147"/>
       <c r="K21" s="147"/>
@@ -3426,14 +3427,14 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B22" s="147" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" s="147"/>
       <c r="D22" s="147"/>
       <c r="E22" s="148"/>
       <c r="F22" s="148"/>
       <c r="I22" s="147" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J22" s="147"/>
       <c r="K22" s="147"/>
@@ -3442,14 +3443,14 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B23" s="147" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="147"/>
       <c r="D23" s="147"/>
       <c r="E23" s="148"/>
       <c r="F23" s="148"/>
       <c r="I23" s="147" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J23" s="147"/>
       <c r="K23" s="147"/>
@@ -3458,14 +3459,14 @@
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B24" s="147" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="147"/>
       <c r="D24" s="147"/>
       <c r="E24" s="148"/>
       <c r="F24" s="148"/>
       <c r="I24" s="147" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J24" s="147"/>
       <c r="K24" s="147"/>
@@ -3474,7 +3475,7 @@
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B25" s="147" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25" s="147"/>
       <c r="D25" s="147"/>
@@ -3483,7 +3484,7 @@
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B26" s="147" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26" s="147"/>
       <c r="D26" s="147"/>
@@ -3492,16 +3493,16 @@
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B27" s="147" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="147"/>
       <c r="D27" s="147"/>
-      <c r="E27" s="158"/>
-      <c r="F27" s="158"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="149"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B28" s="147" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="147"/>
       <c r="D28" s="147"/>
@@ -3510,7 +3511,7 @@
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B29" s="147" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" s="147"/>
       <c r="D29" s="147"/>
@@ -3519,7 +3520,7 @@
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B30" s="147" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C30" s="147"/>
       <c r="D30" s="147"/>
@@ -3528,86 +3529,6 @@
     </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="B3:C4"/>
@@ -3624,6 +3545,86 @@
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:M22"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\estimateTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF1F301-8CCF-4D28-AE4A-A0E69AE56248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A53E921-C777-47B7-958E-7C14FD3FA79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="45" yWindow="90" windowWidth="28755" windowHeight="15435" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="地震おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -1265,73 +1265,219 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1341,24 +1487,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1437,181 +1565,71 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1619,52 +1637,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2068,10 +2068,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="28"/>
@@ -2081,16 +2081,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="Q3" s="130"/>
+      <c r="R3" s="130"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="86"/>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="86"/>
-      <c r="R4" s="86"/>
+      <c r="O4" s="130"/>
+      <c r="P4" s="130"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="130"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="27"/>
@@ -2153,196 +2153,196 @@
       <c r="R10" s="23"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
+      <c r="B11" s="104"/>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
+      <c r="L11" s="104"/>
+      <c r="M11" s="104"/>
+      <c r="N11" s="104"/>
+      <c r="O11" s="104"/>
+      <c r="P11" s="104"/>
+      <c r="Q11" s="104"/>
+      <c r="R11" s="104"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="80" t="s">
+      <c r="A15" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="80"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="80"/>
-      <c r="M15" s="80"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="80"/>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="80"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="124"/>
+      <c r="J15" s="124"/>
+      <c r="K15" s="124"/>
+      <c r="L15" s="124"/>
+      <c r="M15" s="124"/>
+      <c r="N15" s="124"/>
+      <c r="O15" s="124"/>
+      <c r="P15" s="124"/>
+      <c r="Q15" s="124"/>
+      <c r="R15" s="124"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="81" t="s">
+      <c r="A18" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
-      <c r="M18" s="81"/>
-      <c r="N18" s="81"/>
-      <c r="O18" s="81"/>
-      <c r="P18" s="81"/>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="81"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="125"/>
+      <c r="J18" s="125"/>
+      <c r="K18" s="125"/>
+      <c r="L18" s="125"/>
+      <c r="M18" s="125"/>
+      <c r="N18" s="125"/>
+      <c r="O18" s="125"/>
+      <c r="P18" s="125"/>
+      <c r="Q18" s="125"/>
+      <c r="R18" s="125"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="80" t="s">
         <v>3</v>
       </c>
       <c r="B20" s="60"/>
       <c r="C20" s="60"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="62"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="62"/>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="62"/>
-      <c r="R20" s="63"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
+      <c r="L20" s="106"/>
+      <c r="M20" s="106"/>
+      <c r="N20" s="106"/>
+      <c r="O20" s="106"/>
+      <c r="P20" s="106"/>
+      <c r="Q20" s="106"/>
+      <c r="R20" s="107"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="55"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="65"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="65"/>
-      <c r="M21" s="65"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="65"/>
-      <c r="P21" s="65"/>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="66"/>
+      <c r="A21" s="81"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="109"/>
+      <c r="F21" s="109"/>
+      <c r="G21" s="109"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="109"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="110"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="56"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
       <c r="D22" s="22"/>
       <c r="L22" s="21"/>
-      <c r="M22" s="67" t="s">
+      <c r="M22" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="68"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="72"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="73"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="116"/>
+      <c r="Q22" s="116"/>
+      <c r="R22" s="117"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="55"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="74"/>
-      <c r="P23" s="75"/>
-      <c r="Q23" s="75"/>
-      <c r="R23" s="76"/>
+      <c r="A23" s="81"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="126"/>
+      <c r="E23" s="127"/>
+      <c r="F23" s="127"/>
+      <c r="G23" s="127"/>
+      <c r="H23" s="127"/>
+      <c r="I23" s="127"/>
+      <c r="J23" s="127"/>
+      <c r="K23" s="127"/>
+      <c r="L23" s="128"/>
+      <c r="M23" s="111"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="118"/>
+      <c r="P23" s="119"/>
+      <c r="Q23" s="119"/>
+      <c r="R23" s="120"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="55"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="85"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="67"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="74"/>
-      <c r="P24" s="75"/>
-      <c r="Q24" s="75"/>
-      <c r="R24" s="76"/>
+      <c r="A24" s="81"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="127"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="127"/>
+      <c r="H24" s="127"/>
+      <c r="I24" s="127"/>
+      <c r="J24" s="127"/>
+      <c r="K24" s="127"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="111"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="118"/>
+      <c r="P24" s="119"/>
+      <c r="Q24" s="119"/>
+      <c r="R24" s="120"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="55"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="85"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="83"/>
-      <c r="L25" s="84"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="74"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="76"/>
+      <c r="A25" s="81"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="129"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="127"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="127"/>
+      <c r="I25" s="127"/>
+      <c r="J25" s="127"/>
+      <c r="K25" s="127"/>
+      <c r="L25" s="128"/>
+      <c r="M25" s="111"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="118"/>
+      <c r="P25" s="119"/>
+      <c r="Q25" s="119"/>
+      <c r="R25" s="120"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="55"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
+      <c r="A26" s="81"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
       <c r="D26" s="20"/>
       <c r="E26" s="19"/>
       <c r="F26" s="18"/>
@@ -2352,17 +2352,17 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="16"/>
-      <c r="M26" s="67"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="75"/>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="76"/>
+      <c r="M26" s="111"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="118"/>
+      <c r="P26" s="119"/>
+      <c r="Q26" s="119"/>
+      <c r="R26" s="120"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="55"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="56"/>
+      <c r="A27" s="81"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="62"/>
       <c r="D27" s="15"/>
       <c r="F27" s="13"/>
       <c r="G27" s="14"/>
@@ -2370,17 +2370,17 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="L27" s="11"/>
-      <c r="M27" s="67"/>
-      <c r="N27" s="68"/>
-      <c r="O27" s="74"/>
-      <c r="P27" s="75"/>
-      <c r="Q27" s="75"/>
-      <c r="R27" s="76"/>
+      <c r="M27" s="111"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="118"/>
+      <c r="P27" s="119"/>
+      <c r="Q27" s="119"/>
+      <c r="R27" s="120"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="57"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
+      <c r="A28" s="89"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
       <c r="D28" s="10"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -2390,185 +2390,185 @@
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="8"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="70"/>
-      <c r="O28" s="77"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="78"/>
-      <c r="R28" s="79"/>
+      <c r="M28" s="113"/>
+      <c r="N28" s="114"/>
+      <c r="O28" s="121"/>
+      <c r="P28" s="122"/>
+      <c r="Q28" s="122"/>
+      <c r="R28" s="123"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="59" t="s">
+      <c r="A31" s="80" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="60"/>
       <c r="C31" s="60"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="92"/>
-      <c r="H31" s="92"/>
-      <c r="I31" s="92"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="85"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="85"/>
       <c r="J31" s="60" t="s">
         <v>7</v>
       </c>
       <c r="K31" s="60"/>
       <c r="L31" s="60"/>
-      <c r="M31" s="92"/>
-      <c r="N31" s="92"/>
-      <c r="O31" s="92"/>
-      <c r="P31" s="92"/>
-      <c r="Q31" s="92"/>
-      <c r="R31" s="93"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="85"/>
+      <c r="P31" s="85"/>
+      <c r="Q31" s="85"/>
+      <c r="R31" s="86"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="55"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="94"/>
-      <c r="E32" s="94"/>
-      <c r="F32" s="94"/>
-      <c r="G32" s="94"/>
-      <c r="H32" s="94"/>
-      <c r="I32" s="94"/>
-      <c r="J32" s="56"/>
-      <c r="K32" s="56"/>
-      <c r="L32" s="56"/>
-      <c r="M32" s="94"/>
-      <c r="N32" s="94"/>
-      <c r="O32" s="94"/>
-      <c r="P32" s="94"/>
-      <c r="Q32" s="94"/>
-      <c r="R32" s="95"/>
+      <c r="A32" s="81"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="87"/>
+      <c r="H32" s="87"/>
+      <c r="I32" s="87"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
+      <c r="L32" s="62"/>
+      <c r="M32" s="87"/>
+      <c r="N32" s="87"/>
+      <c r="O32" s="87"/>
+      <c r="P32" s="87"/>
+      <c r="Q32" s="87"/>
+      <c r="R32" s="88"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="159"/>
-      <c r="E33" s="160"/>
-      <c r="F33" s="160"/>
-      <c r="G33" s="160"/>
-      <c r="H33" s="160"/>
-      <c r="I33" s="160"/>
-      <c r="J33" s="160"/>
-      <c r="K33" s="160"/>
-      <c r="L33" s="160"/>
-      <c r="M33" s="160"/>
-      <c r="N33" s="160"/>
-      <c r="O33" s="160"/>
-      <c r="P33" s="160"/>
-      <c r="Q33" s="160"/>
-      <c r="R33" s="161"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="98"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="98"/>
+      <c r="H33" s="98"/>
+      <c r="I33" s="98"/>
+      <c r="J33" s="98"/>
+      <c r="K33" s="98"/>
+      <c r="L33" s="98"/>
+      <c r="M33" s="98"/>
+      <c r="N33" s="98"/>
+      <c r="O33" s="98"/>
+      <c r="P33" s="98"/>
+      <c r="Q33" s="98"/>
+      <c r="R33" s="99"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="55"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="162"/>
-      <c r="E34" s="163"/>
-      <c r="F34" s="163"/>
-      <c r="G34" s="163"/>
-      <c r="H34" s="163"/>
-      <c r="I34" s="163"/>
-      <c r="J34" s="163"/>
-      <c r="K34" s="163"/>
-      <c r="L34" s="163"/>
-      <c r="M34" s="163"/>
-      <c r="N34" s="163"/>
-      <c r="O34" s="163"/>
-      <c r="P34" s="163"/>
-      <c r="Q34" s="163"/>
-      <c r="R34" s="164"/>
+      <c r="A34" s="81"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="101"/>
+      <c r="F34" s="101"/>
+      <c r="G34" s="101"/>
+      <c r="H34" s="101"/>
+      <c r="I34" s="101"/>
+      <c r="J34" s="101"/>
+      <c r="K34" s="101"/>
+      <c r="L34" s="101"/>
+      <c r="M34" s="101"/>
+      <c r="N34" s="101"/>
+      <c r="O34" s="101"/>
+      <c r="P34" s="101"/>
+      <c r="Q34" s="101"/>
+      <c r="R34" s="102"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="55" t="s">
+      <c r="A35" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="97"/>
-      <c r="F35" s="97"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="97"/>
-      <c r="I35" s="97"/>
-      <c r="J35" s="97"/>
-      <c r="K35" s="97"/>
-      <c r="L35" s="97"/>
-      <c r="M35" s="97"/>
-      <c r="N35" s="97"/>
-      <c r="O35" s="97"/>
-      <c r="P35" s="97"/>
-      <c r="Q35" s="97"/>
-      <c r="R35" s="98"/>
+      <c r="B35" s="62"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="91"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="92"/>
+      <c r="H35" s="92"/>
+      <c r="I35" s="92"/>
+      <c r="J35" s="92"/>
+      <c r="K35" s="92"/>
+      <c r="L35" s="92"/>
+      <c r="M35" s="92"/>
+      <c r="N35" s="92"/>
+      <c r="O35" s="92"/>
+      <c r="P35" s="92"/>
+      <c r="Q35" s="92"/>
+      <c r="R35" s="93"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="57"/>
-      <c r="B36" s="58"/>
-      <c r="C36" s="58"/>
-      <c r="D36" s="99"/>
-      <c r="E36" s="100"/>
-      <c r="F36" s="100"/>
-      <c r="G36" s="100"/>
-      <c r="H36" s="100"/>
-      <c r="I36" s="100"/>
-      <c r="J36" s="100"/>
-      <c r="K36" s="100"/>
-      <c r="L36" s="100"/>
-      <c r="M36" s="100"/>
-      <c r="N36" s="100"/>
-      <c r="O36" s="100"/>
-      <c r="P36" s="100"/>
-      <c r="Q36" s="100"/>
-      <c r="R36" s="101"/>
+      <c r="A36" s="89"/>
+      <c r="B36" s="90"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="94"/>
+      <c r="E36" s="95"/>
+      <c r="F36" s="95"/>
+      <c r="G36" s="95"/>
+      <c r="H36" s="95"/>
+      <c r="I36" s="95"/>
+      <c r="J36" s="95"/>
+      <c r="K36" s="95"/>
+      <c r="L36" s="95"/>
+      <c r="M36" s="95"/>
+      <c r="N36" s="95"/>
+      <c r="O36" s="95"/>
+      <c r="P36" s="95"/>
+      <c r="Q36" s="95"/>
+      <c r="R36" s="96"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="87"/>
-      <c r="B37" s="88"/>
-      <c r="C37" s="88"/>
-      <c r="D37" s="88"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="88"/>
-      <c r="H37" s="88"/>
-      <c r="I37" s="88"/>
-      <c r="J37" s="88"/>
-      <c r="K37" s="88"/>
-      <c r="L37" s="88"/>
-      <c r="M37" s="88"/>
-      <c r="N37" s="88"/>
-      <c r="O37" s="88"/>
-      <c r="P37" s="88"/>
-      <c r="Q37" s="88"/>
-      <c r="R37" s="88"/>
+      <c r="A37" s="82"/>
+      <c r="B37" s="83"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="83"/>
+      <c r="K37" s="83"/>
+      <c r="L37" s="83"/>
+      <c r="M37" s="83"/>
+      <c r="N37" s="83"/>
+      <c r="O37" s="83"/>
+      <c r="P37" s="83"/>
+      <c r="Q37" s="83"/>
+      <c r="R37" s="83"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="89"/>
-      <c r="B38" s="89"/>
-      <c r="C38" s="89"/>
-      <c r="D38" s="89"/>
-      <c r="E38" s="89"/>
-      <c r="F38" s="89"/>
-      <c r="G38" s="89"/>
-      <c r="H38" s="89"/>
-      <c r="I38" s="89"/>
-      <c r="J38" s="89"/>
-      <c r="K38" s="89"/>
-      <c r="L38" s="89"/>
-      <c r="M38" s="89"/>
-      <c r="N38" s="89"/>
-      <c r="O38" s="89"/>
-      <c r="P38" s="89"/>
-      <c r="Q38" s="89"/>
-      <c r="R38" s="89"/>
+      <c r="A38" s="84"/>
+      <c r="B38" s="84"/>
+      <c r="C38" s="84"/>
+      <c r="D38" s="84"/>
+      <c r="E38" s="84"/>
+      <c r="F38" s="84"/>
+      <c r="G38" s="84"/>
+      <c r="H38" s="84"/>
+      <c r="I38" s="84"/>
+      <c r="J38" s="84"/>
+      <c r="K38" s="84"/>
+      <c r="L38" s="84"/>
+      <c r="M38" s="84"/>
+      <c r="N38" s="84"/>
+      <c r="O38" s="84"/>
+      <c r="P38" s="84"/>
+      <c r="Q38" s="84"/>
+      <c r="R38" s="84"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="59" t="s">
+      <c r="A39" s="80" t="s">
         <v>10</v>
       </c>
       <c r="B39" s="60"/>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="E39" s="60"/>
       <c r="F39" s="60"/>
-      <c r="G39" s="90"/>
+      <c r="G39" s="74"/>
       <c r="H39" s="60" t="s">
         <v>10</v>
       </c>
@@ -2589,145 +2589,145 @@
       </c>
       <c r="L39" s="60"/>
       <c r="M39" s="60"/>
-      <c r="N39" s="90"/>
+      <c r="N39" s="74"/>
       <c r="O39" s="60" t="s">
         <v>21</v>
       </c>
       <c r="P39" s="60"/>
       <c r="Q39" s="60"/>
-      <c r="R39" s="110"/>
+      <c r="R39" s="61"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="55"/>
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="56"/>
-      <c r="K40" s="56"/>
-      <c r="L40" s="56"/>
-      <c r="M40" s="56"/>
-      <c r="N40" s="91"/>
-      <c r="O40" s="56"/>
-      <c r="P40" s="56"/>
-      <c r="Q40" s="56"/>
-      <c r="R40" s="111"/>
+      <c r="A40" s="81"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="75"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="62"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="62"/>
+      <c r="M40" s="62"/>
+      <c r="N40" s="75"/>
+      <c r="O40" s="62"/>
+      <c r="P40" s="62"/>
+      <c r="Q40" s="62"/>
+      <c r="R40" s="63"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="104" t="s">
+      <c r="A41" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="B41" s="105"/>
-      <c r="C41" s="106"/>
-      <c r="D41" s="112"/>
-      <c r="E41" s="113"/>
-      <c r="F41" s="113"/>
-      <c r="G41" s="114"/>
-      <c r="H41" s="126" t="s">
+      <c r="B41" s="55"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="65"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="I41" s="127"/>
-      <c r="J41" s="128"/>
-      <c r="K41" s="112"/>
-      <c r="L41" s="113"/>
-      <c r="M41" s="113"/>
-      <c r="N41" s="114"/>
-      <c r="O41" s="118"/>
-      <c r="P41" s="118"/>
-      <c r="Q41" s="118"/>
-      <c r="R41" s="119"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="64"/>
+      <c r="L41" s="65"/>
+      <c r="M41" s="65"/>
+      <c r="N41" s="66"/>
+      <c r="O41" s="70"/>
+      <c r="P41" s="70"/>
+      <c r="Q41" s="70"/>
+      <c r="R41" s="71"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="107"/>
-      <c r="B42" s="108"/>
-      <c r="C42" s="109"/>
-      <c r="D42" s="115"/>
-      <c r="E42" s="116"/>
-      <c r="F42" s="116"/>
-      <c r="G42" s="117"/>
-      <c r="H42" s="129"/>
-      <c r="I42" s="130"/>
-      <c r="J42" s="131"/>
-      <c r="K42" s="115"/>
-      <c r="L42" s="116"/>
-      <c r="M42" s="116"/>
-      <c r="N42" s="117"/>
-      <c r="O42" s="118"/>
-      <c r="P42" s="118"/>
-      <c r="Q42" s="118"/>
-      <c r="R42" s="119"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="58"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="69"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="67"/>
+      <c r="L42" s="68"/>
+      <c r="M42" s="68"/>
+      <c r="N42" s="69"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="70"/>
+      <c r="Q42" s="70"/>
+      <c r="R42" s="71"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="104" t="s">
+      <c r="A43" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="B43" s="105"/>
-      <c r="C43" s="106"/>
-      <c r="D43" s="112"/>
-      <c r="E43" s="113"/>
-      <c r="F43" s="113"/>
-      <c r="G43" s="114"/>
-      <c r="H43" s="124" t="s">
+      <c r="B43" s="55"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="I43" s="105"/>
-      <c r="J43" s="106"/>
-      <c r="K43" s="112"/>
-      <c r="L43" s="113"/>
-      <c r="M43" s="113"/>
-      <c r="N43" s="114"/>
-      <c r="O43" s="118"/>
-      <c r="P43" s="118"/>
-      <c r="Q43" s="118"/>
-      <c r="R43" s="119"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="56"/>
+      <c r="K43" s="64"/>
+      <c r="L43" s="65"/>
+      <c r="M43" s="65"/>
+      <c r="N43" s="66"/>
+      <c r="O43" s="70"/>
+      <c r="P43" s="70"/>
+      <c r="Q43" s="70"/>
+      <c r="R43" s="71"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="107"/>
-      <c r="B44" s="108"/>
-      <c r="C44" s="109"/>
-      <c r="D44" s="115"/>
-      <c r="E44" s="116"/>
-      <c r="F44" s="116"/>
-      <c r="G44" s="117"/>
-      <c r="H44" s="125"/>
-      <c r="I44" s="108"/>
-      <c r="J44" s="109"/>
-      <c r="K44" s="115"/>
-      <c r="L44" s="116"/>
-      <c r="M44" s="116"/>
-      <c r="N44" s="117"/>
-      <c r="O44" s="118"/>
-      <c r="P44" s="118"/>
-      <c r="Q44" s="118"/>
-      <c r="R44" s="119"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="58"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="68"/>
+      <c r="F44" s="68"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="79"/>
+      <c r="I44" s="58"/>
+      <c r="J44" s="59"/>
+      <c r="K44" s="67"/>
+      <c r="L44" s="68"/>
+      <c r="M44" s="68"/>
+      <c r="N44" s="69"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="70"/>
+      <c r="Q44" s="70"/>
+      <c r="R44" s="71"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="102" t="s">
+      <c r="A45" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="103"/>
-      <c r="C45" s="103"/>
-      <c r="D45" s="122"/>
-      <c r="E45" s="122"/>
-      <c r="F45" s="122"/>
-      <c r="G45" s="123"/>
-      <c r="H45" s="103" t="s">
+      <c r="B45" s="53"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="76"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="77"/>
+      <c r="H45" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="I45" s="103"/>
-      <c r="J45" s="103"/>
-      <c r="K45" s="122"/>
-      <c r="L45" s="122"/>
-      <c r="M45" s="122"/>
-      <c r="N45" s="123"/>
-      <c r="O45" s="120"/>
-      <c r="P45" s="120"/>
-      <c r="Q45" s="120"/>
-      <c r="R45" s="121"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="76"/>
+      <c r="L45" s="76"/>
+      <c r="M45" s="76"/>
+      <c r="N45" s="77"/>
+      <c r="O45" s="72"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2739,233 +2739,233 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="30"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="136"/>
-      <c r="E49" s="137"/>
-      <c r="F49" s="137"/>
-      <c r="G49" s="137"/>
-      <c r="H49" s="145"/>
-      <c r="I49" s="136"/>
-      <c r="J49" s="137"/>
-      <c r="K49" s="137"/>
-      <c r="L49" s="137"/>
-      <c r="M49" s="145"/>
-      <c r="N49" s="136"/>
-      <c r="O49" s="137"/>
-      <c r="P49" s="137"/>
-      <c r="Q49" s="137"/>
-      <c r="R49" s="138"/>
+      <c r="A49" s="131"/>
+      <c r="B49" s="132"/>
+      <c r="C49" s="133"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="50"/>
+      <c r="I49" s="40"/>
+      <c r="J49" s="41"/>
+      <c r="K49" s="41"/>
+      <c r="L49" s="41"/>
+      <c r="M49" s="50"/>
+      <c r="N49" s="40"/>
+      <c r="O49" s="41"/>
+      <c r="P49" s="41"/>
+      <c r="Q49" s="41"/>
+      <c r="R49" s="42"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="33"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="35"/>
-      <c r="D50" s="139"/>
-      <c r="E50" s="140"/>
-      <c r="F50" s="140"/>
-      <c r="G50" s="140"/>
-      <c r="H50" s="146"/>
-      <c r="I50" s="139"/>
-      <c r="J50" s="140"/>
-      <c r="K50" s="140"/>
-      <c r="L50" s="140"/>
-      <c r="M50" s="146"/>
-      <c r="N50" s="139"/>
-      <c r="O50" s="140"/>
-      <c r="P50" s="140"/>
-      <c r="Q50" s="140"/>
-      <c r="R50" s="141"/>
+      <c r="A50" s="134"/>
+      <c r="B50" s="135"/>
+      <c r="C50" s="136"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="51"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44"/>
+      <c r="L50" s="44"/>
+      <c r="M50" s="51"/>
+      <c r="N50" s="43"/>
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="45"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="46" t="s">
+      <c r="A51" s="147" t="s">
         <v>18</v>
       </c>
-      <c r="B51" s="47"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
-      <c r="G51" s="52"/>
-      <c r="H51" s="52"/>
-      <c r="I51" s="52"/>
-      <c r="J51" s="52"/>
-      <c r="K51" s="52"/>
-      <c r="L51" s="52"/>
-      <c r="M51" s="52"/>
-      <c r="N51" s="52"/>
-      <c r="O51" s="52"/>
-      <c r="P51" s="52"/>
-      <c r="Q51" s="52"/>
-      <c r="R51" s="142"/>
+      <c r="B51" s="148"/>
+      <c r="C51" s="149"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="46"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="46"/>
+      <c r="I51" s="46"/>
+      <c r="J51" s="46"/>
+      <c r="K51" s="46"/>
+      <c r="L51" s="46"/>
+      <c r="M51" s="46"/>
+      <c r="N51" s="46"/>
+      <c r="O51" s="46"/>
+      <c r="P51" s="46"/>
+      <c r="Q51" s="46"/>
+      <c r="R51" s="47"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="49"/>
-      <c r="B52" s="50"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
-      <c r="H52" s="52"/>
-      <c r="I52" s="52"/>
-      <c r="J52" s="52"/>
-      <c r="K52" s="52"/>
-      <c r="L52" s="52"/>
-      <c r="M52" s="52"/>
-      <c r="N52" s="52"/>
-      <c r="O52" s="52"/>
-      <c r="P52" s="52"/>
-      <c r="Q52" s="52"/>
-      <c r="R52" s="142"/>
+      <c r="A52" s="150"/>
+      <c r="B52" s="151"/>
+      <c r="C52" s="152"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="46"/>
+      <c r="I52" s="46"/>
+      <c r="J52" s="46"/>
+      <c r="K52" s="46"/>
+      <c r="L52" s="46"/>
+      <c r="M52" s="46"/>
+      <c r="N52" s="46"/>
+      <c r="O52" s="46"/>
+      <c r="P52" s="46"/>
+      <c r="Q52" s="46"/>
+      <c r="R52" s="47"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
       <c r="B53" s="4"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="133"/>
-      <c r="E53" s="134"/>
-      <c r="F53" s="134"/>
-      <c r="G53" s="134"/>
-      <c r="H53" s="143"/>
-      <c r="I53" s="133"/>
-      <c r="J53" s="134"/>
-      <c r="K53" s="134"/>
-      <c r="L53" s="134"/>
-      <c r="M53" s="143"/>
-      <c r="N53" s="133"/>
-      <c r="O53" s="134"/>
-      <c r="P53" s="134"/>
-      <c r="Q53" s="134"/>
-      <c r="R53" s="135"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="37"/>
+      <c r="J53" s="38"/>
+      <c r="K53" s="38"/>
+      <c r="L53" s="38"/>
+      <c r="M53" s="48"/>
+      <c r="N53" s="37"/>
+      <c r="O53" s="38"/>
+      <c r="P53" s="38"/>
+      <c r="Q53" s="38"/>
+      <c r="R53" s="39"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="40" t="s">
+      <c r="A54" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="41"/>
-      <c r="C54" s="42"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="36"/>
-      <c r="I54" s="36"/>
-      <c r="J54" s="36"/>
-      <c r="K54" s="36"/>
-      <c r="L54" s="36"/>
-      <c r="M54" s="36"/>
-      <c r="N54" s="36"/>
-      <c r="O54" s="36"/>
-      <c r="P54" s="36"/>
-      <c r="Q54" s="36"/>
-      <c r="R54" s="37"/>
+      <c r="B54" s="142"/>
+      <c r="C54" s="143"/>
+      <c r="D54" s="137"/>
+      <c r="E54" s="137"/>
+      <c r="F54" s="137"/>
+      <c r="G54" s="137"/>
+      <c r="H54" s="137"/>
+      <c r="I54" s="137"/>
+      <c r="J54" s="137"/>
+      <c r="K54" s="137"/>
+      <c r="L54" s="137"/>
+      <c r="M54" s="137"/>
+      <c r="N54" s="137"/>
+      <c r="O54" s="137"/>
+      <c r="P54" s="137"/>
+      <c r="Q54" s="137"/>
+      <c r="R54" s="138"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="43"/>
-      <c r="B55" s="44"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="38"/>
-      <c r="I55" s="38"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="38"/>
-      <c r="L55" s="38"/>
-      <c r="M55" s="38"/>
-      <c r="N55" s="38"/>
-      <c r="O55" s="38"/>
-      <c r="P55" s="38"/>
-      <c r="Q55" s="38"/>
-      <c r="R55" s="39"/>
+      <c r="A55" s="144"/>
+      <c r="B55" s="145"/>
+      <c r="C55" s="146"/>
+      <c r="D55" s="139"/>
+      <c r="E55" s="139"/>
+      <c r="F55" s="139"/>
+      <c r="G55" s="139"/>
+      <c r="H55" s="139"/>
+      <c r="I55" s="139"/>
+      <c r="J55" s="139"/>
+      <c r="K55" s="139"/>
+      <c r="L55" s="139"/>
+      <c r="M55" s="139"/>
+      <c r="N55" s="139"/>
+      <c r="O55" s="139"/>
+      <c r="P55" s="139"/>
+      <c r="Q55" s="139"/>
+      <c r="R55" s="140"/>
     </row>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="40" t="s">
+      <c r="A56" s="141" t="s">
         <v>20</v>
       </c>
-      <c r="B56" s="41"/>
-      <c r="C56" s="42"/>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
-      <c r="H56" s="36"/>
-      <c r="I56" s="36"/>
-      <c r="J56" s="36"/>
-      <c r="K56" s="36"/>
-      <c r="L56" s="36"/>
-      <c r="M56" s="36"/>
-      <c r="N56" s="36"/>
-      <c r="O56" s="36"/>
-      <c r="P56" s="36"/>
-      <c r="Q56" s="36"/>
-      <c r="R56" s="37"/>
+      <c r="B56" s="142"/>
+      <c r="C56" s="143"/>
+      <c r="D56" s="137"/>
+      <c r="E56" s="137"/>
+      <c r="F56" s="137"/>
+      <c r="G56" s="137"/>
+      <c r="H56" s="137"/>
+      <c r="I56" s="137"/>
+      <c r="J56" s="137"/>
+      <c r="K56" s="137"/>
+      <c r="L56" s="137"/>
+      <c r="M56" s="137"/>
+      <c r="N56" s="137"/>
+      <c r="O56" s="137"/>
+      <c r="P56" s="137"/>
+      <c r="Q56" s="137"/>
+      <c r="R56" s="138"/>
     </row>
     <row r="57" spans="1:18" s="2" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="43"/>
-      <c r="B57" s="44"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="38"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="38"/>
-      <c r="L57" s="38"/>
-      <c r="M57" s="38"/>
-      <c r="N57" s="38"/>
-      <c r="O57" s="38"/>
-      <c r="P57" s="38"/>
-      <c r="Q57" s="38"/>
-      <c r="R57" s="39"/>
+      <c r="A57" s="144"/>
+      <c r="B57" s="145"/>
+      <c r="C57" s="146"/>
+      <c r="D57" s="139"/>
+      <c r="E57" s="139"/>
+      <c r="F57" s="139"/>
+      <c r="G57" s="139"/>
+      <c r="H57" s="139"/>
+      <c r="I57" s="139"/>
+      <c r="J57" s="139"/>
+      <c r="K57" s="139"/>
+      <c r="L57" s="139"/>
+      <c r="M57" s="139"/>
+      <c r="N57" s="139"/>
+      <c r="O57" s="139"/>
+      <c r="P57" s="139"/>
+      <c r="Q57" s="139"/>
+      <c r="R57" s="140"/>
     </row>
     <row r="58" spans="1:18" s="2" customFormat="1" ht="27" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D58" s="144"/>
-      <c r="E58" s="144"/>
-      <c r="F58" s="144"/>
-      <c r="G58" s="144"/>
-      <c r="H58" s="144"/>
-      <c r="I58" s="144"/>
-      <c r="J58" s="144"/>
-      <c r="K58" s="144"/>
-      <c r="L58" s="144"/>
-      <c r="M58" s="144"/>
-      <c r="N58" s="144"/>
-      <c r="O58" s="144"/>
-      <c r="P58" s="144"/>
-      <c r="Q58" s="144"/>
-      <c r="R58" s="144"/>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="49"/>
+      <c r="J58" s="49"/>
+      <c r="K58" s="49"/>
+      <c r="L58" s="49"/>
+      <c r="M58" s="49"/>
+      <c r="N58" s="49"/>
+      <c r="O58" s="49"/>
+      <c r="P58" s="49"/>
+      <c r="Q58" s="49"/>
+      <c r="R58" s="49"/>
     </row>
     <row r="59" spans="1:18" s="2" customFormat="1" ht="30.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D59" s="132" t="str">
+      <c r="D59" s="36" t="str">
         <f>IF(MOD(D58,1000)=0,"千円単位",IF(MOD(D58,100)=0,"百円単位",IF(MOD(D58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="E59" s="132"/>
-      <c r="F59" s="132"/>
-      <c r="G59" s="132"/>
-      <c r="H59" s="132"/>
-      <c r="I59" s="132" t="str">
+      <c r="E59" s="36"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="36" t="str">
         <f>IF(MOD(I58,1000)=0,"千円単位",IF(MOD(I58,100)=0,"百円単位",IF(MOD(I58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="J59" s="132"/>
-      <c r="K59" s="132"/>
-      <c r="L59" s="132"/>
-      <c r="M59" s="132"/>
-      <c r="N59" s="132" t="str">
+      <c r="J59" s="36"/>
+      <c r="K59" s="36"/>
+      <c r="L59" s="36"/>
+      <c r="M59" s="36"/>
+      <c r="N59" s="36" t="str">
         <f>IF(MOD(N58,1000)=0,"千円単位",IF(MOD(N58,100)=0,"百円単位",IF(MOD(N58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="O59" s="132"/>
-      <c r="P59" s="132"/>
-      <c r="Q59" s="132"/>
-      <c r="R59" s="132"/>
+      <c r="O59" s="36"/>
+      <c r="P59" s="36"/>
+      <c r="Q59" s="36"/>
+      <c r="R59" s="36"/>
     </row>
     <row r="60" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="61" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2977,20 +2977,40 @@
     <row r="67" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="I59:M59"/>
-    <mergeCell ref="N59:R59"/>
-    <mergeCell ref="N53:R53"/>
-    <mergeCell ref="N49:R50"/>
-    <mergeCell ref="N51:R52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="I58:M58"/>
-    <mergeCell ref="N58:R58"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="I53:M53"/>
-    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="N56:R57"/>
+    <mergeCell ref="D54:H55"/>
+    <mergeCell ref="I54:M55"/>
+    <mergeCell ref="N54:R55"/>
+    <mergeCell ref="A54:C55"/>
+    <mergeCell ref="A56:C57"/>
+    <mergeCell ref="D56:H57"/>
+    <mergeCell ref="I56:M57"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="I51:M52"/>
+    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A22:C28"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:R21"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="O22:R28"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="D33:R34"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="H45:J45"/>
     <mergeCell ref="A43:C44"/>
@@ -3006,40 +3026,20 @@
     <mergeCell ref="D43:G44"/>
     <mergeCell ref="H43:J44"/>
     <mergeCell ref="D41:G42"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="D31:I32"/>
-    <mergeCell ref="D33:R34"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A22:C28"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:R21"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="O22:R28"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="N56:R57"/>
-    <mergeCell ref="D54:H55"/>
-    <mergeCell ref="I54:M55"/>
-    <mergeCell ref="N54:R55"/>
-    <mergeCell ref="A54:C55"/>
-    <mergeCell ref="A56:C57"/>
-    <mergeCell ref="D56:H57"/>
-    <mergeCell ref="I56:M57"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="I51:M52"/>
-    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="I59:M59"/>
+    <mergeCell ref="N59:R59"/>
+    <mergeCell ref="N53:R53"/>
+    <mergeCell ref="N49:R50"/>
+    <mergeCell ref="N51:R52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="I58:M58"/>
+    <mergeCell ref="N58:R58"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="I53:M53"/>
+    <mergeCell ref="I49:M50"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="D51:R52">
@@ -3083,7 +3083,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D737899-3511-4F7A-96FD-F5F4470F525C}">
-  <dimension ref="B2:N30"/>
+  <dimension ref="B2:N28"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="15" width="4.625" customWidth="1"/>
@@ -3093,26 +3093,26 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="154" t="s">
+      <c r="E2" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="154"/>
-      <c r="G2" s="154" t="s">
+      <c r="F2" s="161"/>
+      <c r="G2" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="154"/>
-      <c r="I2" s="154" t="s">
+      <c r="H2" s="161"/>
+      <c r="I2" s="161" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="154"/>
-      <c r="K2" s="154" t="s">
+      <c r="J2" s="161"/>
+      <c r="K2" s="161" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="154"/>
-      <c r="M2" s="154" t="s">
+      <c r="L2" s="161"/>
+      <c r="M2" s="161" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="154"/>
+      <c r="N2" s="161"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B3" s="155" t="s">
@@ -3169,26 +3169,26 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="150" t="s">
+      <c r="E6" s="162" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="151"/>
-      <c r="G6" s="150" t="s">
+      <c r="F6" s="163"/>
+      <c r="G6" s="162" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="151"/>
-      <c r="I6" s="150" t="s">
+      <c r="H6" s="163"/>
+      <c r="I6" s="162" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="151"/>
-      <c r="K6" s="150" t="s">
+      <c r="J6" s="163"/>
+      <c r="K6" s="162" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="151"/>
-      <c r="M6" s="150" t="s">
+      <c r="L6" s="163"/>
+      <c r="M6" s="162" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="151"/>
+      <c r="N6" s="163"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B7" s="155" t="s">
@@ -3198,16 +3198,16 @@
       <c r="D7" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="152"/>
-      <c r="F7" s="153"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="158"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="153"/>
-      <c r="K7" s="152"/>
-      <c r="L7" s="153"/>
-      <c r="M7" s="152"/>
-      <c r="N7" s="153"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="160"/>
+      <c r="I7" s="157"/>
+      <c r="J7" s="158"/>
+      <c r="K7" s="157"/>
+      <c r="L7" s="158"/>
+      <c r="M7" s="157"/>
+      <c r="N7" s="158"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B8" s="155"/>
@@ -3215,16 +3215,16 @@
       <c r="D8" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="152"/>
-      <c r="F8" s="153"/>
-      <c r="G8" s="152"/>
-      <c r="H8" s="153"/>
-      <c r="I8" s="152"/>
-      <c r="J8" s="153"/>
-      <c r="K8" s="152"/>
-      <c r="L8" s="153"/>
-      <c r="M8" s="152"/>
-      <c r="N8" s="153"/>
+      <c r="E8" s="157"/>
+      <c r="F8" s="158"/>
+      <c r="G8" s="157"/>
+      <c r="H8" s="158"/>
+      <c r="I8" s="157"/>
+      <c r="J8" s="158"/>
+      <c r="K8" s="157"/>
+      <c r="L8" s="158"/>
+      <c r="M8" s="157"/>
+      <c r="N8" s="158"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
@@ -3245,26 +3245,26 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="150" t="s">
+      <c r="E10" s="162" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="151"/>
-      <c r="G10" s="150" t="s">
+      <c r="F10" s="163"/>
+      <c r="G10" s="162" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="151"/>
-      <c r="I10" s="150" t="s">
+      <c r="H10" s="163"/>
+      <c r="I10" s="162" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="151"/>
-      <c r="K10" s="150" t="s">
+      <c r="J10" s="163"/>
+      <c r="K10" s="162" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="151"/>
-      <c r="M10" s="150" t="s">
+      <c r="L10" s="163"/>
+      <c r="M10" s="162" t="s">
         <v>26</v>
       </c>
-      <c r="N10" s="151"/>
+      <c r="N10" s="163"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B11" s="155" t="s">
@@ -3274,16 +3274,16 @@
       <c r="D11" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="152"/>
-      <c r="F11" s="153"/>
-      <c r="G11" s="157"/>
-      <c r="H11" s="158"/>
-      <c r="I11" s="152"/>
-      <c r="J11" s="153"/>
-      <c r="K11" s="152"/>
-      <c r="L11" s="153"/>
-      <c r="M11" s="152"/>
-      <c r="N11" s="153"/>
+      <c r="E11" s="157"/>
+      <c r="F11" s="158"/>
+      <c r="G11" s="159"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="157"/>
+      <c r="J11" s="158"/>
+      <c r="K11" s="157"/>
+      <c r="L11" s="158"/>
+      <c r="M11" s="157"/>
+      <c r="N11" s="158"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B12" s="155"/>
@@ -3291,16 +3291,16 @@
       <c r="D12" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="152"/>
-      <c r="F12" s="153"/>
-      <c r="G12" s="152"/>
-      <c r="H12" s="153"/>
-      <c r="I12" s="152"/>
-      <c r="J12" s="153"/>
-      <c r="K12" s="152"/>
-      <c r="L12" s="153"/>
-      <c r="M12" s="152"/>
-      <c r="N12" s="153"/>
+      <c r="E12" s="157"/>
+      <c r="F12" s="158"/>
+      <c r="G12" s="157"/>
+      <c r="H12" s="158"/>
+      <c r="I12" s="157"/>
+      <c r="J12" s="158"/>
+      <c r="K12" s="157"/>
+      <c r="L12" s="158"/>
+      <c r="M12" s="157"/>
+      <c r="N12" s="158"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
@@ -3336,26 +3336,26 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="150" t="s">
+      <c r="E15" s="162" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="151"/>
-      <c r="G15" s="150" t="s">
+      <c r="F15" s="163"/>
+      <c r="G15" s="162" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="151"/>
-      <c r="I15" s="150" t="s">
+      <c r="H15" s="163"/>
+      <c r="I15" s="162" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="151"/>
-      <c r="K15" s="150" t="s">
+      <c r="J15" s="163"/>
+      <c r="K15" s="162" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="151"/>
-      <c r="M15" s="150" t="s">
+      <c r="L15" s="163"/>
+      <c r="M15" s="162" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="151"/>
+      <c r="N15" s="163"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B16" s="155" t="s">
@@ -3365,16 +3365,16 @@
       <c r="D16" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="152"/>
-      <c r="F16" s="153"/>
-      <c r="G16" s="157"/>
-      <c r="H16" s="158"/>
-      <c r="I16" s="152"/>
-      <c r="J16" s="153"/>
-      <c r="K16" s="152"/>
-      <c r="L16" s="153"/>
-      <c r="M16" s="152"/>
-      <c r="N16" s="153"/>
+      <c r="E16" s="157"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="159"/>
+      <c r="H16" s="160"/>
+      <c r="I16" s="157"/>
+      <c r="J16" s="158"/>
+      <c r="K16" s="157"/>
+      <c r="L16" s="158"/>
+      <c r="M16" s="157"/>
+      <c r="N16" s="158"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B17" s="155"/>
@@ -3382,155 +3382,231 @@
       <c r="D17" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="152"/>
-      <c r="F17" s="153"/>
-      <c r="G17" s="152"/>
-      <c r="H17" s="153"/>
-      <c r="I17" s="152"/>
-      <c r="J17" s="153"/>
-      <c r="K17" s="152"/>
-      <c r="L17" s="153"/>
-      <c r="M17" s="152"/>
-      <c r="N17" s="153"/>
+      <c r="E17" s="157"/>
+      <c r="F17" s="158"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="158"/>
+      <c r="I17" s="157"/>
+      <c r="J17" s="158"/>
+      <c r="K17" s="157"/>
+      <c r="L17" s="158"/>
+      <c r="M17" s="157"/>
+      <c r="N17" s="158"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B20" s="147"/>
-      <c r="C20" s="147"/>
-      <c r="D20" s="147"/>
-      <c r="E20" s="147" t="s">
+      <c r="B20" s="153"/>
+      <c r="C20" s="153"/>
+      <c r="D20" s="153"/>
+      <c r="E20" s="153" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="147"/>
-      <c r="I20" s="147"/>
-      <c r="J20" s="147"/>
-      <c r="K20" s="147"/>
-      <c r="L20" s="147" t="s">
+      <c r="F20" s="153"/>
+      <c r="I20" s="153"/>
+      <c r="J20" s="153"/>
+      <c r="K20" s="153"/>
+      <c r="L20" s="153" t="s">
         <v>33</v>
       </c>
-      <c r="M20" s="147"/>
+      <c r="M20" s="153"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B21" s="147" t="s">
+      <c r="B21" s="153" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="147"/>
-      <c r="D21" s="147"/>
-      <c r="E21" s="148"/>
-      <c r="F21" s="148"/>
-      <c r="I21" s="147" t="s">
+      <c r="C21" s="153"/>
+      <c r="D21" s="153"/>
+      <c r="E21" s="154"/>
+      <c r="F21" s="154"/>
+      <c r="I21" s="153" t="s">
         <v>44</v>
       </c>
-      <c r="J21" s="147"/>
-      <c r="K21" s="147"/>
-      <c r="L21" s="148"/>
-      <c r="M21" s="148"/>
+      <c r="J21" s="153"/>
+      <c r="K21" s="153"/>
+      <c r="L21" s="154"/>
+      <c r="M21" s="154"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B22" s="147" t="s">
+      <c r="B22" s="153" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="147"/>
-      <c r="D22" s="147"/>
-      <c r="E22" s="148"/>
-      <c r="F22" s="148"/>
-      <c r="I22" s="147" t="s">
+      <c r="C22" s="153"/>
+      <c r="D22" s="153"/>
+      <c r="E22" s="154"/>
+      <c r="F22" s="154"/>
+      <c r="I22" s="153" t="s">
         <v>45</v>
       </c>
-      <c r="J22" s="147"/>
-      <c r="K22" s="147"/>
-      <c r="L22" s="148"/>
-      <c r="M22" s="148"/>
+      <c r="J22" s="153"/>
+      <c r="K22" s="153"/>
+      <c r="L22" s="154"/>
+      <c r="M22" s="154"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B23" s="147" t="s">
+      <c r="B23" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="147"/>
-      <c r="D23" s="147"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="148"/>
-      <c r="I23" s="147" t="s">
+      <c r="C23" s="153"/>
+      <c r="D23" s="153"/>
+      <c r="E23" s="154"/>
+      <c r="F23" s="154"/>
+      <c r="I23" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="J23" s="147"/>
-      <c r="K23" s="147"/>
-      <c r="L23" s="148"/>
-      <c r="M23" s="148"/>
+      <c r="J23" s="153"/>
+      <c r="K23" s="153"/>
+      <c r="L23" s="154"/>
+      <c r="M23" s="154"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B24" s="147" t="s">
+      <c r="B24" s="153" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="147"/>
-      <c r="D24" s="147"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="148"/>
-      <c r="I24" s="147" t="s">
+      <c r="C24" s="153"/>
+      <c r="D24" s="153"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="154"/>
+      <c r="I24" s="153" t="s">
         <v>47</v>
       </c>
-      <c r="J24" s="147"/>
-      <c r="K24" s="147"/>
-      <c r="L24" s="148"/>
-      <c r="M24" s="148"/>
+      <c r="J24" s="153"/>
+      <c r="K24" s="153"/>
+      <c r="L24" s="154"/>
+      <c r="M24" s="154"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B25" s="147" t="s">
+      <c r="B25" s="153" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="147"/>
-      <c r="D25" s="147"/>
-      <c r="E25" s="148"/>
-      <c r="F25" s="148"/>
+      <c r="C25" s="153"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="154"/>
+      <c r="I25" s="153" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" s="153"/>
+      <c r="K25" s="153"/>
+      <c r="L25" s="154"/>
+      <c r="M25" s="154"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B26" s="147" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="147"/>
-      <c r="D26" s="147"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="148"/>
+      <c r="B26" s="153" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="153"/>
+      <c r="D26" s="153"/>
+      <c r="E26" s="164"/>
+      <c r="F26" s="164"/>
+      <c r="I26" s="153" t="s">
+        <v>43</v>
+      </c>
+      <c r="J26" s="153"/>
+      <c r="K26" s="153"/>
+      <c r="L26" s="154"/>
+      <c r="M26" s="154"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B27" s="147" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="147"/>
-      <c r="D27" s="147"/>
-      <c r="E27" s="149"/>
-      <c r="F27" s="149"/>
+      <c r="B27" s="153" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="153"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="154"/>
+      <c r="F27" s="154"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B28" s="147" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="147"/>
-      <c r="D28" s="147"/>
-      <c r="E28" s="148"/>
-      <c r="F28" s="148"/>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B29" s="147" t="s">
+      <c r="B28" s="153" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="147"/>
-      <c r="D29" s="147"/>
-      <c r="E29" s="148"/>
-      <c r="F29" s="148"/>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B30" s="147" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="147"/>
-      <c r="D30" s="147"/>
-      <c r="E30" s="148"/>
-      <c r="F30" s="148"/>
+      <c r="C28" s="153"/>
+      <c r="D28" s="153"/>
+      <c r="E28" s="154"/>
+      <c r="F28" s="154"/>
     </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:M26"/>
     <mergeCell ref="B3:C4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
@@ -3545,86 +3621,6 @@
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:M22"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\estimateTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ohno\eruful\mitumo\storage\app\estimateTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A53E921-C777-47B7-958E-7C14FD3FA79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A918B56B-6B9C-459B-855C-21B8B0EFD99F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="90" windowWidth="28755" windowHeight="15435" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="地震おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -1265,219 +1265,73 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
     <xf numFmtId="179" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1487,6 +1341,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1565,71 +1437,199 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1637,34 +1637,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1762,9 +1762,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1802,7 +1802,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1908,7 +1908,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2050,7 +2050,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2068,10 +2068,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="103"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="28"/>
@@ -2081,16 +2081,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="130"/>
-      <c r="Q3" s="130"/>
-      <c r="R3" s="130"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+      <c r="R3" s="86"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="130"/>
-      <c r="P4" s="130"/>
-      <c r="Q4" s="130"/>
-      <c r="R4" s="130"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="86"/>
+      <c r="Q4" s="86"/>
+      <c r="R4" s="86"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="27"/>
@@ -2153,196 +2153,196 @@
       <c r="R10" s="23"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="104" t="s">
+      <c r="A11" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="104"/>
-      <c r="C11" s="104"/>
-      <c r="D11" s="104"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="104"/>
-      <c r="K11" s="104"/>
-      <c r="L11" s="104"/>
-      <c r="M11" s="104"/>
-      <c r="N11" s="104"/>
-      <c r="O11" s="104"/>
-      <c r="P11" s="104"/>
-      <c r="Q11" s="104"/>
-      <c r="R11" s="104"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="124" t="s">
+      <c r="A15" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="124"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="124"/>
-      <c r="E15" s="124"/>
-      <c r="F15" s="124"/>
-      <c r="G15" s="124"/>
-      <c r="H15" s="124"/>
-      <c r="I15" s="124"/>
-      <c r="J15" s="124"/>
-      <c r="K15" s="124"/>
-      <c r="L15" s="124"/>
-      <c r="M15" s="124"/>
-      <c r="N15" s="124"/>
-      <c r="O15" s="124"/>
-      <c r="P15" s="124"/>
-      <c r="Q15" s="124"/>
-      <c r="R15" s="124"/>
+      <c r="B15" s="80"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="80"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="125" t="s">
+      <c r="A18" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="125"/>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="125"/>
-      <c r="H18" s="125"/>
-      <c r="I18" s="125"/>
-      <c r="J18" s="125"/>
-      <c r="K18" s="125"/>
-      <c r="L18" s="125"/>
-      <c r="M18" s="125"/>
-      <c r="N18" s="125"/>
-      <c r="O18" s="125"/>
-      <c r="P18" s="125"/>
-      <c r="Q18" s="125"/>
-      <c r="R18" s="125"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="81"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="80" t="s">
+      <c r="A20" s="59" t="s">
         <v>3</v>
       </c>
       <c r="B20" s="60"/>
       <c r="C20" s="60"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="106"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="106"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="106"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="106"/>
-      <c r="N20" s="106"/>
-      <c r="O20" s="106"/>
-      <c r="P20" s="106"/>
-      <c r="Q20" s="106"/>
-      <c r="R20" s="107"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="63"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="81"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="108"/>
-      <c r="E21" s="109"/>
-      <c r="F21" s="109"/>
-      <c r="G21" s="109"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="109"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="110"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="65"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="66"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="81" t="s">
+      <c r="A22" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="22"/>
       <c r="L22" s="21"/>
-      <c r="M22" s="111" t="s">
+      <c r="M22" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="112"/>
-      <c r="O22" s="115"/>
-      <c r="P22" s="116"/>
-      <c r="Q22" s="116"/>
-      <c r="R22" s="117"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="81"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="126"/>
-      <c r="E23" s="127"/>
-      <c r="F23" s="127"/>
-      <c r="G23" s="127"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="127"/>
-      <c r="J23" s="127"/>
-      <c r="K23" s="127"/>
-      <c r="L23" s="128"/>
-      <c r="M23" s="111"/>
-      <c r="N23" s="112"/>
-      <c r="O23" s="118"/>
-      <c r="P23" s="119"/>
-      <c r="Q23" s="119"/>
-      <c r="R23" s="120"/>
+      <c r="A23" s="55"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="83"/>
+      <c r="J23" s="83"/>
+      <c r="K23" s="83"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="74"/>
+      <c r="P23" s="75"/>
+      <c r="Q23" s="75"/>
+      <c r="R23" s="76"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="81"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="129"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="127"/>
-      <c r="H24" s="127"/>
-      <c r="I24" s="127"/>
-      <c r="J24" s="127"/>
-      <c r="K24" s="127"/>
-      <c r="L24" s="128"/>
-      <c r="M24" s="111"/>
-      <c r="N24" s="112"/>
-      <c r="O24" s="118"/>
-      <c r="P24" s="119"/>
-      <c r="Q24" s="119"/>
-      <c r="R24" s="120"/>
+      <c r="A24" s="55"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="85"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="83"/>
+      <c r="J24" s="83"/>
+      <c r="K24" s="83"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="74"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="76"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="81"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="129"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="127"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="127"/>
-      <c r="J25" s="127"/>
-      <c r="K25" s="127"/>
-      <c r="L25" s="128"/>
-      <c r="M25" s="111"/>
-      <c r="N25" s="112"/>
-      <c r="O25" s="118"/>
-      <c r="P25" s="119"/>
-      <c r="Q25" s="119"/>
-      <c r="R25" s="120"/>
+      <c r="A25" s="55"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="83"/>
+      <c r="J25" s="83"/>
+      <c r="K25" s="83"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="74"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="76"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="81"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="56"/>
       <c r="D26" s="20"/>
       <c r="E26" s="19"/>
       <c r="F26" s="18"/>
@@ -2352,17 +2352,17 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="16"/>
-      <c r="M26" s="111"/>
-      <c r="N26" s="112"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="119"/>
-      <c r="Q26" s="119"/>
-      <c r="R26" s="120"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="75"/>
+      <c r="R26" s="76"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="81"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
       <c r="D27" s="15"/>
       <c r="F27" s="13"/>
       <c r="G27" s="14"/>
@@ -2370,17 +2370,17 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="L27" s="11"/>
-      <c r="M27" s="111"/>
-      <c r="N27" s="112"/>
-      <c r="O27" s="118"/>
-      <c r="P27" s="119"/>
-      <c r="Q27" s="119"/>
-      <c r="R27" s="120"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="68"/>
+      <c r="O27" s="74"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="75"/>
+      <c r="R27" s="76"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="89"/>
-      <c r="B28" s="90"/>
-      <c r="C28" s="90"/>
+      <c r="A28" s="57"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="58"/>
       <c r="D28" s="10"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -2390,185 +2390,185 @@
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="8"/>
-      <c r="M28" s="113"/>
-      <c r="N28" s="114"/>
-      <c r="O28" s="121"/>
-      <c r="P28" s="122"/>
-      <c r="Q28" s="122"/>
-      <c r="R28" s="123"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="70"/>
+      <c r="O28" s="77"/>
+      <c r="P28" s="78"/>
+      <c r="Q28" s="78"/>
+      <c r="R28" s="79"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="80" t="s">
+      <c r="A31" s="59" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="60"/>
       <c r="C31" s="60"/>
-      <c r="D31" s="85"/>
-      <c r="E31" s="85"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="85"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="92"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="92"/>
       <c r="J31" s="60" t="s">
         <v>7</v>
       </c>
       <c r="K31" s="60"/>
       <c r="L31" s="60"/>
-      <c r="M31" s="85"/>
-      <c r="N31" s="85"/>
-      <c r="O31" s="85"/>
-      <c r="P31" s="85"/>
-      <c r="Q31" s="85"/>
-      <c r="R31" s="86"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="92"/>
+      <c r="O31" s="92"/>
+      <c r="P31" s="92"/>
+      <c r="Q31" s="92"/>
+      <c r="R31" s="93"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="81"/>
-      <c r="B32" s="62"/>
-      <c r="C32" s="62"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="87"/>
-      <c r="F32" s="87"/>
-      <c r="G32" s="87"/>
-      <c r="H32" s="87"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
-      <c r="L32" s="62"/>
-      <c r="M32" s="87"/>
-      <c r="N32" s="87"/>
-      <c r="O32" s="87"/>
-      <c r="P32" s="87"/>
-      <c r="Q32" s="87"/>
-      <c r="R32" s="88"/>
+      <c r="A32" s="55"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
+      <c r="F32" s="94"/>
+      <c r="G32" s="94"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="94"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="94"/>
+      <c r="N32" s="94"/>
+      <c r="O32" s="94"/>
+      <c r="P32" s="94"/>
+      <c r="Q32" s="94"/>
+      <c r="R32" s="95"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="81" t="s">
+      <c r="A33" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="62"/>
-      <c r="C33" s="62"/>
-      <c r="D33" s="97"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="98"/>
-      <c r="H33" s="98"/>
-      <c r="I33" s="98"/>
-      <c r="J33" s="98"/>
-      <c r="K33" s="98"/>
-      <c r="L33" s="98"/>
-      <c r="M33" s="98"/>
-      <c r="N33" s="98"/>
-      <c r="O33" s="98"/>
-      <c r="P33" s="98"/>
-      <c r="Q33" s="98"/>
-      <c r="R33" s="99"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="102"/>
+      <c r="E33" s="103"/>
+      <c r="F33" s="103"/>
+      <c r="G33" s="103"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="103"/>
+      <c r="J33" s="103"/>
+      <c r="K33" s="103"/>
+      <c r="L33" s="103"/>
+      <c r="M33" s="103"/>
+      <c r="N33" s="103"/>
+      <c r="O33" s="103"/>
+      <c r="P33" s="103"/>
+      <c r="Q33" s="103"/>
+      <c r="R33" s="104"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="81"/>
-      <c r="B34" s="62"/>
-      <c r="C34" s="62"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="101"/>
-      <c r="F34" s="101"/>
-      <c r="G34" s="101"/>
-      <c r="H34" s="101"/>
-      <c r="I34" s="101"/>
-      <c r="J34" s="101"/>
-      <c r="K34" s="101"/>
-      <c r="L34" s="101"/>
-      <c r="M34" s="101"/>
-      <c r="N34" s="101"/>
-      <c r="O34" s="101"/>
-      <c r="P34" s="101"/>
-      <c r="Q34" s="101"/>
-      <c r="R34" s="102"/>
+      <c r="A34" s="55"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="106"/>
+      <c r="F34" s="106"/>
+      <c r="G34" s="106"/>
+      <c r="H34" s="106"/>
+      <c r="I34" s="106"/>
+      <c r="J34" s="106"/>
+      <c r="K34" s="106"/>
+      <c r="L34" s="106"/>
+      <c r="M34" s="106"/>
+      <c r="N34" s="106"/>
+      <c r="O34" s="106"/>
+      <c r="P34" s="106"/>
+      <c r="Q34" s="106"/>
+      <c r="R34" s="107"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="81" t="s">
+      <c r="A35" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="62"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="91"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="92"/>
-      <c r="H35" s="92"/>
-      <c r="I35" s="92"/>
-      <c r="J35" s="92"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="92"/>
-      <c r="M35" s="92"/>
-      <c r="N35" s="92"/>
-      <c r="O35" s="92"/>
-      <c r="P35" s="92"/>
-      <c r="Q35" s="92"/>
-      <c r="R35" s="93"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="97"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="97"/>
+      <c r="I35" s="97"/>
+      <c r="J35" s="97"/>
+      <c r="K35" s="97"/>
+      <c r="L35" s="97"/>
+      <c r="M35" s="97"/>
+      <c r="N35" s="97"/>
+      <c r="O35" s="97"/>
+      <c r="P35" s="97"/>
+      <c r="Q35" s="97"/>
+      <c r="R35" s="98"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="89"/>
-      <c r="B36" s="90"/>
-      <c r="C36" s="90"/>
-      <c r="D36" s="94"/>
-      <c r="E36" s="95"/>
-      <c r="F36" s="95"/>
-      <c r="G36" s="95"/>
-      <c r="H36" s="95"/>
-      <c r="I36" s="95"/>
-      <c r="J36" s="95"/>
-      <c r="K36" s="95"/>
-      <c r="L36" s="95"/>
-      <c r="M36" s="95"/>
-      <c r="N36" s="95"/>
-      <c r="O36" s="95"/>
-      <c r="P36" s="95"/>
-      <c r="Q36" s="95"/>
-      <c r="R36" s="96"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="99"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="100"/>
+      <c r="G36" s="100"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="100"/>
+      <c r="J36" s="100"/>
+      <c r="K36" s="100"/>
+      <c r="L36" s="100"/>
+      <c r="M36" s="100"/>
+      <c r="N36" s="100"/>
+      <c r="O36" s="100"/>
+      <c r="P36" s="100"/>
+      <c r="Q36" s="100"/>
+      <c r="R36" s="101"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="82"/>
-      <c r="B37" s="83"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="83"/>
-      <c r="L37" s="83"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="83"/>
-      <c r="O37" s="83"/>
-      <c r="P37" s="83"/>
-      <c r="Q37" s="83"/>
-      <c r="R37" s="83"/>
+      <c r="A37" s="87"/>
+      <c r="B37" s="88"/>
+      <c r="C37" s="88"/>
+      <c r="D37" s="88"/>
+      <c r="E37" s="88"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="88"/>
+      <c r="I37" s="88"/>
+      <c r="J37" s="88"/>
+      <c r="K37" s="88"/>
+      <c r="L37" s="88"/>
+      <c r="M37" s="88"/>
+      <c r="N37" s="88"/>
+      <c r="O37" s="88"/>
+      <c r="P37" s="88"/>
+      <c r="Q37" s="88"/>
+      <c r="R37" s="88"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="84"/>
-      <c r="B38" s="84"/>
-      <c r="C38" s="84"/>
-      <c r="D38" s="84"/>
-      <c r="E38" s="84"/>
-      <c r="F38" s="84"/>
-      <c r="G38" s="84"/>
-      <c r="H38" s="84"/>
-      <c r="I38" s="84"/>
-      <c r="J38" s="84"/>
-      <c r="K38" s="84"/>
-      <c r="L38" s="84"/>
-      <c r="M38" s="84"/>
-      <c r="N38" s="84"/>
-      <c r="O38" s="84"/>
-      <c r="P38" s="84"/>
-      <c r="Q38" s="84"/>
-      <c r="R38" s="84"/>
+      <c r="A38" s="89"/>
+      <c r="B38" s="89"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="89"/>
+      <c r="H38" s="89"/>
+      <c r="I38" s="89"/>
+      <c r="J38" s="89"/>
+      <c r="K38" s="89"/>
+      <c r="L38" s="89"/>
+      <c r="M38" s="89"/>
+      <c r="N38" s="89"/>
+      <c r="O38" s="89"/>
+      <c r="P38" s="89"/>
+      <c r="Q38" s="89"/>
+      <c r="R38" s="89"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="80" t="s">
+      <c r="A39" s="59" t="s">
         <v>10</v>
       </c>
       <c r="B39" s="60"/>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="E39" s="60"/>
       <c r="F39" s="60"/>
-      <c r="G39" s="74"/>
+      <c r="G39" s="90"/>
       <c r="H39" s="60" t="s">
         <v>10</v>
       </c>
@@ -2589,145 +2589,145 @@
       </c>
       <c r="L39" s="60"/>
       <c r="M39" s="60"/>
-      <c r="N39" s="74"/>
+      <c r="N39" s="90"/>
       <c r="O39" s="60" t="s">
         <v>21</v>
       </c>
       <c r="P39" s="60"/>
       <c r="Q39" s="60"/>
-      <c r="R39" s="61"/>
+      <c r="R39" s="116"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="81"/>
-      <c r="B40" s="62"/>
-      <c r="C40" s="62"/>
-      <c r="D40" s="62"/>
-      <c r="E40" s="62"/>
-      <c r="F40" s="62"/>
-      <c r="G40" s="75"/>
-      <c r="H40" s="62"/>
-      <c r="I40" s="62"/>
-      <c r="J40" s="62"/>
-      <c r="K40" s="62"/>
-      <c r="L40" s="62"/>
-      <c r="M40" s="62"/>
-      <c r="N40" s="75"/>
-      <c r="O40" s="62"/>
-      <c r="P40" s="62"/>
-      <c r="Q40" s="62"/>
-      <c r="R40" s="63"/>
+      <c r="A40" s="55"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="56"/>
+      <c r="N40" s="91"/>
+      <c r="O40" s="56"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="56"/>
+      <c r="R40" s="117"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="54" t="s">
+      <c r="A41" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="B41" s="55"/>
-      <c r="C41" s="56"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="65"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="66"/>
-      <c r="H41" s="30" t="s">
+      <c r="B41" s="111"/>
+      <c r="C41" s="112"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="119"/>
+      <c r="F41" s="119"/>
+      <c r="G41" s="120"/>
+      <c r="H41" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="I41" s="31"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="64"/>
-      <c r="L41" s="65"/>
-      <c r="M41" s="65"/>
-      <c r="N41" s="66"/>
-      <c r="O41" s="70"/>
-      <c r="P41" s="70"/>
-      <c r="Q41" s="70"/>
-      <c r="R41" s="71"/>
+      <c r="I41" s="133"/>
+      <c r="J41" s="134"/>
+      <c r="K41" s="118"/>
+      <c r="L41" s="119"/>
+      <c r="M41" s="119"/>
+      <c r="N41" s="120"/>
+      <c r="O41" s="124"/>
+      <c r="P41" s="124"/>
+      <c r="Q41" s="124"/>
+      <c r="R41" s="125"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="57"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="59"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="69"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="67"/>
-      <c r="L42" s="68"/>
-      <c r="M42" s="68"/>
-      <c r="N42" s="69"/>
-      <c r="O42" s="70"/>
-      <c r="P42" s="70"/>
-      <c r="Q42" s="70"/>
-      <c r="R42" s="71"/>
+      <c r="A42" s="113"/>
+      <c r="B42" s="114"/>
+      <c r="C42" s="115"/>
+      <c r="D42" s="121"/>
+      <c r="E42" s="122"/>
+      <c r="F42" s="122"/>
+      <c r="G42" s="123"/>
+      <c r="H42" s="135"/>
+      <c r="I42" s="136"/>
+      <c r="J42" s="137"/>
+      <c r="K42" s="121"/>
+      <c r="L42" s="122"/>
+      <c r="M42" s="122"/>
+      <c r="N42" s="123"/>
+      <c r="O42" s="124"/>
+      <c r="P42" s="124"/>
+      <c r="Q42" s="124"/>
+      <c r="R42" s="125"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="54" t="s">
+      <c r="A43" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="B43" s="55"/>
-      <c r="C43" s="56"/>
-      <c r="D43" s="64"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="66"/>
-      <c r="H43" s="78" t="s">
+      <c r="B43" s="111"/>
+      <c r="C43" s="112"/>
+      <c r="D43" s="118"/>
+      <c r="E43" s="119"/>
+      <c r="F43" s="119"/>
+      <c r="G43" s="120"/>
+      <c r="H43" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="I43" s="55"/>
-      <c r="J43" s="56"/>
-      <c r="K43" s="64"/>
-      <c r="L43" s="65"/>
-      <c r="M43" s="65"/>
-      <c r="N43" s="66"/>
-      <c r="O43" s="70"/>
-      <c r="P43" s="70"/>
-      <c r="Q43" s="70"/>
-      <c r="R43" s="71"/>
+      <c r="I43" s="111"/>
+      <c r="J43" s="112"/>
+      <c r="K43" s="118"/>
+      <c r="L43" s="119"/>
+      <c r="M43" s="119"/>
+      <c r="N43" s="120"/>
+      <c r="O43" s="124"/>
+      <c r="P43" s="124"/>
+      <c r="Q43" s="124"/>
+      <c r="R43" s="125"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="57"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="59"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="68"/>
-      <c r="G44" s="69"/>
-      <c r="H44" s="79"/>
-      <c r="I44" s="58"/>
-      <c r="J44" s="59"/>
-      <c r="K44" s="67"/>
-      <c r="L44" s="68"/>
-      <c r="M44" s="68"/>
-      <c r="N44" s="69"/>
-      <c r="O44" s="70"/>
-      <c r="P44" s="70"/>
-      <c r="Q44" s="70"/>
-      <c r="R44" s="71"/>
+      <c r="A44" s="113"/>
+      <c r="B44" s="114"/>
+      <c r="C44" s="115"/>
+      <c r="D44" s="121"/>
+      <c r="E44" s="122"/>
+      <c r="F44" s="122"/>
+      <c r="G44" s="123"/>
+      <c r="H44" s="131"/>
+      <c r="I44" s="114"/>
+      <c r="J44" s="115"/>
+      <c r="K44" s="121"/>
+      <c r="L44" s="122"/>
+      <c r="M44" s="122"/>
+      <c r="N44" s="123"/>
+      <c r="O44" s="124"/>
+      <c r="P44" s="124"/>
+      <c r="Q44" s="124"/>
+      <c r="R44" s="125"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="52" t="s">
+      <c r="A45" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="53"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="76"/>
-      <c r="E45" s="76"/>
-      <c r="F45" s="76"/>
-      <c r="G45" s="77"/>
-      <c r="H45" s="53" t="s">
+      <c r="B45" s="109"/>
+      <c r="C45" s="109"/>
+      <c r="D45" s="128"/>
+      <c r="E45" s="128"/>
+      <c r="F45" s="128"/>
+      <c r="G45" s="129"/>
+      <c r="H45" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="I45" s="53"/>
-      <c r="J45" s="53"/>
-      <c r="K45" s="76"/>
-      <c r="L45" s="76"/>
-      <c r="M45" s="76"/>
-      <c r="N45" s="77"/>
-      <c r="O45" s="72"/>
-      <c r="P45" s="72"/>
-      <c r="Q45" s="72"/>
-      <c r="R45" s="73"/>
+      <c r="I45" s="109"/>
+      <c r="J45" s="109"/>
+      <c r="K45" s="128"/>
+      <c r="L45" s="128"/>
+      <c r="M45" s="128"/>
+      <c r="N45" s="129"/>
+      <c r="O45" s="126"/>
+      <c r="P45" s="126"/>
+      <c r="Q45" s="126"/>
+      <c r="R45" s="127"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2739,233 +2739,233 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="131"/>
-      <c r="B49" s="132"/>
-      <c r="C49" s="133"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="50"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
-      <c r="M49" s="50"/>
-      <c r="N49" s="40"/>
-      <c r="O49" s="41"/>
-      <c r="P49" s="41"/>
-      <c r="Q49" s="41"/>
-      <c r="R49" s="42"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="142"/>
+      <c r="E49" s="143"/>
+      <c r="F49" s="143"/>
+      <c r="G49" s="143"/>
+      <c r="H49" s="151"/>
+      <c r="I49" s="142"/>
+      <c r="J49" s="143"/>
+      <c r="K49" s="143"/>
+      <c r="L49" s="143"/>
+      <c r="M49" s="151"/>
+      <c r="N49" s="142"/>
+      <c r="O49" s="143"/>
+      <c r="P49" s="143"/>
+      <c r="Q49" s="143"/>
+      <c r="R49" s="144"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="134"/>
-      <c r="B50" s="135"/>
-      <c r="C50" s="136"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="44"/>
-      <c r="F50" s="44"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="43"/>
-      <c r="J50" s="44"/>
-      <c r="K50" s="44"/>
-      <c r="L50" s="44"/>
-      <c r="M50" s="51"/>
-      <c r="N50" s="43"/>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
-      <c r="R50" s="45"/>
+      <c r="A50" s="33"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="145"/>
+      <c r="E50" s="146"/>
+      <c r="F50" s="146"/>
+      <c r="G50" s="146"/>
+      <c r="H50" s="152"/>
+      <c r="I50" s="145"/>
+      <c r="J50" s="146"/>
+      <c r="K50" s="146"/>
+      <c r="L50" s="146"/>
+      <c r="M50" s="152"/>
+      <c r="N50" s="145"/>
+      <c r="O50" s="146"/>
+      <c r="P50" s="146"/>
+      <c r="Q50" s="146"/>
+      <c r="R50" s="147"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="147" t="s">
+      <c r="A51" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B51" s="148"/>
-      <c r="C51" s="149"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="46"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="46"/>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46"/>
-      <c r="O51" s="46"/>
-      <c r="P51" s="46"/>
-      <c r="Q51" s="46"/>
-      <c r="R51" s="47"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="52"/>
+      <c r="J51" s="52"/>
+      <c r="K51" s="52"/>
+      <c r="L51" s="52"/>
+      <c r="M51" s="52"/>
+      <c r="N51" s="52"/>
+      <c r="O51" s="52"/>
+      <c r="P51" s="52"/>
+      <c r="Q51" s="52"/>
+      <c r="R51" s="148"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="150"/>
-      <c r="B52" s="151"/>
-      <c r="C52" s="152"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="46"/>
-      <c r="L52" s="46"/>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
-      <c r="O52" s="46"/>
-      <c r="P52" s="46"/>
-      <c r="Q52" s="46"/>
-      <c r="R52" s="47"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="50"/>
+      <c r="C52" s="51"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
+      <c r="G52" s="52"/>
+      <c r="H52" s="52"/>
+      <c r="I52" s="52"/>
+      <c r="J52" s="52"/>
+      <c r="K52" s="52"/>
+      <c r="L52" s="52"/>
+      <c r="M52" s="52"/>
+      <c r="N52" s="52"/>
+      <c r="O52" s="52"/>
+      <c r="P52" s="52"/>
+      <c r="Q52" s="52"/>
+      <c r="R52" s="148"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
       <c r="B53" s="4"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="37"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
-      <c r="L53" s="38"/>
-      <c r="M53" s="48"/>
-      <c r="N53" s="37"/>
-      <c r="O53" s="38"/>
-      <c r="P53" s="38"/>
-      <c r="Q53" s="38"/>
-      <c r="R53" s="39"/>
+      <c r="D53" s="139"/>
+      <c r="E53" s="140"/>
+      <c r="F53" s="140"/>
+      <c r="G53" s="140"/>
+      <c r="H53" s="149"/>
+      <c r="I53" s="139"/>
+      <c r="J53" s="140"/>
+      <c r="K53" s="140"/>
+      <c r="L53" s="140"/>
+      <c r="M53" s="149"/>
+      <c r="N53" s="139"/>
+      <c r="O53" s="140"/>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="140"/>
+      <c r="R53" s="141"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="141" t="s">
+      <c r="A54" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="142"/>
-      <c r="C54" s="143"/>
-      <c r="D54" s="137"/>
-      <c r="E54" s="137"/>
-      <c r="F54" s="137"/>
-      <c r="G54" s="137"/>
-      <c r="H54" s="137"/>
-      <c r="I54" s="137"/>
-      <c r="J54" s="137"/>
-      <c r="K54" s="137"/>
-      <c r="L54" s="137"/>
-      <c r="M54" s="137"/>
-      <c r="N54" s="137"/>
-      <c r="O54" s="137"/>
-      <c r="P54" s="137"/>
-      <c r="Q54" s="137"/>
-      <c r="R54" s="138"/>
+      <c r="B54" s="41"/>
+      <c r="C54" s="42"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="36"/>
+      <c r="I54" s="36"/>
+      <c r="J54" s="36"/>
+      <c r="K54" s="36"/>
+      <c r="L54" s="36"/>
+      <c r="M54" s="36"/>
+      <c r="N54" s="36"/>
+      <c r="O54" s="36"/>
+      <c r="P54" s="36"/>
+      <c r="Q54" s="36"/>
+      <c r="R54" s="37"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="144"/>
-      <c r="B55" s="145"/>
-      <c r="C55" s="146"/>
-      <c r="D55" s="139"/>
-      <c r="E55" s="139"/>
-      <c r="F55" s="139"/>
-      <c r="G55" s="139"/>
-      <c r="H55" s="139"/>
-      <c r="I55" s="139"/>
-      <c r="J55" s="139"/>
-      <c r="K55" s="139"/>
-      <c r="L55" s="139"/>
-      <c r="M55" s="139"/>
-      <c r="N55" s="139"/>
-      <c r="O55" s="139"/>
-      <c r="P55" s="139"/>
-      <c r="Q55" s="139"/>
-      <c r="R55" s="140"/>
+      <c r="A55" s="43"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="38"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="38"/>
+      <c r="G55" s="38"/>
+      <c r="H55" s="38"/>
+      <c r="I55" s="38"/>
+      <c r="J55" s="38"/>
+      <c r="K55" s="38"/>
+      <c r="L55" s="38"/>
+      <c r="M55" s="38"/>
+      <c r="N55" s="38"/>
+      <c r="O55" s="38"/>
+      <c r="P55" s="38"/>
+      <c r="Q55" s="38"/>
+      <c r="R55" s="39"/>
     </row>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="141" t="s">
+      <c r="A56" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B56" s="142"/>
-      <c r="C56" s="143"/>
-      <c r="D56" s="137"/>
-      <c r="E56" s="137"/>
-      <c r="F56" s="137"/>
-      <c r="G56" s="137"/>
-      <c r="H56" s="137"/>
-      <c r="I56" s="137"/>
-      <c r="J56" s="137"/>
-      <c r="K56" s="137"/>
-      <c r="L56" s="137"/>
-      <c r="M56" s="137"/>
-      <c r="N56" s="137"/>
-      <c r="O56" s="137"/>
-      <c r="P56" s="137"/>
-      <c r="Q56" s="137"/>
-      <c r="R56" s="138"/>
+      <c r="B56" s="41"/>
+      <c r="C56" s="42"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="36"/>
+      <c r="J56" s="36"/>
+      <c r="K56" s="36"/>
+      <c r="L56" s="36"/>
+      <c r="M56" s="36"/>
+      <c r="N56" s="36"/>
+      <c r="O56" s="36"/>
+      <c r="P56" s="36"/>
+      <c r="Q56" s="36"/>
+      <c r="R56" s="37"/>
     </row>
     <row r="57" spans="1:18" s="2" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="144"/>
-      <c r="B57" s="145"/>
-      <c r="C57" s="146"/>
-      <c r="D57" s="139"/>
-      <c r="E57" s="139"/>
-      <c r="F57" s="139"/>
-      <c r="G57" s="139"/>
-      <c r="H57" s="139"/>
-      <c r="I57" s="139"/>
-      <c r="J57" s="139"/>
-      <c r="K57" s="139"/>
-      <c r="L57" s="139"/>
-      <c r="M57" s="139"/>
-      <c r="N57" s="139"/>
-      <c r="O57" s="139"/>
-      <c r="P57" s="139"/>
-      <c r="Q57" s="139"/>
-      <c r="R57" s="140"/>
+      <c r="A57" s="43"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="38"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="38"/>
+      <c r="I57" s="38"/>
+      <c r="J57" s="38"/>
+      <c r="K57" s="38"/>
+      <c r="L57" s="38"/>
+      <c r="M57" s="38"/>
+      <c r="N57" s="38"/>
+      <c r="O57" s="38"/>
+      <c r="P57" s="38"/>
+      <c r="Q57" s="38"/>
+      <c r="R57" s="39"/>
     </row>
     <row r="58" spans="1:18" s="2" customFormat="1" ht="27" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D58" s="49"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="49"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="49"/>
-      <c r="J58" s="49"/>
-      <c r="K58" s="49"/>
-      <c r="L58" s="49"/>
-      <c r="M58" s="49"/>
-      <c r="N58" s="49"/>
-      <c r="O58" s="49"/>
-      <c r="P58" s="49"/>
-      <c r="Q58" s="49"/>
-      <c r="R58" s="49"/>
+      <c r="D58" s="150"/>
+      <c r="E58" s="150"/>
+      <c r="F58" s="150"/>
+      <c r="G58" s="150"/>
+      <c r="H58" s="150"/>
+      <c r="I58" s="150"/>
+      <c r="J58" s="150"/>
+      <c r="K58" s="150"/>
+      <c r="L58" s="150"/>
+      <c r="M58" s="150"/>
+      <c r="N58" s="150"/>
+      <c r="O58" s="150"/>
+      <c r="P58" s="150"/>
+      <c r="Q58" s="150"/>
+      <c r="R58" s="150"/>
     </row>
     <row r="59" spans="1:18" s="2" customFormat="1" ht="30.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D59" s="36" t="str">
+      <c r="D59" s="138" t="str">
         <f>IF(MOD(D58,1000)=0,"千円単位",IF(MOD(D58,100)=0,"百円単位",IF(MOD(D58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
-      <c r="H59" s="36"/>
-      <c r="I59" s="36" t="str">
+      <c r="E59" s="138"/>
+      <c r="F59" s="138"/>
+      <c r="G59" s="138"/>
+      <c r="H59" s="138"/>
+      <c r="I59" s="138" t="str">
         <f>IF(MOD(I58,1000)=0,"千円単位",IF(MOD(I58,100)=0,"百円単位",IF(MOD(I58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="J59" s="36"/>
-      <c r="K59" s="36"/>
-      <c r="L59" s="36"/>
-      <c r="M59" s="36"/>
-      <c r="N59" s="36" t="str">
+      <c r="J59" s="138"/>
+      <c r="K59" s="138"/>
+      <c r="L59" s="138"/>
+      <c r="M59" s="138"/>
+      <c r="N59" s="138" t="str">
         <f>IF(MOD(N58,1000)=0,"千円単位",IF(MOD(N58,100)=0,"百円単位",IF(MOD(N58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="O59" s="36"/>
-      <c r="P59" s="36"/>
-      <c r="Q59" s="36"/>
-      <c r="R59" s="36"/>
+      <c r="O59" s="138"/>
+      <c r="P59" s="138"/>
+      <c r="Q59" s="138"/>
+      <c r="R59" s="138"/>
     </row>
     <row r="60" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="61" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2977,40 +2977,19 @@
     <row r="67" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="N56:R57"/>
-    <mergeCell ref="D54:H55"/>
-    <mergeCell ref="I54:M55"/>
-    <mergeCell ref="N54:R55"/>
-    <mergeCell ref="A54:C55"/>
-    <mergeCell ref="A56:C57"/>
-    <mergeCell ref="D56:H57"/>
-    <mergeCell ref="I56:M57"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="I51:M52"/>
-    <mergeCell ref="D51:H52"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A22:C28"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:R21"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="O22:R28"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="D31:I32"/>
-    <mergeCell ref="D33:R34"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="I59:M59"/>
+    <mergeCell ref="N59:R59"/>
+    <mergeCell ref="N53:R53"/>
+    <mergeCell ref="N49:R50"/>
+    <mergeCell ref="N51:R52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="I58:M58"/>
+    <mergeCell ref="N58:R58"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="I53:M53"/>
+    <mergeCell ref="I49:M50"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="H45:J45"/>
     <mergeCell ref="A43:C44"/>
@@ -3027,19 +3006,40 @@
     <mergeCell ref="H43:J44"/>
     <mergeCell ref="D41:G42"/>
     <mergeCell ref="H41:J42"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="I59:M59"/>
-    <mergeCell ref="N59:R59"/>
-    <mergeCell ref="N53:R53"/>
-    <mergeCell ref="N49:R50"/>
-    <mergeCell ref="N51:R52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="I58:M58"/>
-    <mergeCell ref="N58:R58"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="I53:M53"/>
-    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="D33:R34"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A22:C28"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:R21"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="O22:R28"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="N56:R57"/>
+    <mergeCell ref="D54:H55"/>
+    <mergeCell ref="I54:M55"/>
+    <mergeCell ref="N54:R55"/>
+    <mergeCell ref="A54:C55"/>
+    <mergeCell ref="A56:C57"/>
+    <mergeCell ref="D56:H57"/>
+    <mergeCell ref="I56:M57"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="I51:M52"/>
+    <mergeCell ref="D51:H52"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="D51:R52">
@@ -3069,11 +3069,9 @@
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.44" bottom="0.55118110236220474" header="0.25" footer="0.31496062992125984"/>
+  <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.43307086614173229" bottom="0.55118110236220474" header="0.23622047244094491" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;R&amp;"ＭＳ Ｐ明朝,標準"&amp;7Ver.3-12.03-01</oddFooter>
-  </headerFooter>
+  <headerFooter alignWithMargins="0"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="18" max="1048575" man="1"/>
   </colBreaks>
@@ -3093,62 +3091,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="161" t="s">
+      <c r="E2" s="160" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161" t="s">
+      <c r="F2" s="160"/>
+      <c r="G2" s="160" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="161"/>
-      <c r="I2" s="161" t="s">
+      <c r="H2" s="160"/>
+      <c r="I2" s="160" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161" t="s">
+      <c r="J2" s="160"/>
+      <c r="K2" s="160" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="161"/>
-      <c r="M2" s="161" t="s">
+      <c r="L2" s="160"/>
+      <c r="M2" s="160" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="161"/>
+      <c r="N2" s="160"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="155" t="s">
+      <c r="B3" s="161" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="155"/>
+      <c r="C3" s="161"/>
       <c r="D3" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="155"/>
-      <c r="K3" s="155"/>
-      <c r="L3" s="155"/>
-      <c r="M3" s="155"/>
-      <c r="N3" s="155"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="161"/>
+      <c r="K3" s="161"/>
+      <c r="L3" s="161"/>
+      <c r="M3" s="161"/>
+      <c r="N3" s="161"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="155"/>
-      <c r="C4" s="155"/>
+      <c r="B4" s="161"/>
+      <c r="C4" s="161"/>
       <c r="D4" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="155"/>
-      <c r="F4" s="155"/>
-      <c r="G4" s="155"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="155"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="155"/>
-      <c r="L4" s="155"/>
-      <c r="M4" s="155"/>
-      <c r="N4" s="155"/>
+      <c r="E4" s="161"/>
+      <c r="F4" s="161"/>
+      <c r="G4" s="161"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="161"/>
+      <c r="J4" s="161"/>
+      <c r="K4" s="161"/>
+      <c r="L4" s="161"/>
+      <c r="M4" s="161"/>
+      <c r="N4" s="161"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -3169,62 +3167,62 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="162" t="s">
+      <c r="E6" s="156" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="163"/>
-      <c r="G6" s="162" t="s">
+      <c r="F6" s="157"/>
+      <c r="G6" s="156" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="163"/>
-      <c r="I6" s="162" t="s">
+      <c r="H6" s="157"/>
+      <c r="I6" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="163"/>
-      <c r="K6" s="162" t="s">
+      <c r="J6" s="157"/>
+      <c r="K6" s="156" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="163"/>
-      <c r="M6" s="162" t="s">
+      <c r="L6" s="157"/>
+      <c r="M6" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="163"/>
+      <c r="N6" s="157"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="161" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="155"/>
+      <c r="C7" s="161"/>
       <c r="D7" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="157"/>
-      <c r="F7" s="158"/>
-      <c r="G7" s="159"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="157"/>
-      <c r="J7" s="158"/>
-      <c r="K7" s="157"/>
-      <c r="L7" s="158"/>
-      <c r="M7" s="157"/>
-      <c r="N7" s="158"/>
+      <c r="E7" s="158"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="163"/>
+      <c r="H7" s="164"/>
+      <c r="I7" s="158"/>
+      <c r="J7" s="159"/>
+      <c r="K7" s="158"/>
+      <c r="L7" s="159"/>
+      <c r="M7" s="158"/>
+      <c r="N7" s="159"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="155"/>
-      <c r="C8" s="155"/>
+      <c r="B8" s="161"/>
+      <c r="C8" s="161"/>
       <c r="D8" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="157"/>
-      <c r="F8" s="158"/>
-      <c r="G8" s="157"/>
-      <c r="H8" s="158"/>
-      <c r="I8" s="157"/>
-      <c r="J8" s="158"/>
-      <c r="K8" s="157"/>
-      <c r="L8" s="158"/>
-      <c r="M8" s="157"/>
-      <c r="N8" s="158"/>
+      <c r="E8" s="158"/>
+      <c r="F8" s="159"/>
+      <c r="G8" s="158"/>
+      <c r="H8" s="159"/>
+      <c r="I8" s="158"/>
+      <c r="J8" s="159"/>
+      <c r="K8" s="158"/>
+      <c r="L8" s="159"/>
+      <c r="M8" s="158"/>
+      <c r="N8" s="159"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
@@ -3245,62 +3243,62 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="162" t="s">
+      <c r="E10" s="156" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="163"/>
-      <c r="G10" s="162" t="s">
+      <c r="F10" s="157"/>
+      <c r="G10" s="156" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="163"/>
-      <c r="I10" s="162" t="s">
+      <c r="H10" s="157"/>
+      <c r="I10" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="163"/>
-      <c r="K10" s="162" t="s">
+      <c r="J10" s="157"/>
+      <c r="K10" s="156" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="163"/>
-      <c r="M10" s="162" t="s">
+      <c r="L10" s="157"/>
+      <c r="M10" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="N10" s="163"/>
+      <c r="N10" s="157"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="155" t="s">
+      <c r="B11" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="155"/>
+      <c r="C11" s="161"/>
       <c r="D11" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="157"/>
-      <c r="F11" s="158"/>
-      <c r="G11" s="159"/>
-      <c r="H11" s="160"/>
-      <c r="I11" s="157"/>
-      <c r="J11" s="158"/>
-      <c r="K11" s="157"/>
-      <c r="L11" s="158"/>
-      <c r="M11" s="157"/>
-      <c r="N11" s="158"/>
+      <c r="E11" s="158"/>
+      <c r="F11" s="159"/>
+      <c r="G11" s="163"/>
+      <c r="H11" s="164"/>
+      <c r="I11" s="158"/>
+      <c r="J11" s="159"/>
+      <c r="K11" s="158"/>
+      <c r="L11" s="159"/>
+      <c r="M11" s="158"/>
+      <c r="N11" s="159"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="155"/>
-      <c r="C12" s="155"/>
+      <c r="B12" s="161"/>
+      <c r="C12" s="161"/>
       <c r="D12" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="157"/>
-      <c r="F12" s="158"/>
-      <c r="G12" s="157"/>
-      <c r="H12" s="158"/>
-      <c r="I12" s="157"/>
-      <c r="J12" s="158"/>
-      <c r="K12" s="157"/>
-      <c r="L12" s="158"/>
-      <c r="M12" s="157"/>
-      <c r="N12" s="158"/>
+      <c r="E12" s="158"/>
+      <c r="F12" s="159"/>
+      <c r="G12" s="158"/>
+      <c r="H12" s="159"/>
+      <c r="I12" s="158"/>
+      <c r="J12" s="159"/>
+      <c r="K12" s="158"/>
+      <c r="L12" s="159"/>
+      <c r="M12" s="158"/>
+      <c r="N12" s="159"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
@@ -3336,62 +3334,62 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="162" t="s">
+      <c r="E15" s="156" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="163"/>
-      <c r="G15" s="162" t="s">
+      <c r="F15" s="157"/>
+      <c r="G15" s="156" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="163"/>
-      <c r="I15" s="162" t="s">
+      <c r="H15" s="157"/>
+      <c r="I15" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="163"/>
-      <c r="K15" s="162" t="s">
+      <c r="J15" s="157"/>
+      <c r="K15" s="156" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="163"/>
-      <c r="M15" s="162" t="s">
+      <c r="L15" s="157"/>
+      <c r="M15" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="163"/>
+      <c r="N15" s="157"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="155" t="s">
+      <c r="B16" s="161" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="155"/>
+      <c r="C16" s="161"/>
       <c r="D16" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="157"/>
-      <c r="F16" s="158"/>
-      <c r="G16" s="159"/>
-      <c r="H16" s="160"/>
-      <c r="I16" s="157"/>
-      <c r="J16" s="158"/>
-      <c r="K16" s="157"/>
-      <c r="L16" s="158"/>
-      <c r="M16" s="157"/>
-      <c r="N16" s="158"/>
+      <c r="E16" s="158"/>
+      <c r="F16" s="159"/>
+      <c r="G16" s="163"/>
+      <c r="H16" s="164"/>
+      <c r="I16" s="158"/>
+      <c r="J16" s="159"/>
+      <c r="K16" s="158"/>
+      <c r="L16" s="159"/>
+      <c r="M16" s="158"/>
+      <c r="N16" s="159"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="155"/>
-      <c r="C17" s="155"/>
+      <c r="B17" s="161"/>
+      <c r="C17" s="161"/>
       <c r="D17" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="157"/>
-      <c r="F17" s="158"/>
-      <c r="G17" s="157"/>
-      <c r="H17" s="158"/>
-      <c r="I17" s="157"/>
-      <c r="J17" s="158"/>
-      <c r="K17" s="157"/>
-      <c r="L17" s="158"/>
-      <c r="M17" s="157"/>
-      <c r="N17" s="158"/>
+      <c r="E17" s="158"/>
+      <c r="F17" s="159"/>
+      <c r="G17" s="158"/>
+      <c r="H17" s="159"/>
+      <c r="I17" s="158"/>
+      <c r="J17" s="159"/>
+      <c r="K17" s="158"/>
+      <c r="L17" s="159"/>
+      <c r="M17" s="158"/>
+      <c r="N17" s="159"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B20" s="153"/>
@@ -3495,8 +3493,8 @@
       </c>
       <c r="C26" s="153"/>
       <c r="D26" s="153"/>
-      <c r="E26" s="164"/>
-      <c r="F26" s="164"/>
+      <c r="E26" s="155"/>
+      <c r="F26" s="155"/>
       <c r="I26" s="153" t="s">
         <v>43</v>
       </c>
@@ -3525,34 +3523,59 @@
     </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
     <mergeCell ref="M15:N15"/>
     <mergeCell ref="M16:N16"/>
     <mergeCell ref="E17:F17"/>
@@ -3566,61 +3589,36 @@
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
     <mergeCell ref="I26:K26"/>
     <mergeCell ref="L26:M26"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:M22"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfEarthquake.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ohno\eruful\mitumo\storage\app\estimateTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A918B56B-6B9C-459B-855C-21B8B0EFD99F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF12E5C-0DDA-4E8C-9DB1-A455FD49FB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="地震おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="49">
   <si>
     <t>御　　見　　積　　書</t>
     <rPh sb="0" eb="1">
@@ -503,6 +503,13 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>ワリビキ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>作業人数</t>
+    <rPh sb="0" eb="4">
+      <t>サギョウニンズ</t>
     </rPh>
     <phoneticPr fontId="19"/>
   </si>
@@ -1265,73 +1272,219 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1341,24 +1494,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1437,234 +1572,106 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2068,10 +2075,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="28"/>
@@ -2081,16 +2088,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="Q3" s="130"/>
+      <c r="R3" s="130"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="86"/>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="86"/>
-      <c r="R4" s="86"/>
+      <c r="O4" s="130"/>
+      <c r="P4" s="130"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="130"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="27"/>
@@ -2153,194 +2160,194 @@
       <c r="R10" s="23"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
+      <c r="B11" s="104"/>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
+      <c r="L11" s="104"/>
+      <c r="M11" s="104"/>
+      <c r="N11" s="104"/>
+      <c r="O11" s="104"/>
+      <c r="P11" s="104"/>
+      <c r="Q11" s="104"/>
+      <c r="R11" s="104"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="80" t="s">
+      <c r="A15" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="80"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="80"/>
-      <c r="M15" s="80"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="80"/>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="80"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="124"/>
+      <c r="J15" s="124"/>
+      <c r="K15" s="124"/>
+      <c r="L15" s="124"/>
+      <c r="M15" s="124"/>
+      <c r="N15" s="124"/>
+      <c r="O15" s="124"/>
+      <c r="P15" s="124"/>
+      <c r="Q15" s="124"/>
+      <c r="R15" s="124"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="81" t="s">
+      <c r="A18" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
-      <c r="M18" s="81"/>
-      <c r="N18" s="81"/>
-      <c r="O18" s="81"/>
-      <c r="P18" s="81"/>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="81"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="125"/>
+      <c r="J18" s="125"/>
+      <c r="K18" s="125"/>
+      <c r="L18" s="125"/>
+      <c r="M18" s="125"/>
+      <c r="N18" s="125"/>
+      <c r="O18" s="125"/>
+      <c r="P18" s="125"/>
+      <c r="Q18" s="125"/>
+      <c r="R18" s="125"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="62"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="62"/>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="62"/>
-      <c r="R20" s="63"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
+      <c r="L20" s="106"/>
+      <c r="M20" s="106"/>
+      <c r="N20" s="106"/>
+      <c r="O20" s="106"/>
+      <c r="P20" s="106"/>
+      <c r="Q20" s="106"/>
+      <c r="R20" s="107"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="55"/>
+      <c r="A21" s="81"/>
       <c r="B21" s="56"/>
       <c r="C21" s="56"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="65"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="65"/>
-      <c r="M21" s="65"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="65"/>
-      <c r="P21" s="65"/>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="66"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="109"/>
+      <c r="F21" s="109"/>
+      <c r="G21" s="109"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="109"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="110"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="81" t="s">
         <v>4</v>
       </c>
       <c r="B22" s="56"/>
       <c r="C22" s="56"/>
       <c r="D22" s="22"/>
       <c r="L22" s="21"/>
-      <c r="M22" s="67" t="s">
+      <c r="M22" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="68"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="72"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="73"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="116"/>
+      <c r="Q22" s="116"/>
+      <c r="R22" s="117"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="55"/>
+      <c r="A23" s="81"/>
       <c r="B23" s="56"/>
       <c r="C23" s="56"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="74"/>
-      <c r="P23" s="75"/>
-      <c r="Q23" s="75"/>
-      <c r="R23" s="76"/>
+      <c r="D23" s="126"/>
+      <c r="E23" s="127"/>
+      <c r="F23" s="127"/>
+      <c r="G23" s="127"/>
+      <c r="H23" s="127"/>
+      <c r="I23" s="127"/>
+      <c r="J23" s="127"/>
+      <c r="K23" s="127"/>
+      <c r="L23" s="128"/>
+      <c r="M23" s="111"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="118"/>
+      <c r="P23" s="119"/>
+      <c r="Q23" s="119"/>
+      <c r="R23" s="120"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="55"/>
+      <c r="A24" s="81"/>
       <c r="B24" s="56"/>
       <c r="C24" s="56"/>
-      <c r="D24" s="85"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="67"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="74"/>
-      <c r="P24" s="75"/>
-      <c r="Q24" s="75"/>
-      <c r="R24" s="76"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="127"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="127"/>
+      <c r="H24" s="127"/>
+      <c r="I24" s="127"/>
+      <c r="J24" s="127"/>
+      <c r="K24" s="127"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="111"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="118"/>
+      <c r="P24" s="119"/>
+      <c r="Q24" s="119"/>
+      <c r="R24" s="120"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="55"/>
+      <c r="A25" s="81"/>
       <c r="B25" s="56"/>
       <c r="C25" s="56"/>
-      <c r="D25" s="85"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="83"/>
-      <c r="L25" s="84"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="74"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="76"/>
+      <c r="D25" s="129"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="127"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="127"/>
+      <c r="I25" s="127"/>
+      <c r="J25" s="127"/>
+      <c r="K25" s="127"/>
+      <c r="L25" s="128"/>
+      <c r="M25" s="111"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="118"/>
+      <c r="P25" s="119"/>
+      <c r="Q25" s="119"/>
+      <c r="R25" s="120"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="55"/>
+      <c r="A26" s="81"/>
       <c r="B26" s="56"/>
       <c r="C26" s="56"/>
       <c r="D26" s="20"/>
@@ -2352,15 +2359,15 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="16"/>
-      <c r="M26" s="67"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="75"/>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="76"/>
+      <c r="M26" s="111"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="118"/>
+      <c r="P26" s="119"/>
+      <c r="Q26" s="119"/>
+      <c r="R26" s="120"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="55"/>
+      <c r="A27" s="81"/>
       <c r="B27" s="56"/>
       <c r="C27" s="56"/>
       <c r="D27" s="15"/>
@@ -2370,17 +2377,17 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="L27" s="11"/>
-      <c r="M27" s="67"/>
-      <c r="N27" s="68"/>
-      <c r="O27" s="74"/>
-      <c r="P27" s="75"/>
-      <c r="Q27" s="75"/>
-      <c r="R27" s="76"/>
+      <c r="M27" s="111"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="118"/>
+      <c r="P27" s="119"/>
+      <c r="Q27" s="119"/>
+      <c r="R27" s="120"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="57"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
+      <c r="A28" s="89"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
       <c r="D28" s="10"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -2390,344 +2397,344 @@
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="8"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="70"/>
-      <c r="O28" s="77"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="78"/>
-      <c r="R28" s="79"/>
+      <c r="M28" s="113"/>
+      <c r="N28" s="114"/>
+      <c r="O28" s="121"/>
+      <c r="P28" s="122"/>
+      <c r="Q28" s="122"/>
+      <c r="R28" s="123"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="59" t="s">
+      <c r="A31" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="60"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="92"/>
-      <c r="H31" s="92"/>
-      <c r="I31" s="92"/>
-      <c r="J31" s="60" t="s">
+      <c r="B31" s="54"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="85"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="60"/>
-      <c r="L31" s="60"/>
-      <c r="M31" s="92"/>
-      <c r="N31" s="92"/>
-      <c r="O31" s="92"/>
-      <c r="P31" s="92"/>
-      <c r="Q31" s="92"/>
-      <c r="R31" s="93"/>
+      <c r="K31" s="54"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="85"/>
+      <c r="P31" s="85"/>
+      <c r="Q31" s="85"/>
+      <c r="R31" s="86"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="55"/>
+      <c r="A32" s="81"/>
       <c r="B32" s="56"/>
       <c r="C32" s="56"/>
-      <c r="D32" s="94"/>
-      <c r="E32" s="94"/>
-      <c r="F32" s="94"/>
-      <c r="G32" s="94"/>
-      <c r="H32" s="94"/>
-      <c r="I32" s="94"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="87"/>
+      <c r="H32" s="87"/>
+      <c r="I32" s="87"/>
       <c r="J32" s="56"/>
       <c r="K32" s="56"/>
       <c r="L32" s="56"/>
-      <c r="M32" s="94"/>
-      <c r="N32" s="94"/>
-      <c r="O32" s="94"/>
-      <c r="P32" s="94"/>
-      <c r="Q32" s="94"/>
-      <c r="R32" s="95"/>
+      <c r="M32" s="87"/>
+      <c r="N32" s="87"/>
+      <c r="O32" s="87"/>
+      <c r="P32" s="87"/>
+      <c r="Q32" s="87"/>
+      <c r="R32" s="88"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="81" t="s">
         <v>8</v>
       </c>
       <c r="B33" s="56"/>
       <c r="C33" s="56"/>
-      <c r="D33" s="102"/>
-      <c r="E33" s="103"/>
-      <c r="F33" s="103"/>
-      <c r="G33" s="103"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="103"/>
-      <c r="J33" s="103"/>
-      <c r="K33" s="103"/>
-      <c r="L33" s="103"/>
-      <c r="M33" s="103"/>
-      <c r="N33" s="103"/>
-      <c r="O33" s="103"/>
-      <c r="P33" s="103"/>
-      <c r="Q33" s="103"/>
-      <c r="R33" s="104"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="98"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="98"/>
+      <c r="H33" s="98"/>
+      <c r="I33" s="98"/>
+      <c r="J33" s="98"/>
+      <c r="K33" s="98"/>
+      <c r="L33" s="98"/>
+      <c r="M33" s="98"/>
+      <c r="N33" s="98"/>
+      <c r="O33" s="98"/>
+      <c r="P33" s="98"/>
+      <c r="Q33" s="98"/>
+      <c r="R33" s="99"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="55"/>
+      <c r="A34" s="81"/>
       <c r="B34" s="56"/>
       <c r="C34" s="56"/>
-      <c r="D34" s="105"/>
-      <c r="E34" s="106"/>
-      <c r="F34" s="106"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="106"/>
-      <c r="I34" s="106"/>
-      <c r="J34" s="106"/>
-      <c r="K34" s="106"/>
-      <c r="L34" s="106"/>
-      <c r="M34" s="106"/>
-      <c r="N34" s="106"/>
-      <c r="O34" s="106"/>
-      <c r="P34" s="106"/>
-      <c r="Q34" s="106"/>
-      <c r="R34" s="107"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="101"/>
+      <c r="F34" s="101"/>
+      <c r="G34" s="101"/>
+      <c r="H34" s="101"/>
+      <c r="I34" s="101"/>
+      <c r="J34" s="101"/>
+      <c r="K34" s="101"/>
+      <c r="L34" s="101"/>
+      <c r="M34" s="101"/>
+      <c r="N34" s="101"/>
+      <c r="O34" s="101"/>
+      <c r="P34" s="101"/>
+      <c r="Q34" s="101"/>
+      <c r="R34" s="102"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="55" t="s">
+      <c r="A35" s="81" t="s">
         <v>9</v>
       </c>
       <c r="B35" s="56"/>
       <c r="C35" s="56"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="97"/>
-      <c r="F35" s="97"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="97"/>
-      <c r="I35" s="97"/>
-      <c r="J35" s="97"/>
-      <c r="K35" s="97"/>
-      <c r="L35" s="97"/>
-      <c r="M35" s="97"/>
-      <c r="N35" s="97"/>
-      <c r="O35" s="97"/>
-      <c r="P35" s="97"/>
-      <c r="Q35" s="97"/>
-      <c r="R35" s="98"/>
+      <c r="D35" s="91"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="92"/>
+      <c r="H35" s="92"/>
+      <c r="I35" s="92"/>
+      <c r="J35" s="92"/>
+      <c r="K35" s="92"/>
+      <c r="L35" s="92"/>
+      <c r="M35" s="92"/>
+      <c r="N35" s="92"/>
+      <c r="O35" s="92"/>
+      <c r="P35" s="92"/>
+      <c r="Q35" s="92"/>
+      <c r="R35" s="93"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="57"/>
-      <c r="B36" s="58"/>
-      <c r="C36" s="58"/>
-      <c r="D36" s="99"/>
-      <c r="E36" s="100"/>
-      <c r="F36" s="100"/>
-      <c r="G36" s="100"/>
-      <c r="H36" s="100"/>
-      <c r="I36" s="100"/>
-      <c r="J36" s="100"/>
-      <c r="K36" s="100"/>
-      <c r="L36" s="100"/>
-      <c r="M36" s="100"/>
-      <c r="N36" s="100"/>
-      <c r="O36" s="100"/>
-      <c r="P36" s="100"/>
-      <c r="Q36" s="100"/>
-      <c r="R36" s="101"/>
+      <c r="A36" s="89"/>
+      <c r="B36" s="90"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="94"/>
+      <c r="E36" s="95"/>
+      <c r="F36" s="95"/>
+      <c r="G36" s="95"/>
+      <c r="H36" s="95"/>
+      <c r="I36" s="95"/>
+      <c r="J36" s="95"/>
+      <c r="K36" s="95"/>
+      <c r="L36" s="95"/>
+      <c r="M36" s="95"/>
+      <c r="N36" s="95"/>
+      <c r="O36" s="95"/>
+      <c r="P36" s="95"/>
+      <c r="Q36" s="95"/>
+      <c r="R36" s="96"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="87"/>
-      <c r="B37" s="88"/>
-      <c r="C37" s="88"/>
-      <c r="D37" s="88"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="88"/>
-      <c r="H37" s="88"/>
-      <c r="I37" s="88"/>
-      <c r="J37" s="88"/>
-      <c r="K37" s="88"/>
-      <c r="L37" s="88"/>
-      <c r="M37" s="88"/>
-      <c r="N37" s="88"/>
-      <c r="O37" s="88"/>
-      <c r="P37" s="88"/>
-      <c r="Q37" s="88"/>
-      <c r="R37" s="88"/>
+      <c r="A37" s="82"/>
+      <c r="B37" s="83"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="83"/>
+      <c r="K37" s="83"/>
+      <c r="L37" s="83"/>
+      <c r="M37" s="83"/>
+      <c r="N37" s="83"/>
+      <c r="O37" s="83"/>
+      <c r="P37" s="83"/>
+      <c r="Q37" s="83"/>
+      <c r="R37" s="83"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="89"/>
-      <c r="B38" s="89"/>
-      <c r="C38" s="89"/>
-      <c r="D38" s="89"/>
-      <c r="E38" s="89"/>
-      <c r="F38" s="89"/>
-      <c r="G38" s="89"/>
-      <c r="H38" s="89"/>
-      <c r="I38" s="89"/>
-      <c r="J38" s="89"/>
-      <c r="K38" s="89"/>
-      <c r="L38" s="89"/>
-      <c r="M38" s="89"/>
-      <c r="N38" s="89"/>
-      <c r="O38" s="89"/>
-      <c r="P38" s="89"/>
-      <c r="Q38" s="89"/>
-      <c r="R38" s="89"/>
+      <c r="A38" s="84"/>
+      <c r="B38" s="84"/>
+      <c r="C38" s="84"/>
+      <c r="D38" s="84"/>
+      <c r="E38" s="84"/>
+      <c r="F38" s="84"/>
+      <c r="G38" s="84"/>
+      <c r="H38" s="84"/>
+      <c r="I38" s="84"/>
+      <c r="J38" s="84"/>
+      <c r="K38" s="84"/>
+      <c r="L38" s="84"/>
+      <c r="M38" s="84"/>
+      <c r="N38" s="84"/>
+      <c r="O38" s="84"/>
+      <c r="P38" s="84"/>
+      <c r="Q38" s="84"/>
+      <c r="R38" s="84"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="59" t="s">
+      <c r="A39" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="60"/>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60" t="s">
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="90"/>
-      <c r="H39" s="60" t="s">
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="I39" s="60"/>
-      <c r="J39" s="60"/>
-      <c r="K39" s="60" t="s">
+      <c r="I39" s="54"/>
+      <c r="J39" s="54"/>
+      <c r="K39" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L39" s="60"/>
-      <c r="M39" s="60"/>
-      <c r="N39" s="90"/>
-      <c r="O39" s="60" t="s">
+      <c r="L39" s="54"/>
+      <c r="M39" s="54"/>
+      <c r="N39" s="68"/>
+      <c r="O39" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="P39" s="60"/>
-      <c r="Q39" s="60"/>
-      <c r="R39" s="116"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="55"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="55"/>
+      <c r="A40" s="81"/>
       <c r="B40" s="56"/>
       <c r="C40" s="56"/>
       <c r="D40" s="56"/>
       <c r="E40" s="56"/>
       <c r="F40" s="56"/>
-      <c r="G40" s="91"/>
+      <c r="G40" s="69"/>
       <c r="H40" s="56"/>
       <c r="I40" s="56"/>
       <c r="J40" s="56"/>
       <c r="K40" s="56"/>
       <c r="L40" s="56"/>
       <c r="M40" s="56"/>
-      <c r="N40" s="91"/>
+      <c r="N40" s="69"/>
       <c r="O40" s="56"/>
       <c r="P40" s="56"/>
       <c r="Q40" s="56"/>
-      <c r="R40" s="117"/>
+      <c r="R40" s="57"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="110" t="s">
+      <c r="A41" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B41" s="111"/>
-      <c r="C41" s="112"/>
-      <c r="D41" s="118"/>
-      <c r="E41" s="119"/>
-      <c r="F41" s="119"/>
-      <c r="G41" s="120"/>
-      <c r="H41" s="132" t="s">
+      <c r="B41" s="49"/>
+      <c r="C41" s="50"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="I41" s="133"/>
-      <c r="J41" s="134"/>
-      <c r="K41" s="118"/>
-      <c r="L41" s="119"/>
-      <c r="M41" s="119"/>
-      <c r="N41" s="120"/>
-      <c r="O41" s="124"/>
-      <c r="P41" s="124"/>
-      <c r="Q41" s="124"/>
-      <c r="R41" s="125"/>
+      <c r="I41" s="75"/>
+      <c r="J41" s="76"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="59"/>
+      <c r="M41" s="59"/>
+      <c r="N41" s="60"/>
+      <c r="O41" s="64"/>
+      <c r="P41" s="64"/>
+      <c r="Q41" s="64"/>
+      <c r="R41" s="65"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="113"/>
-      <c r="B42" s="114"/>
-      <c r="C42" s="115"/>
-      <c r="D42" s="121"/>
-      <c r="E42" s="122"/>
-      <c r="F42" s="122"/>
-      <c r="G42" s="123"/>
-      <c r="H42" s="135"/>
-      <c r="I42" s="136"/>
-      <c r="J42" s="137"/>
-      <c r="K42" s="121"/>
-      <c r="L42" s="122"/>
-      <c r="M42" s="122"/>
-      <c r="N42" s="123"/>
-      <c r="O42" s="124"/>
-      <c r="P42" s="124"/>
-      <c r="Q42" s="124"/>
-      <c r="R42" s="125"/>
+      <c r="A42" s="51"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="61"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="77"/>
+      <c r="I42" s="78"/>
+      <c r="J42" s="79"/>
+      <c r="K42" s="61"/>
+      <c r="L42" s="62"/>
+      <c r="M42" s="62"/>
+      <c r="N42" s="63"/>
+      <c r="O42" s="64"/>
+      <c r="P42" s="64"/>
+      <c r="Q42" s="64"/>
+      <c r="R42" s="65"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="110" t="s">
+      <c r="A43" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="B43" s="111"/>
-      <c r="C43" s="112"/>
-      <c r="D43" s="118"/>
-      <c r="E43" s="119"/>
-      <c r="F43" s="119"/>
-      <c r="G43" s="120"/>
-      <c r="H43" s="130" t="s">
+      <c r="B43" s="49"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="60"/>
+      <c r="H43" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="I43" s="111"/>
-      <c r="J43" s="112"/>
-      <c r="K43" s="118"/>
-      <c r="L43" s="119"/>
-      <c r="M43" s="119"/>
-      <c r="N43" s="120"/>
-      <c r="O43" s="124"/>
-      <c r="P43" s="124"/>
-      <c r="Q43" s="124"/>
-      <c r="R43" s="125"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="58"/>
+      <c r="L43" s="59"/>
+      <c r="M43" s="59"/>
+      <c r="N43" s="60"/>
+      <c r="O43" s="64"/>
+      <c r="P43" s="64"/>
+      <c r="Q43" s="64"/>
+      <c r="R43" s="65"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="113"/>
-      <c r="B44" s="114"/>
-      <c r="C44" s="115"/>
-      <c r="D44" s="121"/>
-      <c r="E44" s="122"/>
-      <c r="F44" s="122"/>
-      <c r="G44" s="123"/>
-      <c r="H44" s="131"/>
-      <c r="I44" s="114"/>
-      <c r="J44" s="115"/>
-      <c r="K44" s="121"/>
-      <c r="L44" s="122"/>
-      <c r="M44" s="122"/>
-      <c r="N44" s="123"/>
-      <c r="O44" s="124"/>
-      <c r="P44" s="124"/>
-      <c r="Q44" s="124"/>
-      <c r="R44" s="125"/>
+      <c r="A44" s="51"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="62"/>
+      <c r="F44" s="62"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="73"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="61"/>
+      <c r="L44" s="62"/>
+      <c r="M44" s="62"/>
+      <c r="N44" s="63"/>
+      <c r="O44" s="64"/>
+      <c r="P44" s="64"/>
+      <c r="Q44" s="64"/>
+      <c r="R44" s="65"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="108" t="s">
+      <c r="A45" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="109"/>
-      <c r="C45" s="109"/>
-      <c r="D45" s="128"/>
-      <c r="E45" s="128"/>
-      <c r="F45" s="128"/>
-      <c r="G45" s="129"/>
-      <c r="H45" s="109" t="s">
+      <c r="B45" s="47"/>
+      <c r="C45" s="47"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="I45" s="109"/>
-      <c r="J45" s="109"/>
-      <c r="K45" s="128"/>
-      <c r="L45" s="128"/>
-      <c r="M45" s="128"/>
-      <c r="N45" s="129"/>
-      <c r="O45" s="126"/>
-      <c r="P45" s="126"/>
-      <c r="Q45" s="126"/>
-      <c r="R45" s="127"/>
+      <c r="I45" s="47"/>
+      <c r="J45" s="47"/>
+      <c r="K45" s="70"/>
+      <c r="L45" s="70"/>
+      <c r="M45" s="70"/>
+      <c r="N45" s="71"/>
+      <c r="O45" s="66"/>
+      <c r="P45" s="66"/>
+      <c r="Q45" s="66"/>
+      <c r="R45" s="67"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2739,233 +2746,233 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="30"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="142"/>
-      <c r="E49" s="143"/>
-      <c r="F49" s="143"/>
-      <c r="G49" s="143"/>
-      <c r="H49" s="151"/>
-      <c r="I49" s="142"/>
-      <c r="J49" s="143"/>
-      <c r="K49" s="143"/>
-      <c r="L49" s="143"/>
-      <c r="M49" s="151"/>
-      <c r="N49" s="142"/>
-      <c r="O49" s="143"/>
-      <c r="P49" s="143"/>
-      <c r="Q49" s="143"/>
-      <c r="R49" s="144"/>
+      <c r="A49" s="131"/>
+      <c r="B49" s="132"/>
+      <c r="C49" s="133"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="35"/>
+      <c r="F49" s="35"/>
+      <c r="G49" s="35"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="34"/>
+      <c r="J49" s="35"/>
+      <c r="K49" s="35"/>
+      <c r="L49" s="35"/>
+      <c r="M49" s="44"/>
+      <c r="N49" s="34"/>
+      <c r="O49" s="35"/>
+      <c r="P49" s="35"/>
+      <c r="Q49" s="35"/>
+      <c r="R49" s="36"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="33"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="35"/>
-      <c r="D50" s="145"/>
-      <c r="E50" s="146"/>
-      <c r="F50" s="146"/>
-      <c r="G50" s="146"/>
-      <c r="H50" s="152"/>
-      <c r="I50" s="145"/>
-      <c r="J50" s="146"/>
-      <c r="K50" s="146"/>
-      <c r="L50" s="146"/>
-      <c r="M50" s="152"/>
-      <c r="N50" s="145"/>
-      <c r="O50" s="146"/>
-      <c r="P50" s="146"/>
-      <c r="Q50" s="146"/>
-      <c r="R50" s="147"/>
+      <c r="A50" s="134"/>
+      <c r="B50" s="135"/>
+      <c r="C50" s="136"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="37"/>
+      <c r="J50" s="38"/>
+      <c r="K50" s="38"/>
+      <c r="L50" s="38"/>
+      <c r="M50" s="45"/>
+      <c r="N50" s="37"/>
+      <c r="O50" s="38"/>
+      <c r="P50" s="38"/>
+      <c r="Q50" s="38"/>
+      <c r="R50" s="39"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="46" t="s">
+      <c r="A51" s="147" t="s">
         <v>18</v>
       </c>
-      <c r="B51" s="47"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
-      <c r="G51" s="52"/>
-      <c r="H51" s="52"/>
-      <c r="I51" s="52"/>
-      <c r="J51" s="52"/>
-      <c r="K51" s="52"/>
-      <c r="L51" s="52"/>
-      <c r="M51" s="52"/>
-      <c r="N51" s="52"/>
-      <c r="O51" s="52"/>
-      <c r="P51" s="52"/>
-      <c r="Q51" s="52"/>
-      <c r="R51" s="148"/>
+      <c r="B51" s="148"/>
+      <c r="C51" s="149"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="40"/>
+      <c r="M51" s="40"/>
+      <c r="N51" s="40"/>
+      <c r="O51" s="40"/>
+      <c r="P51" s="40"/>
+      <c r="Q51" s="40"/>
+      <c r="R51" s="41"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="49"/>
-      <c r="B52" s="50"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
-      <c r="H52" s="52"/>
-      <c r="I52" s="52"/>
-      <c r="J52" s="52"/>
-      <c r="K52" s="52"/>
-      <c r="L52" s="52"/>
-      <c r="M52" s="52"/>
-      <c r="N52" s="52"/>
-      <c r="O52" s="52"/>
-      <c r="P52" s="52"/>
-      <c r="Q52" s="52"/>
-      <c r="R52" s="148"/>
+      <c r="A52" s="150"/>
+      <c r="B52" s="151"/>
+      <c r="C52" s="152"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="40"/>
+      <c r="I52" s="40"/>
+      <c r="J52" s="40"/>
+      <c r="K52" s="40"/>
+      <c r="L52" s="40"/>
+      <c r="M52" s="40"/>
+      <c r="N52" s="40"/>
+      <c r="O52" s="40"/>
+      <c r="P52" s="40"/>
+      <c r="Q52" s="40"/>
+      <c r="R52" s="41"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
       <c r="B53" s="4"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="139"/>
-      <c r="E53" s="140"/>
-      <c r="F53" s="140"/>
-      <c r="G53" s="140"/>
-      <c r="H53" s="149"/>
-      <c r="I53" s="139"/>
-      <c r="J53" s="140"/>
-      <c r="K53" s="140"/>
-      <c r="L53" s="140"/>
-      <c r="M53" s="149"/>
-      <c r="N53" s="139"/>
-      <c r="O53" s="140"/>
-      <c r="P53" s="140"/>
-      <c r="Q53" s="140"/>
-      <c r="R53" s="141"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="42"/>
+      <c r="I53" s="31"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="42"/>
+      <c r="N53" s="31"/>
+      <c r="O53" s="32"/>
+      <c r="P53" s="32"/>
+      <c r="Q53" s="32"/>
+      <c r="R53" s="33"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="40" t="s">
+      <c r="A54" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="41"/>
-      <c r="C54" s="42"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="36"/>
-      <c r="I54" s="36"/>
-      <c r="J54" s="36"/>
-      <c r="K54" s="36"/>
-      <c r="L54" s="36"/>
-      <c r="M54" s="36"/>
-      <c r="N54" s="36"/>
-      <c r="O54" s="36"/>
-      <c r="P54" s="36"/>
-      <c r="Q54" s="36"/>
-      <c r="R54" s="37"/>
+      <c r="B54" s="142"/>
+      <c r="C54" s="143"/>
+      <c r="D54" s="137"/>
+      <c r="E54" s="137"/>
+      <c r="F54" s="137"/>
+      <c r="G54" s="137"/>
+      <c r="H54" s="137"/>
+      <c r="I54" s="137"/>
+      <c r="J54" s="137"/>
+      <c r="K54" s="137"/>
+      <c r="L54" s="137"/>
+      <c r="M54" s="137"/>
+      <c r="N54" s="137"/>
+      <c r="O54" s="137"/>
+      <c r="P54" s="137"/>
+      <c r="Q54" s="137"/>
+      <c r="R54" s="138"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="43"/>
-      <c r="B55" s="44"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="38"/>
-      <c r="I55" s="38"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="38"/>
-      <c r="L55" s="38"/>
-      <c r="M55" s="38"/>
-      <c r="N55" s="38"/>
-      <c r="O55" s="38"/>
-      <c r="P55" s="38"/>
-      <c r="Q55" s="38"/>
-      <c r="R55" s="39"/>
+      <c r="A55" s="144"/>
+      <c r="B55" s="145"/>
+      <c r="C55" s="146"/>
+      <c r="D55" s="139"/>
+      <c r="E55" s="139"/>
+      <c r="F55" s="139"/>
+      <c r="G55" s="139"/>
+      <c r="H55" s="139"/>
+      <c r="I55" s="139"/>
+      <c r="J55" s="139"/>
+      <c r="K55" s="139"/>
+      <c r="L55" s="139"/>
+      <c r="M55" s="139"/>
+      <c r="N55" s="139"/>
+      <c r="O55" s="139"/>
+      <c r="P55" s="139"/>
+      <c r="Q55" s="139"/>
+      <c r="R55" s="140"/>
     </row>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="40" t="s">
+      <c r="A56" s="141" t="s">
         <v>20</v>
       </c>
-      <c r="B56" s="41"/>
-      <c r="C56" s="42"/>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
-      <c r="H56" s="36"/>
-      <c r="I56" s="36"/>
-      <c r="J56" s="36"/>
-      <c r="K56" s="36"/>
-      <c r="L56" s="36"/>
-      <c r="M56" s="36"/>
-      <c r="N56" s="36"/>
-      <c r="O56" s="36"/>
-      <c r="P56" s="36"/>
-      <c r="Q56" s="36"/>
-      <c r="R56" s="37"/>
+      <c r="B56" s="142"/>
+      <c r="C56" s="143"/>
+      <c r="D56" s="137"/>
+      <c r="E56" s="137"/>
+      <c r="F56" s="137"/>
+      <c r="G56" s="137"/>
+      <c r="H56" s="137"/>
+      <c r="I56" s="137"/>
+      <c r="J56" s="137"/>
+      <c r="K56" s="137"/>
+      <c r="L56" s="137"/>
+      <c r="M56" s="137"/>
+      <c r="N56" s="137"/>
+      <c r="O56" s="137"/>
+      <c r="P56" s="137"/>
+      <c r="Q56" s="137"/>
+      <c r="R56" s="138"/>
     </row>
     <row r="57" spans="1:18" s="2" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="43"/>
-      <c r="B57" s="44"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="38"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="38"/>
-      <c r="L57" s="38"/>
-      <c r="M57" s="38"/>
-      <c r="N57" s="38"/>
-      <c r="O57" s="38"/>
-      <c r="P57" s="38"/>
-      <c r="Q57" s="38"/>
-      <c r="R57" s="39"/>
+      <c r="A57" s="144"/>
+      <c r="B57" s="145"/>
+      <c r="C57" s="146"/>
+      <c r="D57" s="139"/>
+      <c r="E57" s="139"/>
+      <c r="F57" s="139"/>
+      <c r="G57" s="139"/>
+      <c r="H57" s="139"/>
+      <c r="I57" s="139"/>
+      <c r="J57" s="139"/>
+      <c r="K57" s="139"/>
+      <c r="L57" s="139"/>
+      <c r="M57" s="139"/>
+      <c r="N57" s="139"/>
+      <c r="O57" s="139"/>
+      <c r="P57" s="139"/>
+      <c r="Q57" s="139"/>
+      <c r="R57" s="140"/>
     </row>
     <row r="58" spans="1:18" s="2" customFormat="1" ht="27" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D58" s="150"/>
-      <c r="E58" s="150"/>
-      <c r="F58" s="150"/>
-      <c r="G58" s="150"/>
-      <c r="H58" s="150"/>
-      <c r="I58" s="150"/>
-      <c r="J58" s="150"/>
-      <c r="K58" s="150"/>
-      <c r="L58" s="150"/>
-      <c r="M58" s="150"/>
-      <c r="N58" s="150"/>
-      <c r="O58" s="150"/>
-      <c r="P58" s="150"/>
-      <c r="Q58" s="150"/>
-      <c r="R58" s="150"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="43"/>
+      <c r="I58" s="43"/>
+      <c r="J58" s="43"/>
+      <c r="K58" s="43"/>
+      <c r="L58" s="43"/>
+      <c r="M58" s="43"/>
+      <c r="N58" s="43"/>
+      <c r="O58" s="43"/>
+      <c r="P58" s="43"/>
+      <c r="Q58" s="43"/>
+      <c r="R58" s="43"/>
     </row>
     <row r="59" spans="1:18" s="2" customFormat="1" ht="30.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D59" s="138" t="str">
+      <c r="D59" s="30" t="str">
         <f>IF(MOD(D58,1000)=0,"千円単位",IF(MOD(D58,100)=0,"百円単位",IF(MOD(D58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="138" t="str">
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30" t="str">
         <f>IF(MOD(I58,1000)=0,"千円単位",IF(MOD(I58,100)=0,"百円単位",IF(MOD(I58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="J59" s="138"/>
-      <c r="K59" s="138"/>
-      <c r="L59" s="138"/>
-      <c r="M59" s="138"/>
-      <c r="N59" s="138" t="str">
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="30"/>
+      <c r="N59" s="30" t="str">
         <f>IF(MOD(N58,1000)=0,"千円単位",IF(MOD(N58,100)=0,"百円単位",IF(MOD(N58,10)=0,"十円単位","一円単位")))</f>
         <v>千円単位</v>
       </c>
-      <c r="O59" s="138"/>
-      <c r="P59" s="138"/>
-      <c r="Q59" s="138"/>
-      <c r="R59" s="138"/>
+      <c r="O59" s="30"/>
+      <c r="P59" s="30"/>
+      <c r="Q59" s="30"/>
+      <c r="R59" s="30"/>
     </row>
     <row r="60" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="61" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2977,19 +2984,40 @@
     <row r="67" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="I59:M59"/>
-    <mergeCell ref="N59:R59"/>
-    <mergeCell ref="N53:R53"/>
-    <mergeCell ref="N49:R50"/>
-    <mergeCell ref="N51:R52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="I58:M58"/>
-    <mergeCell ref="N58:R58"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="I53:M53"/>
-    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="N56:R57"/>
+    <mergeCell ref="D54:H55"/>
+    <mergeCell ref="I54:M55"/>
+    <mergeCell ref="N54:R55"/>
+    <mergeCell ref="A54:C55"/>
+    <mergeCell ref="A56:C57"/>
+    <mergeCell ref="D56:H57"/>
+    <mergeCell ref="I56:M57"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="I51:M52"/>
+    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A22:C28"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:R21"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="O22:R28"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="D33:R34"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="H45:J45"/>
     <mergeCell ref="A43:C44"/>
@@ -3006,40 +3034,19 @@
     <mergeCell ref="H43:J44"/>
     <mergeCell ref="D41:G42"/>
     <mergeCell ref="H41:J42"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="D31:I32"/>
-    <mergeCell ref="D33:R34"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A22:C28"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:R21"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="O22:R28"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="N56:R57"/>
-    <mergeCell ref="D54:H55"/>
-    <mergeCell ref="I54:M55"/>
-    <mergeCell ref="N54:R55"/>
-    <mergeCell ref="A54:C55"/>
-    <mergeCell ref="A56:C57"/>
-    <mergeCell ref="D56:H57"/>
-    <mergeCell ref="I56:M57"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="I51:M52"/>
-    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="I59:M59"/>
+    <mergeCell ref="N59:R59"/>
+    <mergeCell ref="N53:R53"/>
+    <mergeCell ref="N49:R50"/>
+    <mergeCell ref="N51:R52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="I58:M58"/>
+    <mergeCell ref="N58:R58"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="I53:M53"/>
+    <mergeCell ref="I49:M50"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="D51:R52">
@@ -3081,7 +3088,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D737899-3511-4F7A-96FD-F5F4470F525C}">
-  <dimension ref="B2:N28"/>
+  <dimension ref="B2:N29"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="15" width="4.625" customWidth="1"/>
@@ -3113,40 +3120,40 @@
       <c r="N2" s="160"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="161" t="s">
+      <c r="B3" s="154" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="161"/>
+      <c r="C3" s="154"/>
       <c r="D3" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="161"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="161"/>
-      <c r="J3" s="161"/>
-      <c r="K3" s="161"/>
-      <c r="L3" s="161"/>
-      <c r="M3" s="161"/>
-      <c r="N3" s="161"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="154"/>
+      <c r="M3" s="154"/>
+      <c r="N3" s="154"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="161"/>
-      <c r="C4" s="161"/>
+      <c r="B4" s="154"/>
+      <c r="C4" s="154"/>
       <c r="D4" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="161"/>
-      <c r="F4" s="161"/>
-      <c r="G4" s="161"/>
-      <c r="H4" s="161"/>
-      <c r="I4" s="161"/>
-      <c r="J4" s="161"/>
-      <c r="K4" s="161"/>
-      <c r="L4" s="161"/>
-      <c r="M4" s="161"/>
-      <c r="N4" s="161"/>
+      <c r="E4" s="154"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="154"/>
+      <c r="I4" s="154"/>
+      <c r="J4" s="154"/>
+      <c r="K4" s="154"/>
+      <c r="L4" s="154"/>
+      <c r="M4" s="154"/>
+      <c r="N4" s="154"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -3167,62 +3174,62 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="156" t="s">
+      <c r="E6" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="157"/>
-      <c r="G6" s="156" t="s">
+      <c r="F6" s="162"/>
+      <c r="G6" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="157"/>
-      <c r="I6" s="156" t="s">
+      <c r="H6" s="162"/>
+      <c r="I6" s="161" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="157"/>
-      <c r="K6" s="156" t="s">
+      <c r="J6" s="162"/>
+      <c r="K6" s="161" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="157"/>
-      <c r="M6" s="156" t="s">
+      <c r="L6" s="162"/>
+      <c r="M6" s="161" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="157"/>
+      <c r="N6" s="162"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="161" t="s">
+      <c r="B7" s="154" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="161"/>
+      <c r="C7" s="154"/>
       <c r="D7" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="158"/>
-      <c r="F7" s="159"/>
-      <c r="G7" s="163"/>
-      <c r="H7" s="164"/>
-      <c r="I7" s="158"/>
-      <c r="J7" s="159"/>
-      <c r="K7" s="158"/>
-      <c r="L7" s="159"/>
-      <c r="M7" s="158"/>
-      <c r="N7" s="159"/>
+      <c r="E7" s="155"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="157"/>
+      <c r="H7" s="158"/>
+      <c r="I7" s="155"/>
+      <c r="J7" s="156"/>
+      <c r="K7" s="155"/>
+      <c r="L7" s="156"/>
+      <c r="M7" s="155"/>
+      <c r="N7" s="156"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="161"/>
-      <c r="C8" s="161"/>
+      <c r="B8" s="154"/>
+      <c r="C8" s="154"/>
       <c r="D8" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="158"/>
-      <c r="F8" s="159"/>
-      <c r="G8" s="158"/>
-      <c r="H8" s="159"/>
-      <c r="I8" s="158"/>
-      <c r="J8" s="159"/>
-      <c r="K8" s="158"/>
-      <c r="L8" s="159"/>
-      <c r="M8" s="158"/>
-      <c r="N8" s="159"/>
+      <c r="E8" s="155"/>
+      <c r="F8" s="156"/>
+      <c r="G8" s="155"/>
+      <c r="H8" s="156"/>
+      <c r="I8" s="155"/>
+      <c r="J8" s="156"/>
+      <c r="K8" s="155"/>
+      <c r="L8" s="156"/>
+      <c r="M8" s="155"/>
+      <c r="N8" s="156"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
@@ -3243,62 +3250,62 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="156" t="s">
+      <c r="E10" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="157"/>
-      <c r="G10" s="156" t="s">
+      <c r="F10" s="162"/>
+      <c r="G10" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="157"/>
-      <c r="I10" s="156" t="s">
+      <c r="H10" s="162"/>
+      <c r="I10" s="161" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="157"/>
-      <c r="K10" s="156" t="s">
+      <c r="J10" s="162"/>
+      <c r="K10" s="161" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="157"/>
-      <c r="M10" s="156" t="s">
+      <c r="L10" s="162"/>
+      <c r="M10" s="161" t="s">
         <v>26</v>
       </c>
-      <c r="N10" s="157"/>
+      <c r="N10" s="162"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="161" t="s">
+      <c r="B11" s="154" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="161"/>
+      <c r="C11" s="154"/>
       <c r="D11" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="158"/>
-      <c r="F11" s="159"/>
-      <c r="G11" s="163"/>
-      <c r="H11" s="164"/>
-      <c r="I11" s="158"/>
-      <c r="J11" s="159"/>
-      <c r="K11" s="158"/>
-      <c r="L11" s="159"/>
-      <c r="M11" s="158"/>
-      <c r="N11" s="159"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="157"/>
+      <c r="H11" s="158"/>
+      <c r="I11" s="155"/>
+      <c r="J11" s="156"/>
+      <c r="K11" s="155"/>
+      <c r="L11" s="156"/>
+      <c r="M11" s="155"/>
+      <c r="N11" s="156"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="161"/>
-      <c r="C12" s="161"/>
+      <c r="B12" s="154"/>
+      <c r="C12" s="154"/>
       <c r="D12" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="158"/>
-      <c r="F12" s="159"/>
-      <c r="G12" s="158"/>
-      <c r="H12" s="159"/>
-      <c r="I12" s="158"/>
-      <c r="J12" s="159"/>
-      <c r="K12" s="158"/>
-      <c r="L12" s="159"/>
-      <c r="M12" s="158"/>
-      <c r="N12" s="159"/>
+      <c r="E12" s="155"/>
+      <c r="F12" s="156"/>
+      <c r="G12" s="155"/>
+      <c r="H12" s="156"/>
+      <c r="I12" s="155"/>
+      <c r="J12" s="156"/>
+      <c r="K12" s="155"/>
+      <c r="L12" s="156"/>
+      <c r="M12" s="155"/>
+      <c r="N12" s="156"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
@@ -3334,62 +3341,62 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="156" t="s">
+      <c r="E15" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="157"/>
-      <c r="G15" s="156" t="s">
+      <c r="F15" s="162"/>
+      <c r="G15" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="157"/>
-      <c r="I15" s="156" t="s">
+      <c r="H15" s="162"/>
+      <c r="I15" s="161" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="157"/>
-      <c r="K15" s="156" t="s">
+      <c r="J15" s="162"/>
+      <c r="K15" s="161" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="157"/>
-      <c r="M15" s="156" t="s">
+      <c r="L15" s="162"/>
+      <c r="M15" s="161" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="157"/>
+      <c r="N15" s="162"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="161" t="s">
+      <c r="B16" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="161"/>
+      <c r="C16" s="154"/>
       <c r="D16" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="158"/>
-      <c r="F16" s="159"/>
-      <c r="G16" s="163"/>
-      <c r="H16" s="164"/>
-      <c r="I16" s="158"/>
-      <c r="J16" s="159"/>
-      <c r="K16" s="158"/>
-      <c r="L16" s="159"/>
-      <c r="M16" s="158"/>
-      <c r="N16" s="159"/>
+      <c r="E16" s="155"/>
+      <c r="F16" s="156"/>
+      <c r="G16" s="157"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="155"/>
+      <c r="J16" s="156"/>
+      <c r="K16" s="155"/>
+      <c r="L16" s="156"/>
+      <c r="M16" s="155"/>
+      <c r="N16" s="156"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="161"/>
-      <c r="C17" s="161"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="154"/>
       <c r="D17" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="158"/>
-      <c r="F17" s="159"/>
-      <c r="G17" s="158"/>
-      <c r="H17" s="159"/>
-      <c r="I17" s="158"/>
-      <c r="J17" s="159"/>
-      <c r="K17" s="158"/>
-      <c r="L17" s="159"/>
-      <c r="M17" s="158"/>
-      <c r="N17" s="159"/>
+      <c r="E17" s="155"/>
+      <c r="F17" s="156"/>
+      <c r="G17" s="155"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="155"/>
+      <c r="J17" s="156"/>
+      <c r="K17" s="155"/>
+      <c r="L17" s="156"/>
+      <c r="M17" s="155"/>
+      <c r="N17" s="156"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B20" s="153"/>
@@ -3413,15 +3420,15 @@
       </c>
       <c r="C21" s="153"/>
       <c r="D21" s="153"/>
-      <c r="E21" s="154"/>
-      <c r="F21" s="154"/>
+      <c r="E21" s="163"/>
+      <c r="F21" s="163"/>
       <c r="I21" s="153" t="s">
         <v>44</v>
       </c>
       <c r="J21" s="153"/>
       <c r="K21" s="153"/>
-      <c r="L21" s="154"/>
-      <c r="M21" s="154"/>
+      <c r="L21" s="163"/>
+      <c r="M21" s="163"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B22" s="153" t="s">
@@ -3429,15 +3436,15 @@
       </c>
       <c r="C22" s="153"/>
       <c r="D22" s="153"/>
-      <c r="E22" s="154"/>
-      <c r="F22" s="154"/>
+      <c r="E22" s="163"/>
+      <c r="F22" s="163"/>
       <c r="I22" s="153" t="s">
         <v>45</v>
       </c>
       <c r="J22" s="153"/>
       <c r="K22" s="153"/>
-      <c r="L22" s="154"/>
-      <c r="M22" s="154"/>
+      <c r="L22" s="163"/>
+      <c r="M22" s="163"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B23" s="153" t="s">
@@ -3445,98 +3452,164 @@
       </c>
       <c r="C23" s="153"/>
       <c r="D23" s="153"/>
-      <c r="E23" s="154"/>
-      <c r="F23" s="154"/>
+      <c r="E23" s="163"/>
+      <c r="F23" s="163"/>
       <c r="I23" s="153" t="s">
         <v>46</v>
       </c>
       <c r="J23" s="153"/>
       <c r="K23" s="153"/>
-      <c r="L23" s="154"/>
-      <c r="M23" s="154"/>
+      <c r="L23" s="163"/>
+      <c r="M23" s="163"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B24" s="153" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C24" s="153"/>
       <c r="D24" s="153"/>
-      <c r="E24" s="154"/>
-      <c r="F24" s="154"/>
+      <c r="E24" s="163"/>
+      <c r="F24" s="163"/>
       <c r="I24" s="153" t="s">
         <v>47</v>
       </c>
       <c r="J24" s="153"/>
       <c r="K24" s="153"/>
-      <c r="L24" s="154"/>
-      <c r="M24" s="154"/>
+      <c r="L24" s="163"/>
+      <c r="M24" s="163"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B25" s="153" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25" s="153"/>
       <c r="D25" s="153"/>
-      <c r="E25" s="154"/>
-      <c r="F25" s="154"/>
+      <c r="E25" s="163"/>
+      <c r="F25" s="163"/>
       <c r="I25" s="153" t="s">
         <v>39</v>
       </c>
       <c r="J25" s="153"/>
       <c r="K25" s="153"/>
-      <c r="L25" s="154"/>
-      <c r="M25" s="154"/>
+      <c r="L25" s="163"/>
+      <c r="M25" s="163"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B26" s="153" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C26" s="153"/>
       <c r="D26" s="153"/>
-      <c r="E26" s="155"/>
-      <c r="F26" s="155"/>
+      <c r="E26" s="163"/>
+      <c r="F26" s="163"/>
       <c r="I26" s="153" t="s">
         <v>43</v>
       </c>
       <c r="J26" s="153"/>
       <c r="K26" s="153"/>
-      <c r="L26" s="154"/>
-      <c r="M26" s="154"/>
+      <c r="L26" s="163"/>
+      <c r="M26" s="163"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B27" s="153" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="153"/>
       <c r="D27" s="153"/>
-      <c r="E27" s="154"/>
-      <c r="F27" s="154"/>
+      <c r="E27" s="164"/>
+      <c r="F27" s="164"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B28" s="153" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="153"/>
       <c r="D28" s="153"/>
-      <c r="E28" s="154"/>
-      <c r="F28" s="154"/>
+      <c r="E28" s="163"/>
+      <c r="F28" s="163"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B29" s="153" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="153"/>
+      <c r="D29" s="153"/>
+      <c r="E29" s="163"/>
+      <c r="F29" s="163"/>
     </row>
   </sheetData>
-  <mergeCells count="96">
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
+  <mergeCells count="98">
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="E4:F4"/>
@@ -3550,75 +3623,20 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
